--- a/easy-widget-excel/中文.xlsx
+++ b/easy-widget-excel/中文.xlsx
@@ -9,17 +9,56 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8860" tabRatio="769" firstSheet="21" activeTab="24"/>
   </bookViews>
   <sheets>
-    <sheet name="PAY_HIS_DIST-支出分布历史数据" sheetId="48" r:id="rId1"/>
+    <sheet name="POP_HIS_PERMA-常住人口历史数据" sheetId="49" r:id="rId1"/>
+    <sheet name="POP_HIS_INSU-参保人口历史数据" sheetId="50" r:id="rId2"/>
+    <sheet name="POP_HIS_STT-人口统计历史数据" sheetId="51" r:id="rId3"/>
+    <sheet name="POP_HIS_FLOW-人口流动历史数据" sheetId="52" r:id="rId4"/>
+    <sheet name="POP_FORT_PERMA-常住人口预测结果" sheetId="53" r:id="rId5"/>
+    <sheet name="POP_FORT_INSU-参保人口预测结果" sheetId="54" r:id="rId6"/>
+    <sheet name="POP_FORT_STT-人口统计预测结果" sheetId="55" r:id="rId7"/>
+    <sheet name="POP_FORT_FLOW-人口流动预测结果" sheetId="56" r:id="rId8"/>
+    <sheet name="POP_FORT_FAC-人口因子标准预测" sheetId="57" r:id="rId9"/>
+    <sheet name="FAC_HIS_STT-影响因子历史数据" sheetId="58" r:id="rId10"/>
+    <sheet name="FAC_FORT_USER-影响因子用户定义" sheetId="59" r:id="rId11"/>
+    <sheet name="FAC_FORT_STD-影响因子标准预测" sheetId="60" r:id="rId12"/>
+    <sheet name="FAC_FORT_ADJ-影响因子预测结果" sheetId="61" r:id="rId13"/>
+    <sheet name="INC_HIS_BASE-基金收入历史数据" sheetId="62" r:id="rId14"/>
+    <sheet name="INC_HIS_DIST-职工收入分布历史" sheetId="63" r:id="rId15"/>
+    <sheet name="INC_HIS_CUM-基金累计收支历史" sheetId="64" r:id="rId16"/>
+    <sheet name="INC_FORT_BASE-基金收入预测结果" sheetId="65" r:id="rId17"/>
+    <sheet name="INC_FORT_DIST-职工收入分布预测" sheetId="66" r:id="rId18"/>
+    <sheet name="INC_HIS_RICH-贫富差距分析历史" sheetId="86" r:id="rId19"/>
+    <sheet name="INC_FORT_RICH-贫富差距分析预测" sheetId="87" r:id="rId20"/>
+    <sheet name="INC_HIS_KAKW-指数历史" sheetId="88" r:id="rId21"/>
+    <sheet name="INC_FORT_KAKW-KAKWANI指数预测" sheetId="89" r:id="rId22"/>
+    <sheet name="PAY_HIS_BASE-基金支出历史数据" sheetId="67" r:id="rId23"/>
+    <sheet name="PAY_HIS_RESU-医疗资源历史数据" sheetId="68" r:id="rId24"/>
+    <sheet name="PAY_HIS_DIST-支出分布历史数据" sheetId="69" r:id="rId25"/>
+    <sheet name="PAY_HIS_DIST_DETL-支出分布明细历史" sheetId="70" r:id="rId26"/>
+    <sheet name="PAY_HIS_DIAG-疾病诊断历史数据" sheetId="71" r:id="rId27"/>
+    <sheet name="PAY_HIS_DIAG_FEE-疾病费用历史数据" sheetId="72" r:id="rId28"/>
+    <sheet name="PAY_HIS_OUT_FLOW-异地流向历史数据" sheetId="73" r:id="rId29"/>
+    <sheet name="PAY_HIS_OUT_DIAG-异地诊断历史数据" sheetId="74" r:id="rId30"/>
+    <sheet name="PAY_HIS_OUT_DEPT-异地科室历史数据" sheetId="75" r:id="rId31"/>
+    <sheet name="PAY_FORT_BASE-基金支出预测结果" sheetId="76" r:id="rId32"/>
+    <sheet name="PAY_FORT_RESU-医疗资源预测结果" sheetId="77" r:id="rId33"/>
+    <sheet name="PAY_FORT_DIST-支出分布预测结果" sheetId="78" r:id="rId34"/>
+    <sheet name="PAY_FORT_DIST_DETL-支出分布明细预测" sheetId="79" r:id="rId35"/>
+    <sheet name="PAY_FORT_DIAG-疾病诊断预测结果" sheetId="80" r:id="rId36"/>
+    <sheet name="PAY_FORT_DIAG_FEE-疾病费用预测结果" sheetId="81" r:id="rId37"/>
+    <sheet name="PAY_FORT_OUT_FLOW-异地流向预测结果" sheetId="82" r:id="rId38"/>
+    <sheet name="PAY_FORT_OUT_DIAG-异地诊断预测结果" sheetId="83" r:id="rId39"/>
+    <sheet name="PAY_FORT_OUT_DEPT-异地科室预测结果" sheetId="84" r:id="rId40"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="185">
   <si>
     <t>字段名</t>
   </si>
@@ -73,13 +112,514 @@
   </si>
   <si>
     <t>1%，10%，20%，80%</t>
+  </si>
+  <si>
+    <t>市级</t>
+  </si>
+  <si>
+    <t>AGE_SEC</t>
+  </si>
+  <si>
+    <t>年龄段</t>
+  </si>
+  <si>
+    <t>PERMA_POP</t>
+  </si>
+  <si>
+    <t>常住人口数</t>
+  </si>
+  <si>
+    <t>INSUTYPE</t>
+  </si>
+  <si>
+    <t>险种类型</t>
+  </si>
+  <si>
+    <t>职工或居民</t>
+  </si>
+  <si>
+    <t>PSN_TYPE</t>
+  </si>
+  <si>
+    <t>人员类别</t>
+  </si>
+  <si>
+    <t>RESD_NATU</t>
+  </si>
+  <si>
+    <t>户口性质</t>
+  </si>
+  <si>
+    <t>本地或流动</t>
+  </si>
+  <si>
+    <t>INSU_PSNCNT</t>
+  </si>
+  <si>
+    <t>参保人数</t>
+  </si>
+  <si>
+    <t>省级和市级</t>
+  </si>
+  <si>
+    <t>FLOW_POP</t>
+  </si>
+  <si>
+    <t>流动人口数</t>
+  </si>
+  <si>
+    <t>流动常住人口量</t>
+  </si>
+  <si>
+    <t>MATN_RATE</t>
+  </si>
+  <si>
+    <t>生育率</t>
+  </si>
+  <si>
+    <t>DIE_RATE</t>
+  </si>
+  <si>
+    <t>死亡率</t>
+  </si>
+  <si>
+    <t>ADMDVS_SOUC</t>
+  </si>
+  <si>
+    <t>迁移源</t>
+  </si>
+  <si>
+    <t>外省或內省地市</t>
+  </si>
+  <si>
+    <t>NET_FLOW_PSNCNT</t>
+  </si>
+  <si>
+    <t>净流入人数</t>
+  </si>
+  <si>
+    <t>未来</t>
+  </si>
+  <si>
+    <t>SCHM_ID</t>
+  </si>
+  <si>
+    <t>方案ID</t>
+  </si>
+  <si>
+    <t>标准方案</t>
+  </si>
+  <si>
+    <t>INSU_RATE</t>
+  </si>
+  <si>
+    <t>参保率</t>
+  </si>
+  <si>
+    <t>历史年份</t>
+  </si>
+  <si>
+    <t>PERPSN_GDP</t>
+  </si>
+  <si>
+    <t>人均GDP</t>
+  </si>
+  <si>
+    <t>SOCA_AVESAL</t>
+  </si>
+  <si>
+    <t>社会平均工资</t>
+  </si>
+  <si>
+    <t>收入因子</t>
+  </si>
+  <si>
+    <t>STAF_CLCT_STD</t>
+  </si>
+  <si>
+    <t>职工筹资标准</t>
+  </si>
+  <si>
+    <t>FLXEMPE_CLCT_STD</t>
+  </si>
+  <si>
+    <t>灵活筹资标准</t>
+  </si>
+  <si>
+    <t>RSDT_CLCT_STD</t>
+  </si>
+  <si>
+    <t>居民筹资标准</t>
+  </si>
+  <si>
+    <t>STU_CLCT_STD</t>
+  </si>
+  <si>
+    <t>学生筹资标准</t>
+  </si>
+  <si>
+    <t>PERPSN_MED_PAY</t>
+  </si>
+  <si>
+    <t>人均医疗支出</t>
+  </si>
+  <si>
+    <t>支出因子</t>
+  </si>
+  <si>
+    <t>STAF_PAY_STD</t>
+  </si>
+  <si>
+    <t>在职支出标准</t>
+  </si>
+  <si>
+    <t>RETR_PAY_STD</t>
+  </si>
+  <si>
+    <t>退休支出标准</t>
+  </si>
+  <si>
+    <t>FLXEMPE_PAY_STD</t>
+  </si>
+  <si>
+    <t>灵活支出标准</t>
+  </si>
+  <si>
+    <t>RSDT_PAY_STD</t>
+  </si>
+  <si>
+    <t>居民支出标准</t>
+  </si>
+  <si>
+    <t>STU_PAY_STD</t>
+  </si>
+  <si>
+    <t>学生支出标准</t>
+  </si>
+  <si>
+    <t>唯一标志</t>
+  </si>
+  <si>
+    <t>未来年份</t>
+  </si>
+  <si>
+    <t>经济因子</t>
+  </si>
+  <si>
+    <t>人口因子</t>
+  </si>
+  <si>
+    <t>本地或流动人口</t>
+  </si>
+  <si>
+    <t>CLCT_PSNTIME</t>
+  </si>
+  <si>
+    <t>缴费人次</t>
+  </si>
+  <si>
+    <t>AVG_CLCTSTD</t>
+  </si>
+  <si>
+    <t>次均缴费基数</t>
+  </si>
+  <si>
+    <t>AVG_CLCT_AMT</t>
+  </si>
+  <si>
+    <t>次均缴费金额</t>
+  </si>
+  <si>
+    <t>省市分开统计</t>
+  </si>
+  <si>
+    <t>每1%一档</t>
+  </si>
+  <si>
+    <t>STAF_INC</t>
+  </si>
+  <si>
+    <t>职工总工资收入</t>
+  </si>
+  <si>
+    <t>STAF_PAY</t>
+  </si>
+  <si>
+    <t>职工总医疗支出</t>
+  </si>
+  <si>
+    <t>FUND_CUM_PAY</t>
+  </si>
+  <si>
+    <t>基金累计收入</t>
+  </si>
+  <si>
+    <t>FUND_CUM_INC</t>
+  </si>
+  <si>
+    <t>基金累计支出</t>
+  </si>
+  <si>
+    <t>人口因子相关</t>
+  </si>
+  <si>
+    <t>收入因子相关</t>
+  </si>
+  <si>
+    <t>支出因子相关</t>
+  </si>
+  <si>
+    <t>MEDINSLV</t>
+  </si>
+  <si>
+    <t>医疗机构等级</t>
+  </si>
+  <si>
+    <t>MED_TYPE</t>
+  </si>
+  <si>
+    <t>医疗类别</t>
+  </si>
+  <si>
+    <t>门诊或住院</t>
+  </si>
+  <si>
+    <t>AVG_IPT_DAYS</t>
+  </si>
+  <si>
+    <t>次均住院天数</t>
+  </si>
+  <si>
+    <t>AVG_MED_FEE</t>
+  </si>
+  <si>
+    <t>次均医疗费用</t>
+  </si>
+  <si>
+    <t>AVG_HIFP_PAY</t>
+  </si>
+  <si>
+    <t>次均基本统筹基金</t>
+  </si>
+  <si>
+    <t>AVG_HIFMI_PAY</t>
+  </si>
+  <si>
+    <t>次均大病医保基金</t>
+  </si>
+  <si>
+    <t>AVG_MAF_PAY</t>
+  </si>
+  <si>
+    <t>次均医疗救助基金</t>
+  </si>
+  <si>
+    <t>AVG_ACCT_PAY</t>
+  </si>
+  <si>
+    <t>次均个账支出</t>
+  </si>
+  <si>
+    <t>AVG_PSN_PAY</t>
+  </si>
+  <si>
+    <t>次均个人自付</t>
+  </si>
+  <si>
+    <t>LV3_MEDINS_CNT</t>
+  </si>
+  <si>
+    <t>三级机构数</t>
+  </si>
+  <si>
+    <t>LV2_MEDINS_CNT</t>
+  </si>
+  <si>
+    <t>二级机构数</t>
+  </si>
+  <si>
+    <t>LV1_MEDINS_CNT</t>
+  </si>
+  <si>
+    <t>一级或无等级机构数</t>
+  </si>
+  <si>
+    <t>FIXPHAC_CNT</t>
+  </si>
+  <si>
+    <t>定点药店数</t>
+  </si>
+  <si>
+    <t>DR_PSNCNT</t>
+  </si>
+  <si>
+    <t>医师数</t>
+  </si>
+  <si>
+    <t>NURS_PSNCNT</t>
+  </si>
+  <si>
+    <t>护士数</t>
+  </si>
+  <si>
+    <t>BED_VAL</t>
+  </si>
+  <si>
+    <t>床位数</t>
+  </si>
+  <si>
+    <t>省级</t>
+  </si>
+  <si>
+    <t>固定10%</t>
+  </si>
+  <si>
+    <t>CITY_ADMDVS</t>
+  </si>
+  <si>
+    <t>市级医保区划</t>
+  </si>
+  <si>
+    <t>GEND</t>
+  </si>
+  <si>
+    <t>性别</t>
+  </si>
+  <si>
+    <t>DIAG_CODE</t>
+  </si>
+  <si>
+    <t>诊断代码</t>
+  </si>
+  <si>
+    <t>NW_PATN_PSNCNT</t>
+  </si>
+  <si>
+    <t>新增病人数</t>
+  </si>
+  <si>
+    <t>发病率</t>
+  </si>
+  <si>
+    <t>MDTRT_PSNCNT</t>
+  </si>
+  <si>
+    <t>就诊人数</t>
+  </si>
+  <si>
+    <t>患病率</t>
+  </si>
+  <si>
+    <t>DIE_PSNCNT</t>
+  </si>
+  <si>
+    <t>死亡人数</t>
+  </si>
+  <si>
+    <t>TCMHERB_FEE</t>
+  </si>
+  <si>
+    <t>中草药费</t>
+  </si>
+  <si>
+    <t>TCMPAT_FEE</t>
+  </si>
+  <si>
+    <t>中成药费</t>
+  </si>
+  <si>
+    <t>WMFEE</t>
+  </si>
+  <si>
+    <t>西药费</t>
+  </si>
+  <si>
+    <t>OPRN_FEE</t>
+  </si>
+  <si>
+    <t>手术费</t>
+  </si>
+  <si>
+    <t>BEDFEE</t>
+  </si>
+  <si>
+    <t>床位费</t>
+  </si>
+  <si>
+    <t>TRTFEE</t>
+  </si>
+  <si>
+    <t>诊疗费</t>
+  </si>
+  <si>
+    <t>EXAMFEE</t>
+  </si>
+  <si>
+    <t>检查费</t>
+  </si>
+  <si>
+    <t>OTH_FEE</t>
+  </si>
+  <si>
+    <t>其他费</t>
+  </si>
+  <si>
+    <t>INSU_ADMDVS</t>
+  </si>
+  <si>
+    <t>参保医保区划</t>
+  </si>
+  <si>
+    <t>外省或内市</t>
+  </si>
+  <si>
+    <t>MDTRT_ADMDVS</t>
+  </si>
+  <si>
+    <t>就医医保区划</t>
+  </si>
+  <si>
+    <t>内市</t>
+  </si>
+  <si>
+    <t>DEPT_NAME</t>
+  </si>
+  <si>
+    <t>科室名称</t>
+  </si>
+  <si>
+    <t>市级则填本身</t>
+  </si>
+  <si>
+    <t>FAIR_LINE</t>
+  </si>
+  <si>
+    <t>绝对公平线</t>
+  </si>
+  <si>
+    <t>CONC_CURVE</t>
+  </si>
+  <si>
+    <t>集中曲线</t>
+  </si>
+  <si>
+    <t>LORENZ_CURVE</t>
+  </si>
+  <si>
+    <t>洛伦兹曲线</t>
+  </si>
+  <si>
+    <t>KAKWANI</t>
+  </si>
+  <si>
+    <t>KAKWANI指数</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -108,6 +648,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,7 +731,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -199,6 +746,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -480,6 +1036,1185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -497,6 +2232,97 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>12</v>
@@ -507,7 +2333,9 @@
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -525,6 +2353,1190 @@
     </row>
     <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="41" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -560,6 +3572,2822 @@
         <v>7</v>
       </c>
       <c r="D6" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="41" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/easy-widget-excel/中文.xlsx
+++ b/easy-widget-excel/中文.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8860" tabRatio="769" firstSheet="21" activeTab="24"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" tabRatio="769" firstSheet="32" activeTab="35"/>
   </bookViews>
   <sheets>
     <sheet name="POP_HIS_PERMA-常住人口历史数据" sheetId="49" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="188">
   <si>
     <t>字段名</t>
   </si>
@@ -507,9 +507,6 @@
     <t>就诊人数</t>
   </si>
   <si>
-    <t>患病率</t>
-  </si>
-  <si>
     <t>DIE_PSNCNT</t>
   </si>
   <si>
@@ -613,6 +610,19 @@
   </si>
   <si>
     <t>KAKWANI指数</t>
+  </si>
+  <si>
+    <t>字段名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUM_MDTRT_PSNCNT</t>
+  </si>
+  <si>
+    <t>累计就诊人数</t>
+  </si>
+  <si>
+    <t>患病率，需统计5年患病人数</t>
   </si>
 </sst>
 </file>
@@ -1037,9 +1047,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -1067,7 +1077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1081,7 +1091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -1093,7 +1103,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1115,9 +1125,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -1145,7 +1155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1159,7 +1169,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>53</v>
       </c>
@@ -1171,7 +1181,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>50</v>
       </c>
@@ -1183,7 +1193,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>55</v>
       </c>
@@ -1197,7 +1207,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1211,7 +1221,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>60</v>
       </c>
@@ -1225,7 +1235,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
@@ -1239,7 +1249,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
@@ -1253,7 +1263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -1267,7 +1277,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>69</v>
       </c>
@@ -1281,7 +1291,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>71</v>
       </c>
@@ -1295,7 +1305,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1309,7 +1319,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>75</v>
       </c>
@@ -1323,7 +1333,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
@@ -1346,9 +1356,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1362,7 +1372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -1376,7 +1386,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1390,7 +1400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1404,7 +1414,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>53</v>
       </c>
@@ -1418,7 +1428,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>50</v>
       </c>
@@ -1432,7 +1442,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1456,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
@@ -1460,7 +1470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -1474,7 +1484,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>62</v>
       </c>
@@ -1488,7 +1498,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>64</v>
       </c>
@@ -1502,7 +1512,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -1516,7 +1526,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>69</v>
       </c>
@@ -1530,7 +1540,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>71</v>
       </c>
@@ -1544,7 +1554,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>73</v>
       </c>
@@ -1558,7 +1568,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1572,7 +1582,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>77</v>
       </c>
@@ -1595,9 +1605,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1611,7 +1621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -1625,7 +1635,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1637,7 +1647,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1651,7 +1661,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>53</v>
       </c>
@@ -1665,7 +1675,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>50</v>
       </c>
@@ -1679,7 +1689,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>55</v>
       </c>
@@ -1693,7 +1703,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
@@ -1707,7 +1717,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -1721,7 +1731,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>62</v>
       </c>
@@ -1735,7 +1745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>64</v>
       </c>
@@ -1749,7 +1759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -1763,7 +1773,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>69</v>
       </c>
@@ -1777,7 +1787,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>71</v>
       </c>
@@ -1791,7 +1801,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>73</v>
       </c>
@@ -1805,7 +1815,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1819,7 +1829,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>77</v>
       </c>
@@ -1842,9 +1852,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1858,7 +1868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -1872,7 +1882,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1884,7 +1894,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1898,7 +1908,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>50</v>
       </c>
@@ -1912,7 +1922,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>55</v>
       </c>
@@ -1926,7 +1936,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1940,7 +1950,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>60</v>
       </c>
@@ -1954,7 +1964,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
@@ -1968,7 +1978,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>64</v>
       </c>
@@ -1982,7 +1992,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -1996,7 +2006,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>69</v>
       </c>
@@ -2010,7 +2020,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>71</v>
       </c>
@@ -2024,7 +2034,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -2038,7 +2048,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>75</v>
       </c>
@@ -2052,7 +2062,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
@@ -2075,9 +2085,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2091,7 +2101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2105,7 +2115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2119,7 +2129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -2131,7 +2141,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -2145,7 +2155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -2157,7 +2167,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
@@ -2171,7 +2181,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>84</v>
       </c>
@@ -2183,7 +2193,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>86</v>
       </c>
@@ -2195,7 +2205,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
@@ -2216,9 +2226,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2232,7 +2242,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2246,7 +2256,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2260,7 +2270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -2274,7 +2284,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>92</v>
       </c>
@@ -2286,7 +2296,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>94</v>
       </c>
@@ -2307,9 +2317,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2323,7 +2333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2337,7 +2347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2351,7 +2361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>96</v>
       </c>
@@ -2363,7 +2373,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>98</v>
       </c>
@@ -2384,9 +2394,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2400,7 +2410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -2412,7 +2422,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2424,7 +2434,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2438,7 +2448,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -2450,7 +2460,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -2464,7 +2474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -2476,7 +2486,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -2490,7 +2500,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>84</v>
       </c>
@@ -2504,7 +2514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>86</v>
       </c>
@@ -2518,7 +2528,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
@@ -2541,9 +2551,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2557,7 +2567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -2569,7 +2579,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2581,7 +2591,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2595,7 +2605,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2609,7 +2619,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>92</v>
       </c>
@@ -2623,7 +2633,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>94</v>
       </c>
@@ -2646,9 +2656,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2662,7 +2672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2674,7 +2684,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2688,7 +2698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -2702,36 +2712,36 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
@@ -2747,9 +2757,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2763,7 +2773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2777,7 +2787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -2791,7 +2801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -2803,7 +2813,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -2817,7 +2827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -2829,7 +2839,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
@@ -2843,7 +2853,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -2864,9 +2874,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2880,7 +2890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -2892,7 +2902,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2904,7 +2914,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2918,7 +2928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2932,36 +2942,36 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
@@ -2977,9 +2987,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2993,7 +3003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3005,7 +3015,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3019,12 +3029,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>7</v>
@@ -3040,9 +3050,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3056,7 +3066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -3068,7 +3078,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -3080,7 +3090,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -3094,12 +3104,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
@@ -3115,9 +3125,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3131,7 +3141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3145,7 +3155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3159,7 +3169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -3171,7 +3181,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -3185,7 +3195,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -3197,7 +3207,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
@@ -3211,7 +3221,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>103</v>
       </c>
@@ -3223,7 +3233,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>105</v>
       </c>
@@ -3237,7 +3247,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3259,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>108</v>
       </c>
@@ -3261,7 +3271,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>110</v>
       </c>
@@ -3273,7 +3283,7 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -3285,7 +3295,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>112</v>
       </c>
@@ -3297,7 +3307,7 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>114</v>
       </c>
@@ -3309,7 +3319,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>116</v>
       </c>
@@ -3321,7 +3331,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>118</v>
       </c>
@@ -3333,7 +3343,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>120</v>
       </c>
@@ -3354,9 +3364,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3370,7 +3380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3384,7 +3394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3398,7 +3408,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>122</v>
       </c>
@@ -3410,7 +3420,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>124</v>
       </c>
@@ -3422,7 +3432,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="41" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>126</v>
       </c>
@@ -3434,7 +3444,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>128</v>
       </c>
@@ -3446,7 +3456,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>130</v>
       </c>
@@ -3458,7 +3468,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>132</v>
       </c>
@@ -3470,7 +3480,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>134</v>
       </c>
@@ -3491,11 +3501,11 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -3507,7 +3517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3521,7 +3531,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3535,7 +3545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -3549,7 +3559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -3561,7 +3571,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -3582,9 +3592,9 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3598,7 +3608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3612,7 +3622,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3626,7 +3636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -3640,7 +3650,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>138</v>
       </c>
@@ -3652,7 +3662,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -3664,7 +3674,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3686,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>105</v>
       </c>
@@ -3690,7 +3700,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -3702,7 +3712,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -3722,10 +3732,10 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3739,7 +3749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3753,7 +3763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3767,7 +3777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>140</v>
       </c>
@@ -3779,7 +3789,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -3791,7 +3801,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -3805,7 +3815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -3817,7 +3827,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>142</v>
       </c>
@@ -3829,7 +3839,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>144</v>
       </c>
@@ -3843,7 +3853,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>147</v>
       </c>
@@ -3853,57 +3863,69 @@
       <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3914,9 +3936,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3930,7 +3952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3944,7 +3966,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -3958,7 +3980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>142</v>
       </c>
@@ -3970,96 +3992,96 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
@@ -4075,9 +4097,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4091,35 +4113,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4133,7 +4155,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -4145,7 +4167,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>110</v>
       </c>
@@ -4157,7 +4179,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -4178,9 +4200,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4194,7 +4216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -4208,7 +4230,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -4222,7 +4244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -4236,7 +4258,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -4248,7 +4270,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
@@ -4269,9 +4291,9 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4285,35 +4307,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4327,7 +4349,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>142</v>
       </c>
@@ -4339,7 +4361,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -4353,7 +4375,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4365,7 +4387,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -4377,7 +4399,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -4398,9 +4420,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4414,35 +4436,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4456,19 +4478,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -4482,7 +4504,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4494,7 +4516,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -4506,7 +4528,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -4527,9 +4549,9 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4543,7 +4565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -4555,7 +4577,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -4567,7 +4589,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4581,7 +4603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -4593,7 +4615,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -4607,7 +4629,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -4619,7 +4641,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -4633,7 +4655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>103</v>
       </c>
@@ -4645,7 +4667,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>105</v>
       </c>
@@ -4659,7 +4681,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -4671,7 +4693,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>108</v>
       </c>
@@ -4683,7 +4705,7 @@
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>110</v>
       </c>
@@ -4695,7 +4717,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
@@ -4707,7 +4729,7 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>112</v>
       </c>
@@ -4719,7 +4741,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -4731,7 +4753,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>116</v>
       </c>
@@ -4743,7 +4765,7 @@
       </c>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>118</v>
       </c>
@@ -4755,7 +4777,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>120</v>
       </c>
@@ -4776,9 +4798,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4792,7 +4814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -4804,7 +4826,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -4818,7 +4840,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>122</v>
       </c>
@@ -4830,7 +4852,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>124</v>
       </c>
@@ -4842,7 +4864,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="41" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>126</v>
       </c>
@@ -4854,7 +4876,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>128</v>
       </c>
@@ -4866,7 +4888,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>130</v>
       </c>
@@ -4878,7 +4900,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>132</v>
       </c>
@@ -4890,7 +4912,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>134</v>
       </c>
@@ -4911,9 +4933,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4927,7 +4949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -4939,7 +4961,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -4953,7 +4975,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -4967,7 +4989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -4979,7 +5001,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -5000,9 +5022,9 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5016,7 +5038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -5028,7 +5050,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5042,7 +5064,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -5056,7 +5078,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>138</v>
       </c>
@@ -5067,10 +5089,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>26</v>
       </c>
@@ -5082,7 +5104,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>103</v>
       </c>
@@ -5094,7 +5116,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>105</v>
       </c>
@@ -5108,7 +5130,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -5120,7 +5142,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>110</v>
       </c>
@@ -5132,7 +5154,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -5152,10 +5174,10 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5169,7 +5191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -5181,7 +5203,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5195,7 +5217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>140</v>
       </c>
@@ -5207,7 +5229,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -5219,7 +5241,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -5233,7 +5255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -5245,7 +5267,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>142</v>
       </c>
@@ -5257,7 +5279,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>144</v>
       </c>
@@ -5271,7 +5293,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>147</v>
       </c>
@@ -5281,57 +5303,69 @@
       <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="58.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -5342,9 +5376,9 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5358,7 +5392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -5370,7 +5404,7 @@
       </c>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5384,7 +5418,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>142</v>
       </c>
@@ -5396,96 +5430,96 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
@@ -5501,9 +5535,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5517,35 +5551,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -5559,7 +5593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -5571,7 +5605,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>110</v>
       </c>
@@ -5583,7 +5617,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -5604,9 +5638,9 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5620,35 +5654,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -5662,7 +5696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>142</v>
       </c>
@@ -5674,7 +5708,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -5688,7 +5722,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -5700,7 +5734,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -5712,7 +5746,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -5733,9 +5767,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5749,7 +5783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -5763,7 +5797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5777,7 +5811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -5791,7 +5825,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -5812,9 +5846,9 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5828,35 +5862,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -5870,19 +5904,19 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>105</v>
       </c>
@@ -5896,7 +5930,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -5908,7 +5942,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -5920,7 +5954,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -5941,9 +5975,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5957,7 +5991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -5971,7 +6005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5985,7 +6019,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -5997,7 +6031,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -6018,9 +6052,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6034,7 +6068,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -6048,7 +6082,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -6062,7 +6096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -6076,7 +6110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -6088,7 +6122,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -6102,7 +6136,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -6114,7 +6148,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -6128,7 +6162,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
@@ -6149,9 +6183,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6165,7 +6199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -6179,7 +6213,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -6193,7 +6227,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -6207,7 +6241,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -6219,7 +6253,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
@@ -6240,9 +6274,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6256,7 +6290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -6270,7 +6304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -6284,7 +6318,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -6298,7 +6332,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>44</v>
       </c>
@@ -6319,9 +6353,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6335,7 +6369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>47</v>
       </c>
@@ -6349,7 +6383,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -6363,7 +6397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -6377,7 +6411,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>50</v>
       </c>

--- a/easy-widget-excel/中文.xlsx
+++ b/easy-widget-excel/中文.xlsx
@@ -173,10 +173,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>合并列单元格1</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>0.0</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -194,7 +192,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44215.763921481484</v>
+        <v>44217.5985556713</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>23.45</v>
@@ -220,7 +218,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855578704</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23.45</v>
@@ -246,7 +244,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855578704</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>23.45</v>
@@ -272,7 +270,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855578704</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>23.45</v>
@@ -298,7 +296,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855578704</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>23.45</v>
@@ -324,7 +322,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855578704</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>23.45</v>
@@ -350,7 +348,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>23.45</v>
@@ -376,7 +374,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>23.45</v>
@@ -402,7 +400,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>23.45</v>
@@ -428,7 +426,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>23.45</v>
@@ -454,7 +452,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>23.45</v>
@@ -480,7 +478,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>23.45</v>
@@ -506,7 +504,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>23.45</v>
@@ -532,7 +530,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>23.45</v>
@@ -558,7 +556,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>23.45</v>
@@ -584,7 +582,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>23.45</v>
@@ -610,7 +608,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855579861</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>23.45</v>
@@ -636,7 +634,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>23.45</v>
@@ -662,7 +660,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>23.45</v>
@@ -688,7 +686,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>23.45</v>
@@ -714,7 +712,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>23.45</v>
@@ -740,7 +738,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>23.45</v>
@@ -766,7 +764,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>23.45</v>
@@ -792,7 +790,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>23.45</v>
@@ -818,7 +816,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>23.45</v>
@@ -844,7 +842,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>23.45</v>
@@ -870,7 +868,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>23.45</v>
@@ -896,7 +894,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>23.45</v>
@@ -922,7 +920,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855581018</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>23.45</v>
@@ -948,7 +946,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>23.45</v>
@@ -974,7 +972,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>23.45</v>
@@ -1000,7 +998,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>23.45</v>
@@ -1026,7 +1024,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>23.45</v>
@@ -1052,7 +1050,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>23.45</v>
@@ -1078,7 +1076,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>44215.763921516205</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>23.45</v>
@@ -1104,7 +1102,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>23.45</v>
@@ -1130,7 +1128,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>23.45</v>
@@ -1156,7 +1154,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>23.45</v>
@@ -1182,7 +1180,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>23.45</v>
@@ -1208,7 +1206,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>23.45</v>
@@ -1234,7 +1232,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>23.45</v>
@@ -1260,7 +1258,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855582176</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>23.45</v>
@@ -1286,7 +1284,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>23.45</v>
@@ -1312,7 +1310,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>23.45</v>
@@ -1338,7 +1336,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>23.45</v>
@@ -1364,7 +1362,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>23.45</v>
@@ -1390,7 +1388,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>23.45</v>
@@ -1416,7 +1414,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>23.45</v>
@@ -1442,7 +1440,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>23.45</v>
@@ -1468,7 +1466,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>23.45</v>
@@ -1494,7 +1492,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>23.45</v>
@@ -1520,7 +1518,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>23.45</v>
@@ -1546,7 +1544,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>23.45</v>
@@ -1572,7 +1570,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.598555833334</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>23.45</v>
@@ -1598,7 +1596,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>23.45</v>
@@ -1624,7 +1622,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>23.45</v>
@@ -1650,7 +1648,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>23.45</v>
@@ -1676,7 +1674,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>23.45</v>
@@ -1702,7 +1700,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>23.45</v>
@@ -1728,7 +1726,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>23.45</v>
@@ -1754,7 +1752,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>23.45</v>
@@ -1780,7 +1778,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>23.45</v>
@@ -1806,7 +1804,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>23.45</v>
@@ -1832,7 +1830,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855584491</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>23.45</v>
@@ -1858,7 +1856,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>23.45</v>
@@ -1884,7 +1882,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>23.45</v>
@@ -1910,7 +1908,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>23.45</v>
@@ -1936,7 +1934,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>23.45</v>
@@ -1962,7 +1960,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>23.45</v>
@@ -1988,7 +1986,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>23.45</v>
@@ -2014,7 +2012,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>44215.76392152778</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>23.45</v>
@@ -2040,7 +2038,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>23.45</v>
@@ -2066,7 +2064,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>23.45</v>
@@ -2092,7 +2090,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>23.45</v>
@@ -2118,7 +2116,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>23.45</v>
@@ -2144,7 +2142,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>23.45</v>
@@ -2170,7 +2168,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855585648</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>23.45</v>
@@ -2196,7 +2194,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>23.45</v>
@@ -2222,7 +2220,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>23.45</v>
@@ -2248,7 +2246,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>23.45</v>
@@ -2274,7 +2272,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>23.45</v>
@@ -2300,7 +2298,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>23.45</v>
@@ -2326,7 +2324,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>23.45</v>
@@ -2352,7 +2350,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>23.45</v>
@@ -2378,7 +2376,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>23.45</v>
@@ -2404,7 +2402,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>23.45</v>
@@ -2430,7 +2428,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>23.45</v>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>23.45</v>
@@ -2482,7 +2480,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>23.45</v>
@@ -2508,7 +2506,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>23.45</v>
@@ -2534,7 +2532,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>23.45</v>
@@ -2560,7 +2558,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>23.45</v>
@@ -2586,7 +2584,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.598555868055</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>23.45</v>
@@ -2612,7 +2610,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>23.45</v>
@@ -2638,7 +2636,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>23.45</v>
@@ -2664,7 +2662,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>23.45</v>
@@ -2690,7 +2688,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>23.45</v>
@@ -2716,7 +2714,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>23.45</v>
@@ -2742,7 +2740,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>23.45</v>
@@ -2768,7 +2766,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>23.45</v>
@@ -2794,7 +2792,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>23.45</v>
@@ -2820,7 +2818,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>23.45</v>
@@ -2846,7 +2844,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855587963</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>23.45</v>
@@ -2872,7 +2870,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>23.45</v>
@@ -2898,7 +2896,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>23.45</v>
@@ -2924,7 +2922,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>44215.76392153935</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>23.45</v>
@@ -2950,7 +2948,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>23.45</v>
@@ -2976,7 +2974,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>23.45</v>
@@ -3002,7 +3000,7 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>23.45</v>
@@ -3028,7 +3026,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>23.45</v>
@@ -3054,7 +3052,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>23.45</v>
@@ -3080,7 +3078,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>23.45</v>
@@ -3106,7 +3104,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>23.45</v>
@@ -3132,7 +3130,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>23.45</v>
@@ -3158,7 +3156,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F117" s="2" t="n">
         <v>23.45</v>
@@ -3184,7 +3182,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>23.45</v>
@@ -3210,7 +3208,7 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>23.45</v>
@@ -3236,7 +3234,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855598379</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>23.45</v>
@@ -3262,7 +3260,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>23.45</v>
@@ -3288,7 +3286,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>23.45</v>
@@ -3314,7 +3312,7 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>23.45</v>
@@ -3340,7 +3338,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>23.45</v>
@@ -3366,7 +3364,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>23.45</v>
@@ -3392,7 +3390,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F126" s="2" t="n">
         <v>23.45</v>
@@ -3418,7 +3416,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F127" s="2" t="n">
         <v>23.45</v>
@@ -3444,7 +3442,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>23.45</v>
@@ -3470,7 +3468,7 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>23.45</v>
@@ -3496,7 +3494,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>23.45</v>
@@ -3522,7 +3520,7 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F131" s="2" t="n">
         <v>23.45</v>
@@ -3548,7 +3546,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>23.45</v>
@@ -3574,7 +3572,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>23.45</v>
@@ -3600,7 +3598,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>23.45</v>
@@ -3626,7 +3624,7 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>23.45</v>
@@ -3652,7 +3650,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>23.45</v>
@@ -3678,7 +3676,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>23.45</v>
@@ -3704,7 +3702,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>23.45</v>
@@ -3730,7 +3728,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F139" s="2" t="n">
         <v>23.45</v>
@@ -3756,7 +3754,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>44215.763921550926</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>23.45</v>
@@ -3782,7 +3780,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>23.45</v>
@@ -3808,7 +3806,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>23.45</v>
@@ -3834,7 +3832,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>23.45</v>
@@ -3860,7 +3858,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>23.45</v>
@@ -3886,7 +3884,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F145" s="2" t="n">
         <v>23.45</v>
@@ -3912,7 +3910,7 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F146" s="2" t="n">
         <v>23.45</v>
@@ -3938,7 +3936,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>23.45</v>
@@ -3964,7 +3962,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F148" s="2" t="n">
         <v>23.45</v>
@@ -3990,7 +3988,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>23.45</v>
@@ -4016,7 +4014,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.59855599537</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>23.45</v>
@@ -4042,7 +4040,7 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F151" s="2" t="n">
         <v>23.45</v>
@@ -4068,7 +4066,7 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F152" s="2" t="n">
         <v>23.45</v>
@@ -4094,7 +4092,7 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>23.45</v>
@@ -4120,7 +4118,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>23.45</v>
@@ -4146,7 +4144,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>23.45</v>
@@ -4172,7 +4170,7 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>23.45</v>
@@ -4198,7 +4196,7 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>23.45</v>
@@ -4224,7 +4222,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>23.45</v>
@@ -4250,7 +4248,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>23.45</v>
@@ -4276,7 +4274,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>23.45</v>
@@ -4302,7 +4300,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>23.45</v>
@@ -4328,7 +4326,7 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>23.45</v>
@@ -4354,7 +4352,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>23.45</v>
@@ -4380,7 +4378,7 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F164" s="2" t="n">
         <v>23.45</v>
@@ -4406,7 +4404,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>23.45</v>
@@ -4432,7 +4430,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>23.45</v>
@@ -4458,7 +4456,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F167" s="2" t="n">
         <v>23.45</v>
@@ -4484,7 +4482,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>23.45</v>
@@ -4510,7 +4508,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>23.45</v>
@@ -4536,7 +4534,7 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F170" s="2" t="n">
         <v>23.45</v>
@@ -4562,7 +4560,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>44215.7639215625</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>23.45</v>
@@ -4588,7 +4586,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F172" s="2" t="n">
         <v>23.45</v>
@@ -4614,7 +4612,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F173" s="2" t="n">
         <v>23.45</v>
@@ -4640,7 +4638,7 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F174" s="2" t="n">
         <v>23.45</v>
@@ -4666,7 +4664,7 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F175" s="2" t="n">
         <v>23.45</v>
@@ -4692,7 +4690,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>23.45</v>
@@ -4718,7 +4716,7 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>23.45</v>
@@ -4744,7 +4742,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>23.45</v>
@@ -4770,7 +4768,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F179" s="2" t="n">
         <v>23.45</v>
@@ -4796,7 +4794,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F180" s="2" t="n">
         <v>23.45</v>
@@ -4822,7 +4820,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F181" s="2" t="n">
         <v>23.45</v>
@@ -4848,7 +4846,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>23.45</v>
@@ -4874,7 +4872,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>23.45</v>
@@ -4900,7 +4898,7 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F184" s="2" t="n">
         <v>23.45</v>
@@ -4926,7 +4924,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.598556006946</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>23.45</v>
@@ -4952,7 +4950,7 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F186" s="2" t="n">
         <v>23.45</v>
@@ -4978,7 +4976,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>23.45</v>
@@ -5004,7 +5002,7 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>23.45</v>
@@ -5030,7 +5028,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>23.45</v>
@@ -5056,7 +5054,7 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F190" s="2" t="n">
         <v>23.45</v>
@@ -5082,7 +5080,7 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F191" s="2" t="n">
         <v>23.45</v>
@@ -5108,7 +5106,7 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F192" s="2" t="n">
         <v>23.45</v>
@@ -5134,7 +5132,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>23.45</v>
@@ -5160,7 +5158,7 @@
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F194" s="2" t="n">
         <v>23.45</v>
@@ -5186,7 +5184,7 @@
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F195" s="2" t="n">
         <v>23.45</v>
@@ -5212,7 +5210,7 @@
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F196" s="2" t="n">
         <v>23.45</v>
@@ -5238,7 +5236,7 @@
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F197" s="2" t="n">
         <v>23.45</v>
@@ -5264,7 +5262,7 @@
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F198" s="2" t="n">
         <v>23.45</v>
@@ -5290,7 +5288,7 @@
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F199" s="2" t="n">
         <v>23.45</v>
@@ -5316,7 +5314,7 @@
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>23.45</v>
@@ -5342,7 +5340,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>23.45</v>
@@ -5368,7 +5366,7 @@
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F202" s="2" t="n">
         <v>23.45</v>
@@ -5394,7 +5392,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>23.45</v>
@@ -5420,7 +5418,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>23.45</v>
@@ -5446,7 +5444,7 @@
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F205" s="2" t="n">
         <v>23.45</v>
@@ -5472,7 +5470,7 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F206" s="2" t="n">
         <v>23.45</v>
@@ -5498,7 +5496,7 @@
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>23.45</v>
@@ -5524,7 +5522,7 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>23.45</v>
@@ -5550,7 +5548,7 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>23.45</v>
@@ -5576,7 +5574,7 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>23.45</v>
@@ -5602,7 +5600,7 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>23.45</v>
@@ -5628,7 +5626,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>23.45</v>
@@ -5654,7 +5652,7 @@
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>23.45</v>
@@ -5680,7 +5678,7 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>23.45</v>
@@ -5706,7 +5704,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>23.45</v>
@@ -5732,7 +5730,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855601852</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>23.45</v>
@@ -5758,7 +5756,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>23.45</v>
@@ -5784,7 +5782,7 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>23.45</v>
@@ -5810,7 +5808,7 @@
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>23.45</v>
@@ -5836,7 +5834,7 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F220" s="2" t="n">
         <v>23.45</v>
@@ -5862,7 +5860,7 @@
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F221" s="2" t="n">
         <v>23.45</v>
@@ -5888,7 +5886,7 @@
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>23.45</v>
@@ -5914,7 +5912,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F223" s="2" t="n">
         <v>23.45</v>
@@ -5940,7 +5938,7 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>23.45</v>
@@ -5966,7 +5964,7 @@
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F225" s="2" t="n">
         <v>23.45</v>
@@ -5992,7 +5990,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>44215.76392157407</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>23.45</v>
@@ -6018,7 +6016,7 @@
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F227" s="2" t="n">
         <v>23.45</v>
@@ -6044,7 +6042,7 @@
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F228" s="2" t="n">
         <v>23.45</v>
@@ -6070,7 +6068,7 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F229" s="2" t="n">
         <v>23.45</v>
@@ -6096,7 +6094,7 @@
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F230" s="2" t="n">
         <v>23.45</v>
@@ -6122,7 +6120,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>23.45</v>
@@ -6148,7 +6146,7 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F232" s="2" t="n">
         <v>23.45</v>
@@ -6174,7 +6172,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>23.45</v>
@@ -6200,7 +6198,7 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F234" s="2" t="n">
         <v>23.45</v>
@@ -6226,7 +6224,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>23.45</v>
@@ -6252,7 +6250,7 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F236" s="2" t="n">
         <v>23.45</v>
@@ -6278,7 +6276,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>23.45</v>
@@ -6304,7 +6302,7 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F238" s="2" t="n">
         <v>23.45</v>
@@ -6330,7 +6328,7 @@
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F239" s="2" t="n">
         <v>23.45</v>
@@ -6356,7 +6354,7 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F240" s="2" t="n">
         <v>23.45</v>
@@ -6382,7 +6380,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>23.45</v>
@@ -6408,7 +6406,7 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F242" s="2" t="n">
         <v>23.45</v>
@@ -6434,7 +6432,7 @@
         </is>
       </c>
       <c r="E243" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855603009</v>
       </c>
       <c r="F243" s="2" t="n">
         <v>23.45</v>
@@ -6460,7 +6458,7 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F244" s="2" t="n">
         <v>23.45</v>
@@ -6486,7 +6484,7 @@
         </is>
       </c>
       <c r="E245" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F245" s="2" t="n">
         <v>23.45</v>
@@ -6512,7 +6510,7 @@
         </is>
       </c>
       <c r="E246" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F246" s="2" t="n">
         <v>23.45</v>
@@ -6538,7 +6536,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>23.45</v>
@@ -6564,7 +6562,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F248" s="2" t="n">
         <v>23.45</v>
@@ -6590,7 +6588,7 @@
         </is>
       </c>
       <c r="E249" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F249" s="2" t="n">
         <v>23.45</v>
@@ -6616,7 +6614,7 @@
         </is>
       </c>
       <c r="E250" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F250" s="2" t="n">
         <v>23.45</v>
@@ -6642,7 +6640,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>23.45</v>
@@ -6668,7 +6666,7 @@
         </is>
       </c>
       <c r="E252" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F252" s="2" t="n">
         <v>23.45</v>
@@ -6694,7 +6692,7 @@
         </is>
       </c>
       <c r="E253" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F253" s="2" t="n">
         <v>23.45</v>
@@ -6720,7 +6718,7 @@
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F254" s="2" t="n">
         <v>23.45</v>
@@ -6746,7 +6744,7 @@
         </is>
       </c>
       <c r="E255" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F255" s="2" t="n">
         <v>23.45</v>
@@ -6772,7 +6770,7 @@
         </is>
       </c>
       <c r="E256" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F256" s="2" t="n">
         <v>23.45</v>
@@ -6798,7 +6796,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855604167</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>23.45</v>
@@ -6824,7 +6822,7 @@
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F258" s="2" t="n">
         <v>23.45</v>
@@ -6850,7 +6848,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>23.45</v>
@@ -6876,7 +6874,7 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F260" s="2" t="n">
         <v>23.45</v>
@@ -6902,7 +6900,7 @@
         </is>
       </c>
       <c r="E261" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F261" s="2" t="n">
         <v>23.45</v>
@@ -6928,7 +6926,7 @@
         </is>
       </c>
       <c r="E262" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F262" s="2" t="n">
         <v>23.45</v>
@@ -6954,7 +6952,7 @@
         </is>
       </c>
       <c r="E263" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F263" s="2" t="n">
         <v>23.45</v>
@@ -6980,7 +6978,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>23.45</v>
@@ -7006,7 +7004,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F265" s="2" t="n">
         <v>23.45</v>
@@ -7032,7 +7030,7 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F266" s="2" t="n">
         <v>23.45</v>
@@ -7058,7 +7056,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>23.45</v>
@@ -7084,7 +7082,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F268" s="2" t="n">
         <v>23.45</v>
@@ -7110,7 +7108,7 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F269" s="2" t="n">
         <v>23.45</v>
@@ -7136,7 +7134,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>23.45</v>
@@ -7162,7 +7160,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>23.45</v>
@@ -7188,7 +7186,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F272" s="2" t="n">
         <v>23.45</v>
@@ -7214,7 +7212,7 @@
         </is>
       </c>
       <c r="E273" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F273" s="2" t="n">
         <v>23.45</v>
@@ -7240,7 +7238,7 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F274" s="2" t="n">
         <v>23.45</v>
@@ -7266,7 +7264,7 @@
         </is>
       </c>
       <c r="E275" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F275" s="2" t="n">
         <v>23.45</v>
@@ -7292,7 +7290,7 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F276" s="2" t="n">
         <v>23.45</v>
@@ -7318,7 +7316,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F277" s="2" t="n">
         <v>23.45</v>
@@ -7344,7 +7342,7 @@
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F278" s="2" t="n">
         <v>23.45</v>
@@ -7370,7 +7368,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F279" s="2" t="n">
         <v>23.45</v>
@@ -7396,7 +7394,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F280" s="2" t="n">
         <v>23.45</v>
@@ -7422,7 +7420,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F281" s="2" t="n">
         <v>23.45</v>
@@ -7448,7 +7446,7 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F282" s="2" t="n">
         <v>23.45</v>
@@ -7474,7 +7472,7 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F283" s="2" t="n">
         <v>23.45</v>
@@ -7500,7 +7498,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>23.45</v>
@@ -7526,7 +7524,7 @@
         </is>
       </c>
       <c r="E285" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F285" s="2" t="n">
         <v>23.45</v>
@@ -7552,7 +7550,7 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F286" s="2" t="n">
         <v>23.45</v>
@@ -7578,7 +7576,7 @@
         </is>
       </c>
       <c r="E287" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F287" s="2" t="n">
         <v>23.45</v>
@@ -7604,7 +7602,7 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F288" s="2" t="n">
         <v>23.45</v>
@@ -7630,7 +7628,7 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F289" s="2" t="n">
         <v>23.45</v>
@@ -7656,7 +7654,7 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F290" s="2" t="n">
         <v>23.45</v>
@@ -7682,7 +7680,7 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F291" s="2" t="n">
         <v>23.45</v>
@@ -7708,7 +7706,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F292" s="2" t="n">
         <v>23.45</v>
@@ -7734,7 +7732,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>44215.76392158565</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F293" s="2" t="n">
         <v>23.45</v>
@@ -7760,7 +7758,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F294" s="2" t="n">
         <v>23.45</v>
@@ -7786,7 +7784,7 @@
         </is>
       </c>
       <c r="E295" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F295" s="2" t="n">
         <v>23.45</v>
@@ -7812,7 +7810,7 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F296" s="2" t="n">
         <v>23.45</v>
@@ -7838,7 +7836,7 @@
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F297" s="2" t="n">
         <v>23.45</v>
@@ -7864,7 +7862,7 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.59855611111</v>
       </c>
       <c r="F298" s="2" t="n">
         <v>23.45</v>
@@ -7890,7 +7888,7 @@
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F299" s="2" t="n">
         <v>23.45</v>
@@ -7916,7 +7914,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F300" s="2" t="n">
         <v>23.45</v>
@@ -7942,7 +7940,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F301" s="2" t="n">
         <v>23.45</v>
@@ -7968,7 +7966,7 @@
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F302" s="2" t="n">
         <v>23.45</v>
@@ -7994,7 +7992,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F303" s="2" t="n">
         <v>23.45</v>
@@ -8020,7 +8018,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F304" s="2" t="n">
         <v>23.45</v>
@@ -8046,7 +8044,7 @@
         </is>
       </c>
       <c r="E305" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F305" s="2" t="n">
         <v>23.45</v>
@@ -8072,7 +8070,7 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F306" s="2" t="n">
         <v>23.45</v>
@@ -8098,7 +8096,7 @@
         </is>
       </c>
       <c r="E307" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F307" s="2" t="n">
         <v>23.45</v>
@@ -8124,7 +8122,7 @@
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F308" s="2" t="n">
         <v>23.45</v>
@@ -8150,7 +8148,7 @@
         </is>
       </c>
       <c r="E309" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F309" s="2" t="n">
         <v>23.45</v>
@@ -8176,7 +8174,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F310" s="2" t="n">
         <v>23.45</v>
@@ -8202,7 +8200,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F311" s="2" t="n">
         <v>23.45</v>
@@ -8228,7 +8226,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>23.45</v>
@@ -8254,7 +8252,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F313" s="2" t="n">
         <v>23.45</v>
@@ -8280,7 +8278,7 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F314" s="2" t="n">
         <v>23.45</v>
@@ -8306,7 +8304,7 @@
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F315" s="2" t="n">
         <v>23.45</v>
@@ -8332,7 +8330,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>23.45</v>
@@ -8358,7 +8356,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F317" s="2" t="n">
         <v>23.45</v>
@@ -8384,7 +8382,7 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F318" s="2" t="n">
         <v>23.45</v>
@@ -8410,7 +8408,7 @@
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F319" s="2" t="n">
         <v>23.45</v>
@@ -8436,7 +8434,7 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F320" s="2" t="n">
         <v>23.45</v>
@@ -8462,7 +8460,7 @@
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F321" s="2" t="n">
         <v>23.45</v>
@@ -8488,7 +8486,7 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F322" s="2" t="n">
         <v>23.45</v>
@@ -8514,7 +8512,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>23.45</v>
@@ -8540,7 +8538,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>23.45</v>
@@ -8566,7 +8564,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>23.45</v>
@@ -8592,7 +8590,7 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F326" s="2" t="n">
         <v>23.45</v>
@@ -8618,7 +8616,7 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F327" s="2" t="n">
         <v>23.45</v>
@@ -8644,7 +8642,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>23.45</v>
@@ -8670,7 +8668,7 @@
         </is>
       </c>
       <c r="E329" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F329" s="2" t="n">
         <v>23.45</v>
@@ -8696,7 +8694,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>23.45</v>
@@ -8722,7 +8720,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>23.45</v>
@@ -8748,7 +8746,7 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F332" s="2" t="n">
         <v>23.45</v>
@@ -8774,7 +8772,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>23.45</v>
@@ -8800,7 +8798,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>23.45</v>
@@ -8826,7 +8824,7 @@
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F335" s="2" t="n">
         <v>23.45</v>
@@ -8852,7 +8850,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F336" s="2" t="n">
         <v>23.45</v>
@@ -8878,7 +8876,7 @@
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F337" s="2" t="n">
         <v>23.45</v>
@@ -8904,7 +8902,7 @@
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F338" s="2" t="n">
         <v>23.45</v>
@@ -8930,7 +8928,7 @@
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F339" s="2" t="n">
         <v>23.45</v>
@@ -8956,7 +8954,7 @@
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F340" s="2" t="n">
         <v>23.45</v>
@@ -8982,7 +8980,7 @@
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F341" s="2" t="n">
         <v>23.45</v>
@@ -9008,7 +9006,7 @@
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F342" s="2" t="n">
         <v>23.45</v>
@@ -9034,7 +9032,7 @@
         </is>
       </c>
       <c r="E343" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F343" s="2" t="n">
         <v>23.45</v>
@@ -9060,7 +9058,7 @@
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F344" s="2" t="n">
         <v>23.45</v>
@@ -9086,7 +9084,7 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F345" s="2" t="n">
         <v>23.45</v>
@@ -9112,7 +9110,7 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F346" s="2" t="n">
         <v>23.45</v>
@@ -9138,7 +9136,7 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F347" s="2" t="n">
         <v>23.45</v>
@@ -9164,7 +9162,7 @@
         </is>
       </c>
       <c r="E348" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F348" s="2" t="n">
         <v>23.45</v>
@@ -9190,7 +9188,7 @@
         </is>
       </c>
       <c r="E349" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F349" s="2" t="n">
         <v>23.45</v>
@@ -9216,7 +9214,7 @@
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F350" s="2" t="n">
         <v>23.45</v>
@@ -9242,7 +9240,7 @@
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F351" s="2" t="n">
         <v>23.45</v>
@@ -9268,7 +9266,7 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F352" s="2" t="n">
         <v>23.45</v>
@@ -9294,7 +9292,7 @@
         </is>
       </c>
       <c r="E353" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F353" s="2" t="n">
         <v>23.45</v>
@@ -9320,7 +9318,7 @@
         </is>
       </c>
       <c r="E354" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F354" s="2" t="n">
         <v>23.45</v>
@@ -9346,7 +9344,7 @@
         </is>
       </c>
       <c r="E355" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F355" s="2" t="n">
         <v>23.45</v>
@@ -9372,7 +9370,7 @@
         </is>
       </c>
       <c r="E356" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F356" s="2" t="n">
         <v>23.45</v>
@@ -9398,7 +9396,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F357" s="2" t="n">
         <v>23.45</v>
@@ -9424,7 +9422,7 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F358" s="2" t="n">
         <v>23.45</v>
@@ -9450,7 +9448,7 @@
         </is>
       </c>
       <c r="E359" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F359" s="2" t="n">
         <v>23.45</v>
@@ -9476,7 +9474,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.598556122684</v>
       </c>
       <c r="F360" s="2" t="n">
         <v>23.45</v>
@@ -9502,7 +9500,7 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>44215.76392159722</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F361" s="2" t="n">
         <v>23.45</v>
@@ -9528,7 +9526,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>44215.763921631944</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F362" s="2" t="n">
         <v>23.45</v>
@@ -9554,7 +9552,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F363" s="2" t="n">
         <v>23.45</v>
@@ -9580,7 +9578,7 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F364" s="2" t="n">
         <v>23.45</v>
@@ -9606,7 +9604,7 @@
         </is>
       </c>
       <c r="E365" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F365" s="2" t="n">
         <v>23.45</v>
@@ -9632,7 +9630,7 @@
         </is>
       </c>
       <c r="E366" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F366" s="2" t="n">
         <v>23.45</v>
@@ -9658,7 +9656,7 @@
         </is>
       </c>
       <c r="E367" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F367" s="2" t="n">
         <v>23.45</v>
@@ -9684,7 +9682,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F368" s="2" t="n">
         <v>23.45</v>
@@ -9710,7 +9708,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F369" s="2" t="n">
         <v>23.45</v>
@@ -9736,7 +9734,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F370" s="2" t="n">
         <v>23.45</v>
@@ -9762,7 +9760,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F371" s="2" t="n">
         <v>23.45</v>
@@ -9788,7 +9786,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F372" s="2" t="n">
         <v>23.45</v>
@@ -9814,7 +9812,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F373" s="2" t="n">
         <v>23.45</v>
@@ -9840,7 +9838,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F374" s="2" t="n">
         <v>23.45</v>
@@ -9866,7 +9864,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F375" s="2" t="n">
         <v>23.45</v>
@@ -9892,7 +9890,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F376" s="2" t="n">
         <v>23.45</v>
@@ -9918,7 +9916,7 @@
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F377" s="2" t="n">
         <v>23.45</v>
@@ -9944,7 +9942,7 @@
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F378" s="2" t="n">
         <v>23.45</v>
@@ -9970,7 +9968,7 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F379" s="2" t="n">
         <v>23.45</v>
@@ -9996,7 +9994,7 @@
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F380" s="2" t="n">
         <v>23.45</v>
@@ -10022,7 +10020,7 @@
         </is>
       </c>
       <c r="E381" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F381" s="2" t="n">
         <v>23.45</v>
@@ -10048,7 +10046,7 @@
         </is>
       </c>
       <c r="E382" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F382" s="2" t="n">
         <v>23.45</v>
@@ -10074,7 +10072,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F383" s="2" t="n">
         <v>23.45</v>
@@ -10100,7 +10098,7 @@
         </is>
       </c>
       <c r="E384" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F384" s="2" t="n">
         <v>23.45</v>
@@ -10126,7 +10124,7 @@
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>44215.76392164352</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F385" s="2" t="n">
         <v>23.45</v>
@@ -10152,7 +10150,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F386" s="2" t="n">
         <v>23.45</v>
@@ -10178,7 +10176,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F387" s="2" t="n">
         <v>23.45</v>
@@ -10204,7 +10202,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F388" s="2" t="n">
         <v>23.45</v>
@@ -10230,7 +10228,7 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F389" s="2" t="n">
         <v>23.45</v>
@@ -10256,7 +10254,7 @@
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F390" s="2" t="n">
         <v>23.45</v>
@@ -10282,7 +10280,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F391" s="2" t="n">
         <v>23.45</v>
@@ -10308,7 +10306,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F392" s="2" t="n">
         <v>23.45</v>
@@ -10334,7 +10332,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F393" s="2" t="n">
         <v>23.45</v>
@@ -10360,7 +10358,7 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F394" s="2" t="n">
         <v>23.45</v>
@@ -10386,7 +10384,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F395" s="2" t="n">
         <v>23.45</v>
@@ -10412,7 +10410,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F396" s="2" t="n">
         <v>23.45</v>
@@ -10438,7 +10436,7 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F397" s="2" t="n">
         <v>23.45</v>
@@ -10464,7 +10462,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F398" s="2" t="n">
         <v>23.45</v>
@@ -10490,7 +10488,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F399" s="2" t="n">
         <v>23.45</v>
@@ -10516,7 +10514,7 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F400" s="2" t="n">
         <v>23.45</v>
@@ -10542,7 +10540,7 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F401" s="2" t="n">
         <v>23.45</v>
@@ -10568,7 +10566,7 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F402" s="2" t="n">
         <v>23.45</v>
@@ -10594,7 +10592,7 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F403" s="2" t="n">
         <v>23.45</v>
@@ -10620,7 +10618,7 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F404" s="2" t="n">
         <v>23.45</v>
@@ -10646,7 +10644,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F405" s="2" t="n">
         <v>23.45</v>
@@ -10672,7 +10670,7 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F406" s="2" t="n">
         <v>23.45</v>
@@ -10698,7 +10696,7 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F407" s="2" t="n">
         <v>23.45</v>
@@ -10724,7 +10722,7 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F408" s="2" t="n">
         <v>23.45</v>
@@ -10750,7 +10748,7 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F409" s="2" t="n">
         <v>23.45</v>
@@ -10776,7 +10774,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F410" s="2" t="n">
         <v>23.45</v>
@@ -10802,7 +10800,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F411" s="2" t="n">
         <v>23.45</v>
@@ -10828,7 +10826,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F412" s="2" t="n">
         <v>23.45</v>
@@ -10854,7 +10852,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F413" s="2" t="n">
         <v>23.45</v>
@@ -10880,7 +10878,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F414" s="2" t="n">
         <v>23.45</v>
@@ -10906,7 +10904,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F415" s="2" t="n">
         <v>23.45</v>
@@ -10932,7 +10930,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F416" s="2" t="n">
         <v>23.45</v>
@@ -10958,7 +10956,7 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F417" s="2" t="n">
         <v>23.45</v>
@@ -10984,7 +10982,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F418" s="2" t="n">
         <v>23.45</v>
@@ -11010,7 +11008,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F419" s="2" t="n">
         <v>23.45</v>
@@ -11036,7 +11034,7 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F420" s="2" t="n">
         <v>23.45</v>
@@ -11062,7 +11060,7 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855613426</v>
       </c>
       <c r="F421" s="2" t="n">
         <v>23.45</v>
@@ -11088,7 +11086,7 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F422" s="2" t="n">
         <v>23.45</v>
@@ -11114,7 +11112,7 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F423" s="2" t="n">
         <v>23.45</v>
@@ -11140,7 +11138,7 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F424" s="2" t="n">
         <v>23.45</v>
@@ -11166,7 +11164,7 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F425" s="2" t="n">
         <v>23.45</v>
@@ -11192,7 +11190,7 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F426" s="2" t="n">
         <v>23.45</v>
@@ -11218,7 +11216,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F427" s="2" t="n">
         <v>23.45</v>
@@ -11244,7 +11242,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F428" s="2" t="n">
         <v>23.45</v>
@@ -11270,7 +11268,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F429" s="2" t="n">
         <v>23.45</v>
@@ -11296,7 +11294,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F430" s="2" t="n">
         <v>23.45</v>
@@ -11322,7 +11320,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F431" s="2" t="n">
         <v>23.45</v>
@@ -11348,7 +11346,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>23.45</v>
@@ -11374,7 +11372,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F433" s="2" t="n">
         <v>23.45</v>
@@ -11400,7 +11398,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F434" s="2" t="n">
         <v>23.45</v>
@@ -11426,7 +11424,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F435" s="2" t="n">
         <v>23.45</v>
@@ -11452,7 +11450,7 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F436" s="2" t="n">
         <v>23.45</v>
@@ -11478,7 +11476,7 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F437" s="2" t="n">
         <v>23.45</v>
@@ -11504,7 +11502,7 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F438" s="2" t="n">
         <v>23.45</v>
@@ -11530,7 +11528,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F439" s="2" t="n">
         <v>23.45</v>
@@ -11556,7 +11554,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F440" s="2" t="n">
         <v>23.45</v>
@@ -11582,7 +11580,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F441" s="2" t="n">
         <v>23.45</v>
@@ -11608,7 +11606,7 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F442" s="2" t="n">
         <v>23.45</v>
@@ -11634,7 +11632,7 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F443" s="2" t="n">
         <v>23.45</v>
@@ -11660,7 +11658,7 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F444" s="2" t="n">
         <v>23.45</v>
@@ -11686,7 +11684,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F445" s="2" t="n">
         <v>23.45</v>
@@ -11712,7 +11710,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F446" s="2" t="n">
         <v>23.45</v>
@@ -11738,7 +11736,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F447" s="2" t="n">
         <v>23.45</v>
@@ -11764,7 +11762,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.59855614584</v>
       </c>
       <c r="F448" s="2" t="n">
         <v>23.45</v>
@@ -11790,7 +11788,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F449" s="2" t="n">
         <v>23.45</v>
@@ -11816,7 +11814,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F450" s="2" t="n">
         <v>23.45</v>
@@ -11842,7 +11840,7 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F451" s="2" t="n">
         <v>23.45</v>
@@ -11868,7 +11866,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F452" s="2" t="n">
         <v>23.45</v>
@@ -11894,7 +11892,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F453" s="2" t="n">
         <v>23.45</v>
@@ -11920,7 +11918,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F454" s="2" t="n">
         <v>23.45</v>
@@ -11946,7 +11944,7 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F455" s="2" t="n">
         <v>23.45</v>
@@ -11972,7 +11970,7 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F456" s="2" t="n">
         <v>23.45</v>
@@ -11998,7 +11996,7 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F457" s="2" t="n">
         <v>23.45</v>
@@ -12024,7 +12022,7 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F458" s="2" t="n">
         <v>23.45</v>
@@ -12050,7 +12048,7 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F459" s="2" t="n">
         <v>23.45</v>
@@ -12076,7 +12074,7 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F460" s="2" t="n">
         <v>23.45</v>
@@ -12102,7 +12100,7 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F461" s="2" t="n">
         <v>23.45</v>
@@ -12128,7 +12126,7 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F462" s="2" t="n">
         <v>23.45</v>
@@ -12154,7 +12152,7 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>44215.76392167824</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F463" s="2" t="n">
         <v>23.45</v>
@@ -12180,7 +12178,7 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F464" s="2" t="n">
         <v>23.45</v>
@@ -12206,7 +12204,7 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F465" s="2" t="n">
         <v>23.45</v>
@@ -12232,7 +12230,7 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F466" s="2" t="n">
         <v>23.45</v>
@@ -12258,7 +12256,7 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F467" s="2" t="n">
         <v>23.45</v>
@@ -12284,7 +12282,7 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F468" s="2" t="n">
         <v>23.45</v>
@@ -12310,7 +12308,7 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F469" s="2" t="n">
         <v>23.45</v>
@@ -12336,7 +12334,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F470" s="2" t="n">
         <v>23.45</v>
@@ -12362,7 +12360,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>23.45</v>
@@ -12388,7 +12386,7 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F472" s="2" t="n">
         <v>23.45</v>
@@ -12414,7 +12412,7 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F473" s="2" t="n">
         <v>23.45</v>
@@ -12440,7 +12438,7 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F474" s="2" t="n">
         <v>23.45</v>
@@ -12466,7 +12464,7 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F475" s="2" t="n">
         <v>23.45</v>
@@ -12492,7 +12490,7 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F476" s="2" t="n">
         <v>23.45</v>
@@ -12518,7 +12516,7 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F477" s="2" t="n">
         <v>23.45</v>
@@ -12544,7 +12542,7 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F478" s="2" t="n">
         <v>23.45</v>
@@ -12570,7 +12568,7 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F479" s="2" t="n">
         <v>23.45</v>
@@ -12596,7 +12594,7 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F480" s="2" t="n">
         <v>23.45</v>
@@ -12622,7 +12620,7 @@
         </is>
       </c>
       <c r="E481" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F481" s="2" t="n">
         <v>23.45</v>
@@ -12648,7 +12646,7 @@
         </is>
       </c>
       <c r="E482" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F482" s="2" t="n">
         <v>23.45</v>
@@ -12674,7 +12672,7 @@
         </is>
       </c>
       <c r="E483" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F483" s="2" t="n">
         <v>23.45</v>
@@ -12700,7 +12698,7 @@
         </is>
       </c>
       <c r="E484" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F484" s="2" t="n">
         <v>23.45</v>
@@ -12726,7 +12724,7 @@
         </is>
       </c>
       <c r="E485" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F485" s="2" t="n">
         <v>23.45</v>
@@ -12752,7 +12750,7 @@
         </is>
       </c>
       <c r="E486" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F486" s="2" t="n">
         <v>23.45</v>
@@ -12778,7 +12776,7 @@
         </is>
       </c>
       <c r="E487" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F487" s="2" t="n">
         <v>23.45</v>
@@ -12804,7 +12802,7 @@
         </is>
       </c>
       <c r="E488" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F488" s="2" t="n">
         <v>23.45</v>
@@ -12830,7 +12828,7 @@
         </is>
       </c>
       <c r="E489" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F489" s="2" t="n">
         <v>23.45</v>
@@ -12856,7 +12854,7 @@
         </is>
       </c>
       <c r="E490" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F490" s="2" t="n">
         <v>23.45</v>
@@ -12882,7 +12880,7 @@
         </is>
       </c>
       <c r="E491" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F491" s="2" t="n">
         <v>23.45</v>
@@ -12908,7 +12906,7 @@
         </is>
       </c>
       <c r="E492" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F492" s="2" t="n">
         <v>23.45</v>
@@ -12934,7 +12932,7 @@
         </is>
       </c>
       <c r="E493" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.598556157405</v>
       </c>
       <c r="F493" s="2" t="n">
         <v>23.45</v>
@@ -12960,7 +12958,7 @@
         </is>
       </c>
       <c r="E494" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F494" s="2" t="n">
         <v>23.45</v>
@@ -12986,7 +12984,7 @@
         </is>
       </c>
       <c r="E495" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F495" s="2" t="n">
         <v>23.45</v>
@@ -13012,7 +13010,7 @@
         </is>
       </c>
       <c r="E496" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F496" s="2" t="n">
         <v>23.45</v>
@@ -13038,7 +13036,7 @@
         </is>
       </c>
       <c r="E497" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F497" s="2" t="n">
         <v>23.45</v>
@@ -13064,7 +13062,7 @@
         </is>
       </c>
       <c r="E498" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F498" s="2" t="n">
         <v>23.45</v>
@@ -13090,7 +13088,7 @@
         </is>
       </c>
       <c r="E499" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F499" s="2" t="n">
         <v>23.45</v>
@@ -13116,7 +13114,7 @@
         </is>
       </c>
       <c r="E500" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F500" s="2" t="n">
         <v>23.45</v>
@@ -13142,7 +13140,7 @@
         </is>
       </c>
       <c r="E501" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F501" s="2" t="n">
         <v>23.45</v>
@@ -13168,7 +13166,7 @@
         </is>
       </c>
       <c r="E502" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F502" s="2" t="n">
         <v>23.45</v>
@@ -13194,7 +13192,7 @@
         </is>
       </c>
       <c r="E503" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F503" s="2" t="n">
         <v>23.45</v>
@@ -13220,7 +13218,7 @@
         </is>
       </c>
       <c r="E504" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F504" s="2" t="n">
         <v>23.45</v>
@@ -13246,7 +13244,7 @@
         </is>
       </c>
       <c r="E505" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F505" s="2" t="n">
         <v>23.45</v>
@@ -13272,7 +13270,7 @@
         </is>
       </c>
       <c r="E506" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F506" s="2" t="n">
         <v>23.45</v>
@@ -13298,7 +13296,7 @@
         </is>
       </c>
       <c r="E507" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F507" s="2" t="n">
         <v>23.45</v>
@@ -13324,7 +13322,7 @@
         </is>
       </c>
       <c r="E508" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F508" s="2" t="n">
         <v>23.45</v>
@@ -13350,7 +13348,7 @@
         </is>
       </c>
       <c r="E509" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F509" s="2" t="n">
         <v>23.45</v>
@@ -13376,7 +13374,7 @@
         </is>
       </c>
       <c r="E510" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F510" s="2" t="n">
         <v>23.45</v>
@@ -13402,7 +13400,7 @@
         </is>
       </c>
       <c r="E511" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F511" s="2" t="n">
         <v>23.45</v>
@@ -13428,7 +13426,7 @@
         </is>
       </c>
       <c r="E512" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F512" s="2" t="n">
         <v>23.45</v>
@@ -13454,7 +13452,7 @@
         </is>
       </c>
       <c r="E513" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F513" s="2" t="n">
         <v>23.45</v>
@@ -13480,7 +13478,7 @@
         </is>
       </c>
       <c r="E514" s="2" t="n">
-        <v>44215.76392168982</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F514" s="2" t="n">
         <v>23.45</v>
@@ -13506,7 +13504,7 @@
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F515" s="2" t="n">
         <v>23.45</v>
@@ -13532,7 +13530,7 @@
         </is>
       </c>
       <c r="E516" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855616898</v>
       </c>
       <c r="F516" s="2" t="n">
         <v>23.45</v>
@@ -13558,7 +13556,7 @@
         </is>
       </c>
       <c r="E517" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855618056</v>
       </c>
       <c r="F517" s="2" t="n">
         <v>23.45</v>
@@ -13584,7 +13582,7 @@
         </is>
       </c>
       <c r="E518" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F518" s="2" t="n">
         <v>23.45</v>
@@ -13610,7 +13608,7 @@
         </is>
       </c>
       <c r="E519" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F519" s="2" t="n">
         <v>23.45</v>
@@ -13636,7 +13634,7 @@
         </is>
       </c>
       <c r="E520" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F520" s="2" t="n">
         <v>23.45</v>
@@ -13662,7 +13660,7 @@
         </is>
       </c>
       <c r="E521" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F521" s="2" t="n">
         <v>23.45</v>
@@ -13688,7 +13686,7 @@
         </is>
       </c>
       <c r="E522" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F522" s="2" t="n">
         <v>23.45</v>
@@ -13714,7 +13712,7 @@
         </is>
       </c>
       <c r="E523" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F523" s="2" t="n">
         <v>23.45</v>
@@ -13740,7 +13738,7 @@
         </is>
       </c>
       <c r="E524" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F524" s="2" t="n">
         <v>23.45</v>
@@ -13766,7 +13764,7 @@
         </is>
       </c>
       <c r="E525" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F525" s="2" t="n">
         <v>23.45</v>
@@ -13792,7 +13790,7 @@
         </is>
       </c>
       <c r="E526" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F526" s="2" t="n">
         <v>23.45</v>
@@ -13818,7 +13816,7 @@
         </is>
       </c>
       <c r="E527" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F527" s="2" t="n">
         <v>23.45</v>
@@ -13844,7 +13842,7 @@
         </is>
       </c>
       <c r="E528" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F528" s="2" t="n">
         <v>23.45</v>
@@ -13870,7 +13868,7 @@
         </is>
       </c>
       <c r="E529" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F529" s="2" t="n">
         <v>23.45</v>
@@ -13896,7 +13894,7 @@
         </is>
       </c>
       <c r="E530" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F530" s="2" t="n">
         <v>23.45</v>
@@ -13922,7 +13920,7 @@
         </is>
       </c>
       <c r="E531" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F531" s="2" t="n">
         <v>23.45</v>
@@ -13948,7 +13946,7 @@
         </is>
       </c>
       <c r="E532" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F532" s="2" t="n">
         <v>23.45</v>
@@ -13974,7 +13972,7 @@
         </is>
       </c>
       <c r="E533" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F533" s="2" t="n">
         <v>23.45</v>
@@ -14000,7 +13998,7 @@
         </is>
       </c>
       <c r="E534" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F534" s="2" t="n">
         <v>23.45</v>
@@ -14026,7 +14024,7 @@
         </is>
       </c>
       <c r="E535" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F535" s="2" t="n">
         <v>23.45</v>
@@ -14052,7 +14050,7 @@
         </is>
       </c>
       <c r="E536" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F536" s="2" t="n">
         <v>23.45</v>
@@ -14078,7 +14076,7 @@
         </is>
       </c>
       <c r="E537" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F537" s="2" t="n">
         <v>23.45</v>
@@ -14104,7 +14102,7 @@
         </is>
       </c>
       <c r="E538" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F538" s="2" t="n">
         <v>23.45</v>
@@ -14130,7 +14128,7 @@
         </is>
       </c>
       <c r="E539" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F539" s="2" t="n">
         <v>23.45</v>
@@ -14156,7 +14154,7 @@
         </is>
       </c>
       <c r="E540" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F540" s="2" t="n">
         <v>23.45</v>
@@ -14182,7 +14180,7 @@
         </is>
       </c>
       <c r="E541" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F541" s="2" t="n">
         <v>23.45</v>
@@ -14208,7 +14206,7 @@
         </is>
       </c>
       <c r="E542" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F542" s="2" t="n">
         <v>23.45</v>
@@ -14234,7 +14232,7 @@
         </is>
       </c>
       <c r="E543" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F543" s="2" t="n">
         <v>23.45</v>
@@ -14260,7 +14258,7 @@
         </is>
       </c>
       <c r="E544" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F544" s="2" t="n">
         <v>23.45</v>
@@ -14286,7 +14284,7 @@
         </is>
       </c>
       <c r="E545" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F545" s="2" t="n">
         <v>23.45</v>
@@ -14312,7 +14310,7 @@
         </is>
       </c>
       <c r="E546" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F546" s="2" t="n">
         <v>23.45</v>
@@ -14338,7 +14336,7 @@
         </is>
       </c>
       <c r="E547" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F547" s="2" t="n">
         <v>23.45</v>
@@ -14364,7 +14362,7 @@
         </is>
       </c>
       <c r="E548" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F548" s="2" t="n">
         <v>23.45</v>
@@ -14390,7 +14388,7 @@
         </is>
       </c>
       <c r="E549" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F549" s="2" t="n">
         <v>23.45</v>
@@ -14416,7 +14414,7 @@
         </is>
       </c>
       <c r="E550" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F550" s="2" t="n">
         <v>23.45</v>
@@ -14442,7 +14440,7 @@
         </is>
       </c>
       <c r="E551" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F551" s="2" t="n">
         <v>23.45</v>
@@ -14468,7 +14466,7 @@
         </is>
       </c>
       <c r="E552" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.5985562037</v>
       </c>
       <c r="F552" s="2" t="n">
         <v>23.45</v>
@@ -14494,7 +14492,7 @@
         </is>
       </c>
       <c r="E553" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F553" s="2" t="n">
         <v>23.45</v>
@@ -14520,7 +14518,7 @@
         </is>
       </c>
       <c r="E554" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F554" s="2" t="n">
         <v>23.45</v>
@@ -14546,7 +14544,7 @@
         </is>
       </c>
       <c r="E555" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F555" s="2" t="n">
         <v>23.45</v>
@@ -14572,7 +14570,7 @@
         </is>
       </c>
       <c r="E556" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F556" s="2" t="n">
         <v>23.45</v>
@@ -14598,7 +14596,7 @@
         </is>
       </c>
       <c r="E557" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F557" s="2" t="n">
         <v>23.45</v>
@@ -14624,7 +14622,7 @@
         </is>
       </c>
       <c r="E558" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F558" s="2" t="n">
         <v>23.45</v>
@@ -14650,7 +14648,7 @@
         </is>
       </c>
       <c r="E559" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F559" s="2" t="n">
         <v>23.45</v>
@@ -14676,7 +14674,7 @@
         </is>
       </c>
       <c r="E560" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F560" s="2" t="n">
         <v>23.45</v>
@@ -14702,7 +14700,7 @@
         </is>
       </c>
       <c r="E561" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F561" s="2" t="n">
         <v>23.45</v>
@@ -14728,7 +14726,7 @@
         </is>
       </c>
       <c r="E562" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F562" s="2" t="n">
         <v>23.45</v>
@@ -14754,7 +14752,7 @@
         </is>
       </c>
       <c r="E563" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F563" s="2" t="n">
         <v>23.45</v>
@@ -14780,7 +14778,7 @@
         </is>
       </c>
       <c r="E564" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F564" s="2" t="n">
         <v>23.45</v>
@@ -14806,7 +14804,7 @@
         </is>
       </c>
       <c r="E565" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F565" s="2" t="n">
         <v>23.45</v>
@@ -14832,7 +14830,7 @@
         </is>
       </c>
       <c r="E566" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F566" s="2" t="n">
         <v>23.45</v>
@@ -14858,7 +14856,7 @@
         </is>
       </c>
       <c r="E567" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F567" s="2" t="n">
         <v>23.45</v>
@@ -14884,7 +14882,7 @@
         </is>
       </c>
       <c r="E568" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F568" s="2" t="n">
         <v>23.45</v>
@@ -14910,7 +14908,7 @@
         </is>
       </c>
       <c r="E569" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F569" s="2" t="n">
         <v>23.45</v>
@@ -14936,7 +14934,7 @@
         </is>
       </c>
       <c r="E570" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F570" s="2" t="n">
         <v>23.45</v>
@@ -14962,7 +14960,7 @@
         </is>
       </c>
       <c r="E571" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F571" s="2" t="n">
         <v>23.45</v>
@@ -14988,7 +14986,7 @@
         </is>
       </c>
       <c r="E572" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F572" s="2" t="n">
         <v>23.45</v>
@@ -15014,7 +15012,7 @@
         </is>
       </c>
       <c r="E573" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F573" s="2" t="n">
         <v>23.45</v>
@@ -15040,7 +15038,7 @@
         </is>
       </c>
       <c r="E574" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F574" s="2" t="n">
         <v>23.45</v>
@@ -15066,7 +15064,7 @@
         </is>
       </c>
       <c r="E575" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F575" s="2" t="n">
         <v>23.45</v>
@@ -15092,7 +15090,7 @@
         </is>
       </c>
       <c r="E576" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F576" s="2" t="n">
         <v>23.45</v>
@@ -15118,7 +15116,7 @@
         </is>
       </c>
       <c r="E577" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F577" s="2" t="n">
         <v>23.45</v>
@@ -15144,7 +15142,7 @@
         </is>
       </c>
       <c r="E578" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F578" s="2" t="n">
         <v>23.45</v>
@@ -15170,7 +15168,7 @@
         </is>
       </c>
       <c r="E579" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F579" s="2" t="n">
         <v>23.45</v>
@@ -15196,7 +15194,7 @@
         </is>
       </c>
       <c r="E580" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F580" s="2" t="n">
         <v>23.45</v>
@@ -15222,7 +15220,7 @@
         </is>
       </c>
       <c r="E581" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F581" s="2" t="n">
         <v>23.45</v>
@@ -15248,7 +15246,7 @@
         </is>
       </c>
       <c r="E582" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F582" s="2" t="n">
         <v>23.45</v>
@@ -15274,7 +15272,7 @@
         </is>
       </c>
       <c r="E583" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F583" s="2" t="n">
         <v>23.45</v>
@@ -15300,7 +15298,7 @@
         </is>
       </c>
       <c r="E584" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F584" s="2" t="n">
         <v>23.45</v>
@@ -15326,7 +15324,7 @@
         </is>
       </c>
       <c r="E585" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F585" s="2" t="n">
         <v>23.45</v>
@@ -15352,7 +15350,7 @@
         </is>
       </c>
       <c r="E586" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F586" s="2" t="n">
         <v>23.45</v>
@@ -15378,7 +15376,7 @@
         </is>
       </c>
       <c r="E587" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F587" s="2" t="n">
         <v>23.45</v>
@@ -15404,7 +15402,7 @@
         </is>
       </c>
       <c r="E588" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F588" s="2" t="n">
         <v>23.45</v>
@@ -15430,7 +15428,7 @@
         </is>
       </c>
       <c r="E589" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F589" s="2" t="n">
         <v>23.45</v>
@@ -15456,7 +15454,7 @@
         </is>
       </c>
       <c r="E590" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F590" s="2" t="n">
         <v>23.45</v>
@@ -15482,7 +15480,7 @@
         </is>
       </c>
       <c r="E591" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F591" s="2" t="n">
         <v>23.45</v>
@@ -15508,7 +15506,7 @@
         </is>
       </c>
       <c r="E592" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F592" s="2" t="n">
         <v>23.45</v>
@@ -15534,7 +15532,7 @@
         </is>
       </c>
       <c r="E593" s="2" t="n">
-        <v>44215.763921701386</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F593" s="2" t="n">
         <v>23.45</v>
@@ -15560,7 +15558,7 @@
         </is>
       </c>
       <c r="E594" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F594" s="2" t="n">
         <v>23.45</v>
@@ -15586,7 +15584,7 @@
         </is>
       </c>
       <c r="E595" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F595" s="2" t="n">
         <v>23.45</v>
@@ -15612,7 +15610,7 @@
         </is>
       </c>
       <c r="E596" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F596" s="2" t="n">
         <v>23.45</v>
@@ -15638,7 +15636,7 @@
         </is>
       </c>
       <c r="E597" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F597" s="2" t="n">
         <v>23.45</v>
@@ -15664,7 +15662,7 @@
         </is>
       </c>
       <c r="E598" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F598" s="2" t="n">
         <v>23.45</v>
@@ -15690,7 +15688,7 @@
         </is>
       </c>
       <c r="E599" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F599" s="2" t="n">
         <v>23.45</v>
@@ -15716,7 +15714,7 @@
         </is>
       </c>
       <c r="E600" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F600" s="2" t="n">
         <v>23.45</v>
@@ -15742,7 +15740,7 @@
         </is>
       </c>
       <c r="E601" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F601" s="2" t="n">
         <v>23.45</v>
@@ -15768,7 +15766,7 @@
         </is>
       </c>
       <c r="E602" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F602" s="2" t="n">
         <v>23.45</v>
@@ -15794,7 +15792,7 @@
         </is>
       </c>
       <c r="E603" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F603" s="2" t="n">
         <v>23.45</v>
@@ -15820,7 +15818,7 @@
         </is>
       </c>
       <c r="E604" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F604" s="2" t="n">
         <v>23.45</v>
@@ -15846,7 +15844,7 @@
         </is>
       </c>
       <c r="E605" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F605" s="2" t="n">
         <v>23.45</v>
@@ -15872,7 +15870,7 @@
         </is>
       </c>
       <c r="E606" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F606" s="2" t="n">
         <v>23.45</v>
@@ -15898,7 +15896,7 @@
         </is>
       </c>
       <c r="E607" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F607" s="2" t="n">
         <v>23.45</v>
@@ -15924,7 +15922,7 @@
         </is>
       </c>
       <c r="E608" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F608" s="2" t="n">
         <v>23.45</v>
@@ -15950,7 +15948,7 @@
         </is>
       </c>
       <c r="E609" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855621528</v>
       </c>
       <c r="F609" s="2" t="n">
         <v>23.45</v>
@@ -15976,7 +15974,7 @@
         </is>
       </c>
       <c r="E610" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F610" s="2" t="n">
         <v>23.45</v>
@@ -16002,7 +16000,7 @@
         </is>
       </c>
       <c r="E611" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F611" s="2" t="n">
         <v>23.45</v>
@@ -16028,7 +16026,7 @@
         </is>
       </c>
       <c r="E612" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F612" s="2" t="n">
         <v>23.45</v>
@@ -16054,7 +16052,7 @@
         </is>
       </c>
       <c r="E613" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F613" s="2" t="n">
         <v>23.45</v>
@@ -16080,7 +16078,7 @@
         </is>
       </c>
       <c r="E614" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F614" s="2" t="n">
         <v>23.45</v>
@@ -16106,7 +16104,7 @@
         </is>
       </c>
       <c r="E615" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F615" s="2" t="n">
         <v>23.45</v>
@@ -16132,7 +16130,7 @@
         </is>
       </c>
       <c r="E616" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F616" s="2" t="n">
         <v>23.45</v>
@@ -16158,7 +16156,7 @@
         </is>
       </c>
       <c r="E617" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F617" s="2" t="n">
         <v>23.45</v>
@@ -16184,7 +16182,7 @@
         </is>
       </c>
       <c r="E618" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F618" s="2" t="n">
         <v>23.45</v>
@@ -16210,7 +16208,7 @@
         </is>
       </c>
       <c r="E619" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F619" s="2" t="n">
         <v>23.45</v>
@@ -16236,7 +16234,7 @@
         </is>
       </c>
       <c r="E620" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F620" s="2" t="n">
         <v>23.45</v>
@@ -16262,7 +16260,7 @@
         </is>
       </c>
       <c r="E621" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F621" s="2" t="n">
         <v>23.45</v>
@@ -16288,7 +16286,7 @@
         </is>
       </c>
       <c r="E622" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F622" s="2" t="n">
         <v>23.45</v>
@@ -16314,7 +16312,7 @@
         </is>
       </c>
       <c r="E623" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F623" s="2" t="n">
         <v>23.45</v>
@@ -16340,7 +16338,7 @@
         </is>
       </c>
       <c r="E624" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F624" s="2" t="n">
         <v>23.45</v>
@@ -16366,7 +16364,7 @@
         </is>
       </c>
       <c r="E625" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F625" s="2" t="n">
         <v>23.45</v>
@@ -16392,7 +16390,7 @@
         </is>
       </c>
       <c r="E626" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F626" s="2" t="n">
         <v>23.45</v>
@@ -16418,7 +16416,7 @@
         </is>
       </c>
       <c r="E627" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F627" s="2" t="n">
         <v>23.45</v>
@@ -16444,7 +16442,7 @@
         </is>
       </c>
       <c r="E628" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F628" s="2" t="n">
         <v>23.45</v>
@@ -16470,7 +16468,7 @@
         </is>
       </c>
       <c r="E629" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F629" s="2" t="n">
         <v>23.45</v>
@@ -16496,7 +16494,7 @@
         </is>
       </c>
       <c r="E630" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F630" s="2" t="n">
         <v>23.45</v>
@@ -16522,7 +16520,7 @@
         </is>
       </c>
       <c r="E631" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F631" s="2" t="n">
         <v>23.45</v>
@@ -16548,7 +16546,7 @@
         </is>
       </c>
       <c r="E632" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F632" s="2" t="n">
         <v>23.45</v>
@@ -16574,7 +16572,7 @@
         </is>
       </c>
       <c r="E633" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F633" s="2" t="n">
         <v>23.45</v>
@@ -16600,7 +16598,7 @@
         </is>
       </c>
       <c r="E634" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F634" s="2" t="n">
         <v>23.45</v>
@@ -16626,7 +16624,7 @@
         </is>
       </c>
       <c r="E635" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F635" s="2" t="n">
         <v>23.45</v>
@@ -16652,7 +16650,7 @@
         </is>
       </c>
       <c r="E636" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F636" s="2" t="n">
         <v>23.45</v>
@@ -16678,7 +16676,7 @@
         </is>
       </c>
       <c r="E637" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F637" s="2" t="n">
         <v>23.45</v>
@@ -16704,7 +16702,7 @@
         </is>
       </c>
       <c r="E638" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F638" s="2" t="n">
         <v>23.45</v>
@@ -16730,7 +16728,7 @@
         </is>
       </c>
       <c r="E639" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F639" s="2" t="n">
         <v>23.45</v>
@@ -16756,7 +16754,7 @@
         </is>
       </c>
       <c r="E640" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F640" s="2" t="n">
         <v>23.45</v>
@@ -16782,7 +16780,7 @@
         </is>
       </c>
       <c r="E641" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F641" s="2" t="n">
         <v>23.45</v>
@@ -16808,7 +16806,7 @@
         </is>
       </c>
       <c r="E642" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F642" s="2" t="n">
         <v>23.45</v>
@@ -16834,7 +16832,7 @@
         </is>
       </c>
       <c r="E643" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F643" s="2" t="n">
         <v>23.45</v>
@@ -16860,7 +16858,7 @@
         </is>
       </c>
       <c r="E644" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F644" s="2" t="n">
         <v>23.45</v>
@@ -16886,7 +16884,7 @@
         </is>
       </c>
       <c r="E645" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F645" s="2" t="n">
         <v>23.45</v>
@@ -16912,7 +16910,7 @@
         </is>
       </c>
       <c r="E646" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F646" s="2" t="n">
         <v>23.45</v>
@@ -16938,7 +16936,7 @@
         </is>
       </c>
       <c r="E647" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F647" s="2" t="n">
         <v>23.45</v>
@@ -16964,7 +16962,7 @@
         </is>
       </c>
       <c r="E648" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F648" s="2" t="n">
         <v>23.45</v>
@@ -16990,7 +16988,7 @@
         </is>
       </c>
       <c r="E649" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F649" s="2" t="n">
         <v>23.45</v>
@@ -17016,7 +17014,7 @@
         </is>
       </c>
       <c r="E650" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F650" s="2" t="n">
         <v>23.45</v>
@@ -17042,7 +17040,7 @@
         </is>
       </c>
       <c r="E651" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F651" s="2" t="n">
         <v>23.45</v>
@@ -17068,7 +17066,7 @@
         </is>
       </c>
       <c r="E652" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F652" s="2" t="n">
         <v>23.45</v>
@@ -17094,7 +17092,7 @@
         </is>
       </c>
       <c r="E653" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F653" s="2" t="n">
         <v>23.45</v>
@@ -17120,7 +17118,7 @@
         </is>
       </c>
       <c r="E654" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F654" s="2" t="n">
         <v>23.45</v>
@@ -17146,7 +17144,7 @@
         </is>
       </c>
       <c r="E655" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F655" s="2" t="n">
         <v>23.45</v>
@@ -17172,7 +17170,7 @@
         </is>
       </c>
       <c r="E656" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F656" s="2" t="n">
         <v>23.45</v>
@@ -17198,7 +17196,7 @@
         </is>
       </c>
       <c r="E657" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F657" s="2" t="n">
         <v>23.45</v>
@@ -17224,7 +17222,7 @@
         </is>
       </c>
       <c r="E658" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F658" s="2" t="n">
         <v>23.45</v>
@@ -17250,7 +17248,7 @@
         </is>
       </c>
       <c r="E659" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F659" s="2" t="n">
         <v>23.45</v>
@@ -17276,7 +17274,7 @@
         </is>
       </c>
       <c r="E660" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F660" s="2" t="n">
         <v>23.45</v>
@@ -17302,7 +17300,7 @@
         </is>
       </c>
       <c r="E661" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F661" s="2" t="n">
         <v>23.45</v>
@@ -17328,7 +17326,7 @@
         </is>
       </c>
       <c r="E662" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F662" s="2" t="n">
         <v>23.45</v>
@@ -17354,7 +17352,7 @@
         </is>
       </c>
       <c r="E663" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F663" s="2" t="n">
         <v>23.45</v>
@@ -17380,7 +17378,7 @@
         </is>
       </c>
       <c r="E664" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F664" s="2" t="n">
         <v>23.45</v>
@@ -17406,7 +17404,7 @@
         </is>
       </c>
       <c r="E665" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F665" s="2" t="n">
         <v>23.45</v>
@@ -17432,7 +17430,7 @@
         </is>
       </c>
       <c r="E666" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F666" s="2" t="n">
         <v>23.45</v>
@@ -17458,7 +17456,7 @@
         </is>
       </c>
       <c r="E667" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.598556226854</v>
       </c>
       <c r="F667" s="2" t="n">
         <v>23.45</v>
@@ -17484,7 +17482,7 @@
         </is>
       </c>
       <c r="E668" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F668" s="2" t="n">
         <v>23.45</v>
@@ -17510,7 +17508,7 @@
         </is>
       </c>
       <c r="E669" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F669" s="2" t="n">
         <v>23.45</v>
@@ -17536,7 +17534,7 @@
         </is>
       </c>
       <c r="E670" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F670" s="2" t="n">
         <v>23.45</v>
@@ -17562,7 +17560,7 @@
         </is>
       </c>
       <c r="E671" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F671" s="2" t="n">
         <v>23.45</v>
@@ -17588,7 +17586,7 @@
         </is>
       </c>
       <c r="E672" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F672" s="2" t="n">
         <v>23.45</v>
@@ -17614,7 +17612,7 @@
         </is>
       </c>
       <c r="E673" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F673" s="2" t="n">
         <v>23.45</v>
@@ -17640,7 +17638,7 @@
         </is>
       </c>
       <c r="E674" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F674" s="2" t="n">
         <v>23.45</v>
@@ -17666,7 +17664,7 @@
         </is>
       </c>
       <c r="E675" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F675" s="2" t="n">
         <v>23.45</v>
@@ -17692,7 +17690,7 @@
         </is>
       </c>
       <c r="E676" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F676" s="2" t="n">
         <v>23.45</v>
@@ -17718,7 +17716,7 @@
         </is>
       </c>
       <c r="E677" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F677" s="2" t="n">
         <v>23.45</v>
@@ -17744,7 +17742,7 @@
         </is>
       </c>
       <c r="E678" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F678" s="2" t="n">
         <v>23.45</v>
@@ -17770,7 +17768,7 @@
         </is>
       </c>
       <c r="E679" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F679" s="2" t="n">
         <v>23.45</v>
@@ -17796,7 +17794,7 @@
         </is>
       </c>
       <c r="E680" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F680" s="2" t="n">
         <v>23.45</v>
@@ -17822,7 +17820,7 @@
         </is>
       </c>
       <c r="E681" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F681" s="2" t="n">
         <v>23.45</v>
@@ -17848,7 +17846,7 @@
         </is>
       </c>
       <c r="E682" s="2" t="n">
-        <v>44215.76392171296</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F682" s="2" t="n">
         <v>23.45</v>
@@ -17874,7 +17872,7 @@
         </is>
       </c>
       <c r="E683" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F683" s="2" t="n">
         <v>23.45</v>
@@ -17900,7 +17898,7 @@
         </is>
       </c>
       <c r="E684" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F684" s="2" t="n">
         <v>23.45</v>
@@ -17926,7 +17924,7 @@
         </is>
       </c>
       <c r="E685" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F685" s="2" t="n">
         <v>23.45</v>
@@ -17952,7 +17950,7 @@
         </is>
       </c>
       <c r="E686" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F686" s="2" t="n">
         <v>23.45</v>
@@ -17978,7 +17976,7 @@
         </is>
       </c>
       <c r="E687" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F687" s="2" t="n">
         <v>23.45</v>
@@ -18004,7 +18002,7 @@
         </is>
       </c>
       <c r="E688" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F688" s="2" t="n">
         <v>23.45</v>
@@ -18030,7 +18028,7 @@
         </is>
       </c>
       <c r="E689" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F689" s="2" t="n">
         <v>23.45</v>
@@ -18056,7 +18054,7 @@
         </is>
       </c>
       <c r="E690" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F690" s="2" t="n">
         <v>23.45</v>
@@ -18082,7 +18080,7 @@
         </is>
       </c>
       <c r="E691" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F691" s="2" t="n">
         <v>23.45</v>
@@ -18108,7 +18106,7 @@
         </is>
       </c>
       <c r="E692" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F692" s="2" t="n">
         <v>23.45</v>
@@ -18134,7 +18132,7 @@
         </is>
       </c>
       <c r="E693" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F693" s="2" t="n">
         <v>23.45</v>
@@ -18160,7 +18158,7 @@
         </is>
       </c>
       <c r="E694" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F694" s="2" t="n">
         <v>23.45</v>
@@ -18186,7 +18184,7 @@
         </is>
       </c>
       <c r="E695" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F695" s="2" t="n">
         <v>23.45</v>
@@ -18212,7 +18210,7 @@
         </is>
       </c>
       <c r="E696" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F696" s="2" t="n">
         <v>23.45</v>
@@ -18238,7 +18236,7 @@
         </is>
       </c>
       <c r="E697" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F697" s="2" t="n">
         <v>23.45</v>
@@ -18264,7 +18262,7 @@
         </is>
       </c>
       <c r="E698" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F698" s="2" t="n">
         <v>23.45</v>
@@ -18290,7 +18288,7 @@
         </is>
       </c>
       <c r="E699" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F699" s="2" t="n">
         <v>23.45</v>
@@ -18316,7 +18314,7 @@
         </is>
       </c>
       <c r="E700" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F700" s="2" t="n">
         <v>23.45</v>
@@ -18342,7 +18340,7 @@
         </is>
       </c>
       <c r="E701" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F701" s="2" t="n">
         <v>23.45</v>
@@ -18368,7 +18366,7 @@
         </is>
       </c>
       <c r="E702" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F702" s="2" t="n">
         <v>23.45</v>
@@ -18394,7 +18392,7 @@
         </is>
       </c>
       <c r="E703" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F703" s="2" t="n">
         <v>23.45</v>
@@ -18420,7 +18418,7 @@
         </is>
       </c>
       <c r="E704" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F704" s="2" t="n">
         <v>23.45</v>
@@ -18446,7 +18444,7 @@
         </is>
       </c>
       <c r="E705" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855623842</v>
       </c>
       <c r="F705" s="2" t="n">
         <v>23.45</v>
@@ -18472,7 +18470,7 @@
         </is>
       </c>
       <c r="E706" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F706" s="2" t="n">
         <v>23.45</v>
@@ -18498,7 +18496,7 @@
         </is>
       </c>
       <c r="E707" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F707" s="2" t="n">
         <v>23.45</v>
@@ -18524,7 +18522,7 @@
         </is>
       </c>
       <c r="E708" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F708" s="2" t="n">
         <v>23.45</v>
@@ -18550,7 +18548,7 @@
         </is>
       </c>
       <c r="E709" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F709" s="2" t="n">
         <v>23.45</v>
@@ -18576,7 +18574,7 @@
         </is>
       </c>
       <c r="E710" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F710" s="2" t="n">
         <v>23.45</v>
@@ -18602,7 +18600,7 @@
         </is>
       </c>
       <c r="E711" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F711" s="2" t="n">
         <v>23.45</v>
@@ -18628,7 +18626,7 @@
         </is>
       </c>
       <c r="E712" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F712" s="2" t="n">
         <v>23.45</v>
@@ -18654,7 +18652,7 @@
         </is>
       </c>
       <c r="E713" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F713" s="2" t="n">
         <v>23.45</v>
@@ -18680,7 +18678,7 @@
         </is>
       </c>
       <c r="E714" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F714" s="2" t="n">
         <v>23.45</v>
@@ -18706,7 +18704,7 @@
         </is>
       </c>
       <c r="E715" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F715" s="2" t="n">
         <v>23.45</v>
@@ -18732,7 +18730,7 @@
         </is>
       </c>
       <c r="E716" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F716" s="2" t="n">
         <v>23.45</v>
@@ -18758,7 +18756,7 @@
         </is>
       </c>
       <c r="E717" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F717" s="2" t="n">
         <v>23.45</v>
@@ -18784,7 +18782,7 @@
         </is>
       </c>
       <c r="E718" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F718" s="2" t="n">
         <v>23.45</v>
@@ -18810,7 +18808,7 @@
         </is>
       </c>
       <c r="E719" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F719" s="2" t="n">
         <v>23.45</v>
@@ -18836,7 +18834,7 @@
         </is>
       </c>
       <c r="E720" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F720" s="2" t="n">
         <v>23.45</v>
@@ -18862,7 +18860,7 @@
         </is>
       </c>
       <c r="E721" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F721" s="2" t="n">
         <v>23.45</v>
@@ -18888,7 +18886,7 @@
         </is>
       </c>
       <c r="E722" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F722" s="2" t="n">
         <v>23.45</v>
@@ -18914,7 +18912,7 @@
         </is>
       </c>
       <c r="E723" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F723" s="2" t="n">
         <v>23.45</v>
@@ -18940,7 +18938,7 @@
         </is>
       </c>
       <c r="E724" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F724" s="2" t="n">
         <v>23.45</v>
@@ -18966,7 +18964,7 @@
         </is>
       </c>
       <c r="E725" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F725" s="2" t="n">
         <v>23.45</v>
@@ -18992,7 +18990,7 @@
         </is>
       </c>
       <c r="E726" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F726" s="2" t="n">
         <v>23.45</v>
@@ -19018,7 +19016,7 @@
         </is>
       </c>
       <c r="E727" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F727" s="2" t="n">
         <v>23.45</v>
@@ -19044,7 +19042,7 @@
         </is>
       </c>
       <c r="E728" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F728" s="2" t="n">
         <v>23.45</v>
@@ -19070,7 +19068,7 @@
         </is>
       </c>
       <c r="E729" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F729" s="2" t="n">
         <v>23.45</v>
@@ -19096,7 +19094,7 @@
         </is>
       </c>
       <c r="E730" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F730" s="2" t="n">
         <v>23.45</v>
@@ -19122,7 +19120,7 @@
         </is>
       </c>
       <c r="E731" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F731" s="2" t="n">
         <v>23.45</v>
@@ -19148,7 +19146,7 @@
         </is>
       </c>
       <c r="E732" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F732" s="2" t="n">
         <v>23.45</v>
@@ -19174,7 +19172,7 @@
         </is>
       </c>
       <c r="E733" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F733" s="2" t="n">
         <v>23.45</v>
@@ -19200,7 +19198,7 @@
         </is>
       </c>
       <c r="E734" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F734" s="2" t="n">
         <v>23.45</v>
@@ -19226,7 +19224,7 @@
         </is>
       </c>
       <c r="E735" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F735" s="2" t="n">
         <v>23.45</v>
@@ -19252,7 +19250,7 @@
         </is>
       </c>
       <c r="E736" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F736" s="2" t="n">
         <v>23.45</v>
@@ -19278,7 +19276,7 @@
         </is>
       </c>
       <c r="E737" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F737" s="2" t="n">
         <v>23.45</v>
@@ -19304,7 +19302,7 @@
         </is>
       </c>
       <c r="E738" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F738" s="2" t="n">
         <v>23.45</v>
@@ -19330,7 +19328,7 @@
         </is>
       </c>
       <c r="E739" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F739" s="2" t="n">
         <v>23.45</v>
@@ -19356,7 +19354,7 @@
         </is>
       </c>
       <c r="E740" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F740" s="2" t="n">
         <v>23.45</v>
@@ -19382,7 +19380,7 @@
         </is>
       </c>
       <c r="E741" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F741" s="2" t="n">
         <v>23.45</v>
@@ -19408,7 +19406,7 @@
         </is>
       </c>
       <c r="E742" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F742" s="2" t="n">
         <v>23.45</v>
@@ -19434,7 +19432,7 @@
         </is>
       </c>
       <c r="E743" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F743" s="2" t="n">
         <v>23.45</v>
@@ -19460,7 +19458,7 @@
         </is>
       </c>
       <c r="E744" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F744" s="2" t="n">
         <v>23.45</v>
@@ -19486,7 +19484,7 @@
         </is>
       </c>
       <c r="E745" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F745" s="2" t="n">
         <v>23.45</v>
@@ -19512,7 +19510,7 @@
         </is>
       </c>
       <c r="E746" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F746" s="2" t="n">
         <v>23.45</v>
@@ -19538,7 +19536,7 @@
         </is>
       </c>
       <c r="E747" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F747" s="2" t="n">
         <v>23.45</v>
@@ -19564,7 +19562,7 @@
         </is>
       </c>
       <c r="E748" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F748" s="2" t="n">
         <v>23.45</v>
@@ -19590,7 +19588,7 @@
         </is>
       </c>
       <c r="E749" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F749" s="2" t="n">
         <v>23.45</v>
@@ -19616,7 +19614,7 @@
         </is>
       </c>
       <c r="E750" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F750" s="2" t="n">
         <v>23.45</v>
@@ -19642,7 +19640,7 @@
         </is>
       </c>
       <c r="E751" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F751" s="2" t="n">
         <v>23.45</v>
@@ -19668,7 +19666,7 @@
         </is>
       </c>
       <c r="E752" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F752" s="2" t="n">
         <v>23.45</v>
@@ -19694,7 +19692,7 @@
         </is>
       </c>
       <c r="E753" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F753" s="2" t="n">
         <v>23.45</v>
@@ -19720,7 +19718,7 @@
         </is>
       </c>
       <c r="E754" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F754" s="2" t="n">
         <v>23.45</v>
@@ -19746,7 +19744,7 @@
         </is>
       </c>
       <c r="E755" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F755" s="2" t="n">
         <v>23.45</v>
@@ -19772,7 +19770,7 @@
         </is>
       </c>
       <c r="E756" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F756" s="2" t="n">
         <v>23.45</v>
@@ -19798,7 +19796,7 @@
         </is>
       </c>
       <c r="E757" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F757" s="2" t="n">
         <v>23.45</v>
@@ -19824,7 +19822,7 @@
         </is>
       </c>
       <c r="E758" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F758" s="2" t="n">
         <v>23.45</v>
@@ -19850,7 +19848,7 @@
         </is>
       </c>
       <c r="E759" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F759" s="2" t="n">
         <v>23.45</v>
@@ -19876,7 +19874,7 @@
         </is>
       </c>
       <c r="E760" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F760" s="2" t="n">
         <v>23.45</v>
@@ -19902,7 +19900,7 @@
         </is>
       </c>
       <c r="E761" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F761" s="2" t="n">
         <v>23.45</v>
@@ -19928,7 +19926,7 @@
         </is>
       </c>
       <c r="E762" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F762" s="2" t="n">
         <v>23.45</v>
@@ -19954,7 +19952,7 @@
         </is>
       </c>
       <c r="E763" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F763" s="2" t="n">
         <v>23.45</v>
@@ -19980,7 +19978,7 @@
         </is>
       </c>
       <c r="E764" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F764" s="2" t="n">
         <v>23.45</v>
@@ -20006,7 +20004,7 @@
         </is>
       </c>
       <c r="E765" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F765" s="2" t="n">
         <v>23.45</v>
@@ -20032,7 +20030,7 @@
         </is>
       </c>
       <c r="E766" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F766" s="2" t="n">
         <v>23.45</v>
@@ -20058,7 +20056,7 @@
         </is>
       </c>
       <c r="E767" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F767" s="2" t="n">
         <v>23.45</v>
@@ -20084,7 +20082,7 @@
         </is>
       </c>
       <c r="E768" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F768" s="2" t="n">
         <v>23.45</v>
@@ -20110,7 +20108,7 @@
         </is>
       </c>
       <c r="E769" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F769" s="2" t="n">
         <v>23.45</v>
@@ -20136,7 +20134,7 @@
         </is>
       </c>
       <c r="E770" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F770" s="2" t="n">
         <v>23.45</v>
@@ -20162,7 +20160,7 @@
         </is>
       </c>
       <c r="E771" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F771" s="2" t="n">
         <v>23.45</v>
@@ -20188,7 +20186,7 @@
         </is>
       </c>
       <c r="E772" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F772" s="2" t="n">
         <v>23.45</v>
@@ -20214,7 +20212,7 @@
         </is>
       </c>
       <c r="E773" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F773" s="2" t="n">
         <v>23.45</v>
@@ -20240,7 +20238,7 @@
         </is>
       </c>
       <c r="E774" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F774" s="2" t="n">
         <v>23.45</v>
@@ -20266,7 +20264,7 @@
         </is>
       </c>
       <c r="E775" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F775" s="2" t="n">
         <v>23.45</v>
@@ -20292,7 +20290,7 @@
         </is>
       </c>
       <c r="E776" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F776" s="2" t="n">
         <v>23.45</v>
@@ -20318,7 +20316,7 @@
         </is>
       </c>
       <c r="E777" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F777" s="2" t="n">
         <v>23.45</v>
@@ -20344,7 +20342,7 @@
         </is>
       </c>
       <c r="E778" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F778" s="2" t="n">
         <v>23.45</v>
@@ -20370,7 +20368,7 @@
         </is>
       </c>
       <c r="E779" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F779" s="2" t="n">
         <v>23.45</v>
@@ -20396,7 +20394,7 @@
         </is>
       </c>
       <c r="E780" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F780" s="2" t="n">
         <v>23.45</v>
@@ -20422,7 +20420,7 @@
         </is>
       </c>
       <c r="E781" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F781" s="2" t="n">
         <v>23.45</v>
@@ -20448,7 +20446,7 @@
         </is>
       </c>
       <c r="E782" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F782" s="2" t="n">
         <v>23.45</v>
@@ -20474,7 +20472,7 @@
         </is>
       </c>
       <c r="E783" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F783" s="2" t="n">
         <v>23.45</v>
@@ -20500,7 +20498,7 @@
         </is>
       </c>
       <c r="E784" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F784" s="2" t="n">
         <v>23.45</v>
@@ -20526,7 +20524,7 @@
         </is>
       </c>
       <c r="E785" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F785" s="2" t="n">
         <v>23.45</v>
@@ -20552,7 +20550,7 @@
         </is>
       </c>
       <c r="E786" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F786" s="2" t="n">
         <v>23.45</v>
@@ -20578,7 +20576,7 @@
         </is>
       </c>
       <c r="E787" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F787" s="2" t="n">
         <v>23.45</v>
@@ -20604,7 +20602,7 @@
         </is>
       </c>
       <c r="E788" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F788" s="2" t="n">
         <v>23.45</v>
@@ -20630,7 +20628,7 @@
         </is>
       </c>
       <c r="E789" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F789" s="2" t="n">
         <v>23.45</v>
@@ -20656,7 +20654,7 @@
         </is>
       </c>
       <c r="E790" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F790" s="2" t="n">
         <v>23.45</v>
@@ -20682,7 +20680,7 @@
         </is>
       </c>
       <c r="E791" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F791" s="2" t="n">
         <v>23.45</v>
@@ -20708,7 +20706,7 @@
         </is>
       </c>
       <c r="E792" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F792" s="2" t="n">
         <v>23.45</v>
@@ -20734,7 +20732,7 @@
         </is>
       </c>
       <c r="E793" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F793" s="2" t="n">
         <v>23.45</v>
@@ -20760,7 +20758,7 @@
         </is>
       </c>
       <c r="E794" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F794" s="2" t="n">
         <v>23.45</v>
@@ -20786,7 +20784,7 @@
         </is>
       </c>
       <c r="E795" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F795" s="2" t="n">
         <v>23.45</v>
@@ -20812,7 +20810,7 @@
         </is>
       </c>
       <c r="E796" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F796" s="2" t="n">
         <v>23.45</v>
@@ -20838,7 +20836,7 @@
         </is>
       </c>
       <c r="E797" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F797" s="2" t="n">
         <v>23.45</v>
@@ -20864,7 +20862,7 @@
         </is>
       </c>
       <c r="E798" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F798" s="2" t="n">
         <v>23.45</v>
@@ -20890,7 +20888,7 @@
         </is>
       </c>
       <c r="E799" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F799" s="2" t="n">
         <v>23.45</v>
@@ -20916,7 +20914,7 @@
         </is>
       </c>
       <c r="E800" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F800" s="2" t="n">
         <v>23.45</v>
@@ -20942,7 +20940,7 @@
         </is>
       </c>
       <c r="E801" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F801" s="2" t="n">
         <v>23.45</v>
@@ -20968,7 +20966,7 @@
         </is>
       </c>
       <c r="E802" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F802" s="2" t="n">
         <v>23.45</v>
@@ -20994,7 +20992,7 @@
         </is>
       </c>
       <c r="E803" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F803" s="2" t="n">
         <v>23.45</v>
@@ -21020,7 +21018,7 @@
         </is>
       </c>
       <c r="E804" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F804" s="2" t="n">
         <v>23.45</v>
@@ -21046,7 +21044,7 @@
         </is>
       </c>
       <c r="E805" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F805" s="2" t="n">
         <v>23.45</v>
@@ -21072,7 +21070,7 @@
         </is>
       </c>
       <c r="E806" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F806" s="2" t="n">
         <v>23.45</v>
@@ -21098,7 +21096,7 @@
         </is>
       </c>
       <c r="E807" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F807" s="2" t="n">
         <v>23.45</v>
@@ -21124,7 +21122,7 @@
         </is>
       </c>
       <c r="E808" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F808" s="2" t="n">
         <v>23.45</v>
@@ -21150,7 +21148,7 @@
         </is>
       </c>
       <c r="E809" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F809" s="2" t="n">
         <v>23.45</v>
@@ -21176,7 +21174,7 @@
         </is>
       </c>
       <c r="E810" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F810" s="2" t="n">
         <v>23.45</v>
@@ -21202,7 +21200,7 @@
         </is>
       </c>
       <c r="E811" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F811" s="2" t="n">
         <v>23.45</v>
@@ -21228,7 +21226,7 @@
         </is>
       </c>
       <c r="E812" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F812" s="2" t="n">
         <v>23.45</v>
@@ -21254,7 +21252,7 @@
         </is>
       </c>
       <c r="E813" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F813" s="2" t="n">
         <v>23.45</v>
@@ -21280,7 +21278,7 @@
         </is>
       </c>
       <c r="E814" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F814" s="2" t="n">
         <v>23.45</v>
@@ -21306,7 +21304,7 @@
         </is>
       </c>
       <c r="E815" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F815" s="2" t="n">
         <v>23.45</v>
@@ -21332,7 +21330,7 @@
         </is>
       </c>
       <c r="E816" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F816" s="2" t="n">
         <v>23.45</v>
@@ -21358,7 +21356,7 @@
         </is>
       </c>
       <c r="E817" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F817" s="2" t="n">
         <v>23.45</v>
@@ -21384,7 +21382,7 @@
         </is>
       </c>
       <c r="E818" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F818" s="2" t="n">
         <v>23.45</v>
@@ -21410,7 +21408,7 @@
         </is>
       </c>
       <c r="E819" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F819" s="2" t="n">
         <v>23.45</v>
@@ -21436,7 +21434,7 @@
         </is>
       </c>
       <c r="E820" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F820" s="2" t="n">
         <v>23.45</v>
@@ -21462,7 +21460,7 @@
         </is>
       </c>
       <c r="E821" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F821" s="2" t="n">
         <v>23.45</v>
@@ -21488,7 +21486,7 @@
         </is>
       </c>
       <c r="E822" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F822" s="2" t="n">
         <v>23.45</v>
@@ -21514,7 +21512,7 @@
         </is>
       </c>
       <c r="E823" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F823" s="2" t="n">
         <v>23.45</v>
@@ -21540,7 +21538,7 @@
         </is>
       </c>
       <c r="E824" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F824" s="2" t="n">
         <v>23.45</v>
@@ -21566,7 +21564,7 @@
         </is>
       </c>
       <c r="E825" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F825" s="2" t="n">
         <v>23.45</v>
@@ -21592,7 +21590,7 @@
         </is>
       </c>
       <c r="E826" s="2" t="n">
-        <v>44215.76392172454</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F826" s="2" t="n">
         <v>23.45</v>
@@ -21618,7 +21616,7 @@
         </is>
       </c>
       <c r="E827" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F827" s="2" t="n">
         <v>23.45</v>
@@ -21644,7 +21642,7 @@
         </is>
       </c>
       <c r="E828" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F828" s="2" t="n">
         <v>23.45</v>
@@ -21670,7 +21668,7 @@
         </is>
       </c>
       <c r="E829" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F829" s="2" t="n">
         <v>23.45</v>
@@ -21696,7 +21694,7 @@
         </is>
       </c>
       <c r="E830" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F830" s="2" t="n">
         <v>23.45</v>
@@ -21722,7 +21720,7 @@
         </is>
       </c>
       <c r="E831" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F831" s="2" t="n">
         <v>23.45</v>
@@ -21748,7 +21746,7 @@
         </is>
       </c>
       <c r="E832" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F832" s="2" t="n">
         <v>23.45</v>
@@ -21774,7 +21772,7 @@
         </is>
       </c>
       <c r="E833" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F833" s="2" t="n">
         <v>23.45</v>
@@ -21800,7 +21798,7 @@
         </is>
       </c>
       <c r="E834" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F834" s="2" t="n">
         <v>23.45</v>
@@ -21826,7 +21824,7 @@
         </is>
       </c>
       <c r="E835" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F835" s="2" t="n">
         <v>23.45</v>
@@ -21852,7 +21850,7 @@
         </is>
       </c>
       <c r="E836" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F836" s="2" t="n">
         <v>23.45</v>
@@ -21878,7 +21876,7 @@
         </is>
       </c>
       <c r="E837" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F837" s="2" t="n">
         <v>23.45</v>
@@ -21904,7 +21902,7 @@
         </is>
       </c>
       <c r="E838" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F838" s="2" t="n">
         <v>23.45</v>
@@ -21930,7 +21928,7 @@
         </is>
       </c>
       <c r="E839" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F839" s="2" t="n">
         <v>23.45</v>
@@ -21956,7 +21954,7 @@
         </is>
       </c>
       <c r="E840" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F840" s="2" t="n">
         <v>23.45</v>
@@ -21982,7 +21980,7 @@
         </is>
       </c>
       <c r="E841" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855625</v>
       </c>
       <c r="F841" s="2" t="n">
         <v>23.45</v>
@@ -22008,7 +22006,7 @@
         </is>
       </c>
       <c r="E842" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F842" s="2" t="n">
         <v>23.45</v>
@@ -22034,7 +22032,7 @@
         </is>
       </c>
       <c r="E843" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F843" s="2" t="n">
         <v>23.45</v>
@@ -22060,7 +22058,7 @@
         </is>
       </c>
       <c r="E844" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F844" s="2" t="n">
         <v>23.45</v>
@@ -22086,7 +22084,7 @@
         </is>
       </c>
       <c r="E845" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F845" s="2" t="n">
         <v>23.45</v>
@@ -22112,7 +22110,7 @@
         </is>
       </c>
       <c r="E846" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F846" s="2" t="n">
         <v>23.45</v>
@@ -22138,7 +22136,7 @@
         </is>
       </c>
       <c r="E847" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F847" s="2" t="n">
         <v>23.45</v>
@@ -22164,7 +22162,7 @@
         </is>
       </c>
       <c r="E848" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F848" s="2" t="n">
         <v>23.45</v>
@@ -22190,7 +22188,7 @@
         </is>
       </c>
       <c r="E849" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F849" s="2" t="n">
         <v>23.45</v>
@@ -22216,7 +22214,7 @@
         </is>
       </c>
       <c r="E850" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F850" s="2" t="n">
         <v>23.45</v>
@@ -22242,7 +22240,7 @@
         </is>
       </c>
       <c r="E851" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F851" s="2" t="n">
         <v>23.45</v>
@@ -22268,7 +22266,7 @@
         </is>
       </c>
       <c r="E852" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F852" s="2" t="n">
         <v>23.45</v>
@@ -22294,7 +22292,7 @@
         </is>
       </c>
       <c r="E853" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F853" s="2" t="n">
         <v>23.45</v>
@@ -22320,7 +22318,7 @@
         </is>
       </c>
       <c r="E854" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F854" s="2" t="n">
         <v>23.45</v>
@@ -22346,7 +22344,7 @@
         </is>
       </c>
       <c r="E855" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F855" s="2" t="n">
         <v>23.45</v>
@@ -22372,7 +22370,7 @@
         </is>
       </c>
       <c r="E856" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F856" s="2" t="n">
         <v>23.45</v>
@@ -22398,7 +22396,7 @@
         </is>
       </c>
       <c r="E857" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F857" s="2" t="n">
         <v>23.45</v>
@@ -22424,7 +22422,7 @@
         </is>
       </c>
       <c r="E858" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F858" s="2" t="n">
         <v>23.45</v>
@@ -22450,7 +22448,7 @@
         </is>
       </c>
       <c r="E859" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F859" s="2" t="n">
         <v>23.45</v>
@@ -22476,7 +22474,7 @@
         </is>
       </c>
       <c r="E860" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F860" s="2" t="n">
         <v>23.45</v>
@@ -22502,7 +22500,7 @@
         </is>
       </c>
       <c r="E861" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F861" s="2" t="n">
         <v>23.45</v>
@@ -22528,7 +22526,7 @@
         </is>
       </c>
       <c r="E862" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F862" s="2" t="n">
         <v>23.45</v>
@@ -22554,7 +22552,7 @@
         </is>
       </c>
       <c r="E863" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F863" s="2" t="n">
         <v>23.45</v>
@@ -22580,7 +22578,7 @@
         </is>
       </c>
       <c r="E864" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F864" s="2" t="n">
         <v>23.45</v>
@@ -22606,7 +22604,7 @@
         </is>
       </c>
       <c r="E865" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F865" s="2" t="n">
         <v>23.45</v>
@@ -22632,7 +22630,7 @@
         </is>
       </c>
       <c r="E866" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F866" s="2" t="n">
         <v>23.45</v>
@@ -22658,7 +22656,7 @@
         </is>
       </c>
       <c r="E867" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F867" s="2" t="n">
         <v>23.45</v>
@@ -22684,7 +22682,7 @@
         </is>
       </c>
       <c r="E868" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F868" s="2" t="n">
         <v>23.45</v>
@@ -22710,7 +22708,7 @@
         </is>
       </c>
       <c r="E869" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F869" s="2" t="n">
         <v>23.45</v>
@@ -22736,7 +22734,7 @@
         </is>
       </c>
       <c r="E870" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F870" s="2" t="n">
         <v>23.45</v>
@@ -22762,7 +22760,7 @@
         </is>
       </c>
       <c r="E871" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F871" s="2" t="n">
         <v>23.45</v>
@@ -22788,7 +22786,7 @@
         </is>
       </c>
       <c r="E872" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F872" s="2" t="n">
         <v>23.45</v>
@@ -22814,7 +22812,7 @@
         </is>
       </c>
       <c r="E873" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F873" s="2" t="n">
         <v>23.45</v>
@@ -22840,7 +22838,7 @@
         </is>
       </c>
       <c r="E874" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F874" s="2" t="n">
         <v>23.45</v>
@@ -22866,7 +22864,7 @@
         </is>
       </c>
       <c r="E875" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F875" s="2" t="n">
         <v>23.45</v>
@@ -22892,7 +22890,7 @@
         </is>
       </c>
       <c r="E876" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F876" s="2" t="n">
         <v>23.45</v>
@@ -22918,7 +22916,7 @@
         </is>
       </c>
       <c r="E877" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F877" s="2" t="n">
         <v>23.45</v>
@@ -22944,7 +22942,7 @@
         </is>
       </c>
       <c r="E878" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F878" s="2" t="n">
         <v>23.45</v>
@@ -22970,7 +22968,7 @@
         </is>
       </c>
       <c r="E879" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F879" s="2" t="n">
         <v>23.45</v>
@@ -22996,7 +22994,7 @@
         </is>
       </c>
       <c r="E880" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F880" s="2" t="n">
         <v>23.45</v>
@@ -23022,7 +23020,7 @@
         </is>
       </c>
       <c r="E881" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F881" s="2" t="n">
         <v>23.45</v>
@@ -23048,7 +23046,7 @@
         </is>
       </c>
       <c r="E882" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F882" s="2" t="n">
         <v>23.45</v>
@@ -23074,7 +23072,7 @@
         </is>
       </c>
       <c r="E883" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F883" s="2" t="n">
         <v>23.45</v>
@@ -23100,7 +23098,7 @@
         </is>
       </c>
       <c r="E884" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F884" s="2" t="n">
         <v>23.45</v>
@@ -23126,7 +23124,7 @@
         </is>
       </c>
       <c r="E885" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F885" s="2" t="n">
         <v>23.45</v>
@@ -23152,7 +23150,7 @@
         </is>
       </c>
       <c r="E886" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F886" s="2" t="n">
         <v>23.45</v>
@@ -23178,7 +23176,7 @@
         </is>
       </c>
       <c r="E887" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F887" s="2" t="n">
         <v>23.45</v>
@@ -23204,7 +23202,7 @@
         </is>
       </c>
       <c r="E888" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F888" s="2" t="n">
         <v>23.45</v>
@@ -23230,7 +23228,7 @@
         </is>
       </c>
       <c r="E889" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F889" s="2" t="n">
         <v>23.45</v>
@@ -23256,7 +23254,7 @@
         </is>
       </c>
       <c r="E890" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F890" s="2" t="n">
         <v>23.45</v>
@@ -23282,7 +23280,7 @@
         </is>
       </c>
       <c r="E891" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F891" s="2" t="n">
         <v>23.45</v>
@@ -23308,7 +23306,7 @@
         </is>
       </c>
       <c r="E892" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F892" s="2" t="n">
         <v>23.45</v>
@@ -23334,7 +23332,7 @@
         </is>
       </c>
       <c r="E893" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F893" s="2" t="n">
         <v>23.45</v>
@@ -23360,7 +23358,7 @@
         </is>
       </c>
       <c r="E894" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F894" s="2" t="n">
         <v>23.45</v>
@@ -23386,7 +23384,7 @@
         </is>
       </c>
       <c r="E895" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F895" s="2" t="n">
         <v>23.45</v>
@@ -23412,7 +23410,7 @@
         </is>
       </c>
       <c r="E896" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F896" s="2" t="n">
         <v>23.45</v>
@@ -23438,7 +23436,7 @@
         </is>
       </c>
       <c r="E897" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F897" s="2" t="n">
         <v>23.45</v>
@@ -23464,7 +23462,7 @@
         </is>
       </c>
       <c r="E898" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F898" s="2" t="n">
         <v>23.45</v>
@@ -23490,7 +23488,7 @@
         </is>
       </c>
       <c r="E899" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F899" s="2" t="n">
         <v>23.45</v>
@@ -23516,7 +23514,7 @@
         </is>
       </c>
       <c r="E900" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F900" s="2" t="n">
         <v>23.45</v>
@@ -23542,7 +23540,7 @@
         </is>
       </c>
       <c r="E901" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F901" s="2" t="n">
         <v>23.45</v>
@@ -23568,7 +23566,7 @@
         </is>
       </c>
       <c r="E902" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F902" s="2" t="n">
         <v>23.45</v>
@@ -23594,7 +23592,7 @@
         </is>
       </c>
       <c r="E903" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F903" s="2" t="n">
         <v>23.45</v>
@@ -23620,7 +23618,7 @@
         </is>
       </c>
       <c r="E904" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F904" s="2" t="n">
         <v>23.45</v>
@@ -23646,7 +23644,7 @@
         </is>
       </c>
       <c r="E905" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F905" s="2" t="n">
         <v>23.45</v>
@@ -23672,7 +23670,7 @@
         </is>
       </c>
       <c r="E906" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F906" s="2" t="n">
         <v>23.45</v>
@@ -23698,7 +23696,7 @@
         </is>
       </c>
       <c r="E907" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F907" s="2" t="n">
         <v>23.45</v>
@@ -23724,7 +23722,7 @@
         </is>
       </c>
       <c r="E908" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F908" s="2" t="n">
         <v>23.45</v>
@@ -23750,7 +23748,7 @@
         </is>
       </c>
       <c r="E909" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F909" s="2" t="n">
         <v>23.45</v>
@@ -23776,7 +23774,7 @@
         </is>
       </c>
       <c r="E910" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F910" s="2" t="n">
         <v>23.45</v>
@@ -23802,7 +23800,7 @@
         </is>
       </c>
       <c r="E911" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F911" s="2" t="n">
         <v>23.45</v>
@@ -23828,7 +23826,7 @@
         </is>
       </c>
       <c r="E912" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F912" s="2" t="n">
         <v>23.45</v>
@@ -23854,7 +23852,7 @@
         </is>
       </c>
       <c r="E913" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F913" s="2" t="n">
         <v>23.45</v>
@@ -23880,7 +23878,7 @@
         </is>
       </c>
       <c r="E914" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F914" s="2" t="n">
         <v>23.45</v>
@@ -23906,7 +23904,7 @@
         </is>
       </c>
       <c r="E915" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F915" s="2" t="n">
         <v>23.45</v>
@@ -23932,7 +23930,7 @@
         </is>
       </c>
       <c r="E916" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F916" s="2" t="n">
         <v>23.45</v>
@@ -23958,7 +23956,7 @@
         </is>
       </c>
       <c r="E917" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F917" s="2" t="n">
         <v>23.45</v>
@@ -23984,7 +23982,7 @@
         </is>
       </c>
       <c r="E918" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F918" s="2" t="n">
         <v>23.45</v>
@@ -24010,7 +24008,7 @@
         </is>
       </c>
       <c r="E919" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F919" s="2" t="n">
         <v>23.45</v>
@@ -24036,7 +24034,7 @@
         </is>
       </c>
       <c r="E920" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F920" s="2" t="n">
         <v>23.45</v>
@@ -24062,7 +24060,7 @@
         </is>
       </c>
       <c r="E921" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F921" s="2" t="n">
         <v>23.45</v>
@@ -24088,7 +24086,7 @@
         </is>
       </c>
       <c r="E922" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F922" s="2" t="n">
         <v>23.45</v>
@@ -24114,7 +24112,7 @@
         </is>
       </c>
       <c r="E923" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F923" s="2" t="n">
         <v>23.45</v>
@@ -24140,7 +24138,7 @@
         </is>
       </c>
       <c r="E924" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F924" s="2" t="n">
         <v>23.45</v>
@@ -24166,7 +24164,7 @@
         </is>
       </c>
       <c r="E925" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F925" s="2" t="n">
         <v>23.45</v>
@@ -24192,7 +24190,7 @@
         </is>
       </c>
       <c r="E926" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F926" s="2" t="n">
         <v>23.45</v>
@@ -24218,7 +24216,7 @@
         </is>
       </c>
       <c r="E927" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F927" s="2" t="n">
         <v>23.45</v>
@@ -24244,7 +24242,7 @@
         </is>
       </c>
       <c r="E928" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F928" s="2" t="n">
         <v>23.45</v>
@@ -24270,7 +24268,7 @@
         </is>
       </c>
       <c r="E929" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F929" s="2" t="n">
         <v>23.45</v>
@@ -24296,7 +24294,7 @@
         </is>
       </c>
       <c r="E930" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F930" s="2" t="n">
         <v>23.45</v>
@@ -24322,7 +24320,7 @@
         </is>
       </c>
       <c r="E931" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F931" s="2" t="n">
         <v>23.45</v>
@@ -24348,7 +24346,7 @@
         </is>
       </c>
       <c r="E932" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F932" s="2" t="n">
         <v>23.45</v>
@@ -24374,7 +24372,7 @@
         </is>
       </c>
       <c r="E933" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F933" s="2" t="n">
         <v>23.45</v>
@@ -24400,7 +24398,7 @@
         </is>
       </c>
       <c r="E934" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F934" s="2" t="n">
         <v>23.45</v>
@@ -24426,7 +24424,7 @@
         </is>
       </c>
       <c r="E935" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F935" s="2" t="n">
         <v>23.45</v>
@@ -24452,7 +24450,7 @@
         </is>
       </c>
       <c r="E936" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F936" s="2" t="n">
         <v>23.45</v>
@@ -24478,7 +24476,7 @@
         </is>
       </c>
       <c r="E937" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F937" s="2" t="n">
         <v>23.45</v>
@@ -24504,7 +24502,7 @@
         </is>
       </c>
       <c r="E938" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F938" s="2" t="n">
         <v>23.45</v>
@@ -24530,7 +24528,7 @@
         </is>
       </c>
       <c r="E939" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F939" s="2" t="n">
         <v>23.45</v>
@@ -24556,7 +24554,7 @@
         </is>
       </c>
       <c r="E940" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F940" s="2" t="n">
         <v>23.45</v>
@@ -24582,7 +24580,7 @@
         </is>
       </c>
       <c r="E941" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.598556261575</v>
       </c>
       <c r="F941" s="2" t="n">
         <v>23.45</v>
@@ -24608,7 +24606,7 @@
         </is>
       </c>
       <c r="E942" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F942" s="2" t="n">
         <v>23.45</v>
@@ -24634,7 +24632,7 @@
         </is>
       </c>
       <c r="E943" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F943" s="2" t="n">
         <v>23.45</v>
@@ -24660,7 +24658,7 @@
         </is>
       </c>
       <c r="E944" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F944" s="2" t="n">
         <v>23.45</v>
@@ -24686,7 +24684,7 @@
         </is>
       </c>
       <c r="E945" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F945" s="2" t="n">
         <v>23.45</v>
@@ -24712,7 +24710,7 @@
         </is>
       </c>
       <c r="E946" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F946" s="2" t="n">
         <v>23.45</v>
@@ -24738,7 +24736,7 @@
         </is>
       </c>
       <c r="E947" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F947" s="2" t="n">
         <v>23.45</v>
@@ -24764,7 +24762,7 @@
         </is>
       </c>
       <c r="E948" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F948" s="2" t="n">
         <v>23.45</v>
@@ -24790,7 +24788,7 @@
         </is>
       </c>
       <c r="E949" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F949" s="2" t="n">
         <v>23.45</v>
@@ -24816,7 +24814,7 @@
         </is>
       </c>
       <c r="E950" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F950" s="2" t="n">
         <v>23.45</v>
@@ -24842,7 +24840,7 @@
         </is>
       </c>
       <c r="E951" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F951" s="2" t="n">
         <v>23.45</v>
@@ -24868,7 +24866,7 @@
         </is>
       </c>
       <c r="E952" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F952" s="2" t="n">
         <v>23.45</v>
@@ -24894,7 +24892,7 @@
         </is>
       </c>
       <c r="E953" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F953" s="2" t="n">
         <v>23.45</v>
@@ -24920,7 +24918,7 @@
         </is>
       </c>
       <c r="E954" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F954" s="2" t="n">
         <v>23.45</v>
@@ -24946,7 +24944,7 @@
         </is>
       </c>
       <c r="E955" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F955" s="2" t="n">
         <v>23.45</v>
@@ -24972,7 +24970,7 @@
         </is>
       </c>
       <c r="E956" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F956" s="2" t="n">
         <v>23.45</v>
@@ -24998,7 +24996,7 @@
         </is>
       </c>
       <c r="E957" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F957" s="2" t="n">
         <v>23.45</v>
@@ -25024,7 +25022,7 @@
         </is>
       </c>
       <c r="E958" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F958" s="2" t="n">
         <v>23.45</v>
@@ -25050,7 +25048,7 @@
         </is>
       </c>
       <c r="E959" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F959" s="2" t="n">
         <v>23.45</v>
@@ -25076,7 +25074,7 @@
         </is>
       </c>
       <c r="E960" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F960" s="2" t="n">
         <v>23.45</v>
@@ -25102,7 +25100,7 @@
         </is>
       </c>
       <c r="E961" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F961" s="2" t="n">
         <v>23.45</v>
@@ -25128,7 +25126,7 @@
         </is>
       </c>
       <c r="E962" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F962" s="2" t="n">
         <v>23.45</v>
@@ -25154,7 +25152,7 @@
         </is>
       </c>
       <c r="E963" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F963" s="2" t="n">
         <v>23.45</v>
@@ -25180,7 +25178,7 @@
         </is>
       </c>
       <c r="E964" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F964" s="2" t="n">
         <v>23.45</v>
@@ -25206,7 +25204,7 @@
         </is>
       </c>
       <c r="E965" s="2" t="n">
-        <v>44215.763921736114</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F965" s="2" t="n">
         <v>23.45</v>
@@ -25232,7 +25230,7 @@
         </is>
       </c>
       <c r="E966" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F966" s="2" t="n">
         <v>23.45</v>
@@ -25258,7 +25256,7 @@
         </is>
       </c>
       <c r="E967" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F967" s="2" t="n">
         <v>23.45</v>
@@ -25284,7 +25282,7 @@
         </is>
       </c>
       <c r="E968" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F968" s="2" t="n">
         <v>23.45</v>
@@ -25310,7 +25308,7 @@
         </is>
       </c>
       <c r="E969" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F969" s="2" t="n">
         <v>23.45</v>
@@ -25336,7 +25334,7 @@
         </is>
       </c>
       <c r="E970" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F970" s="2" t="n">
         <v>23.45</v>
@@ -25362,7 +25360,7 @@
         </is>
       </c>
       <c r="E971" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F971" s="2" t="n">
         <v>23.45</v>
@@ -25388,7 +25386,7 @@
         </is>
       </c>
       <c r="E972" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F972" s="2" t="n">
         <v>23.45</v>
@@ -25414,7 +25412,7 @@
         </is>
       </c>
       <c r="E973" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F973" s="2" t="n">
         <v>23.45</v>
@@ -25440,7 +25438,7 @@
         </is>
       </c>
       <c r="E974" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F974" s="2" t="n">
         <v>23.45</v>
@@ -25466,7 +25464,7 @@
         </is>
       </c>
       <c r="E975" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F975" s="2" t="n">
         <v>23.45</v>
@@ -25492,7 +25490,7 @@
         </is>
       </c>
       <c r="E976" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F976" s="2" t="n">
         <v>23.45</v>
@@ -25518,7 +25516,7 @@
         </is>
       </c>
       <c r="E977" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F977" s="2" t="n">
         <v>23.45</v>
@@ -25544,7 +25542,7 @@
         </is>
       </c>
       <c r="E978" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F978" s="2" t="n">
         <v>23.45</v>
@@ -25570,7 +25568,7 @@
         </is>
       </c>
       <c r="E979" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F979" s="2" t="n">
         <v>23.45</v>
@@ -25596,7 +25594,7 @@
         </is>
       </c>
       <c r="E980" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F980" s="2" t="n">
         <v>23.45</v>
@@ -25622,7 +25620,7 @@
         </is>
       </c>
       <c r="E981" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F981" s="2" t="n">
         <v>23.45</v>
@@ -25648,7 +25646,7 @@
         </is>
       </c>
       <c r="E982" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F982" s="2" t="n">
         <v>23.45</v>
@@ -25674,7 +25672,7 @@
         </is>
       </c>
       <c r="E983" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F983" s="2" t="n">
         <v>23.45</v>
@@ -25700,7 +25698,7 @@
         </is>
       </c>
       <c r="E984" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F984" s="2" t="n">
         <v>23.45</v>
@@ -25726,7 +25724,7 @@
         </is>
       </c>
       <c r="E985" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F985" s="2" t="n">
         <v>23.45</v>
@@ -25752,7 +25750,7 @@
         </is>
       </c>
       <c r="E986" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F986" s="2" t="n">
         <v>23.45</v>
@@ -25778,7 +25776,7 @@
         </is>
       </c>
       <c r="E987" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F987" s="2" t="n">
         <v>23.45</v>
@@ -25804,7 +25802,7 @@
         </is>
       </c>
       <c r="E988" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F988" s="2" t="n">
         <v>23.45</v>
@@ -25830,7 +25828,7 @@
         </is>
       </c>
       <c r="E989" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F989" s="2" t="n">
         <v>23.45</v>
@@ -25856,7 +25854,7 @@
         </is>
       </c>
       <c r="E990" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F990" s="2" t="n">
         <v>23.45</v>
@@ -25882,7 +25880,7 @@
         </is>
       </c>
       <c r="E991" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F991" s="2" t="n">
         <v>23.45</v>
@@ -25908,7 +25906,7 @@
         </is>
       </c>
       <c r="E992" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F992" s="2" t="n">
         <v>23.45</v>
@@ -25934,7 +25932,7 @@
         </is>
       </c>
       <c r="E993" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F993" s="2" t="n">
         <v>23.45</v>
@@ -25960,7 +25958,7 @@
         </is>
       </c>
       <c r="E994" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F994" s="2" t="n">
         <v>23.45</v>
@@ -25986,7 +25984,7 @@
         </is>
       </c>
       <c r="E995" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F995" s="2" t="n">
         <v>23.45</v>
@@ -26012,7 +26010,7 @@
         </is>
       </c>
       <c r="E996" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F996" s="2" t="n">
         <v>23.45</v>
@@ -26038,7 +26036,7 @@
         </is>
       </c>
       <c r="E997" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F997" s="2" t="n">
         <v>23.45</v>
@@ -26064,7 +26062,7 @@
         </is>
       </c>
       <c r="E998" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F998" s="2" t="n">
         <v>23.45</v>
@@ -26090,7 +26088,7 @@
         </is>
       </c>
       <c r="E999" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F999" s="2" t="n">
         <v>23.45</v>
@@ -26116,7 +26114,7 @@
         </is>
       </c>
       <c r="E1000" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F1000" s="2" t="n">
         <v>23.45</v>
@@ -26142,7 +26140,7 @@
         </is>
       </c>
       <c r="E1001" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F1001" s="2" t="n">
         <v>23.45</v>
@@ -26168,7 +26166,7 @@
         </is>
       </c>
       <c r="E1002" s="2" t="n">
-        <v>44215.76392174768</v>
+        <v>44217.59855627315</v>
       </c>
       <c r="F1002" s="2" t="n">
         <v>23.45</v>
@@ -26179,7 +26177,8 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F2"/>
-    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/easy-widget-excel/中文.xlsx
+++ b/easy-widget-excel/中文.xlsx
@@ -173,8 +173,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>0.0</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>就诊人次</t>
+        </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -192,7 +194,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44217.5985556713</v>
+        <v>44219.91436498843</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>23.45</v>
@@ -218,7 +220,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>44217.59855578704</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23.45</v>
@@ -244,15 +246,17 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>44217.59855578704</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>23.45</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>3.0</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>就诊人次2</t>
+        </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -270,7 +274,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44217.59855578704</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>23.45</v>
@@ -296,7 +300,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>44217.59855578704</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>23.45</v>
@@ -322,7 +326,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44217.59855578704</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>23.45</v>
@@ -348,7 +352,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>23.45</v>
@@ -374,7 +378,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>23.45</v>
@@ -400,7 +404,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>23.45</v>
@@ -426,7 +430,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>23.45</v>
@@ -452,7 +456,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>23.45</v>
@@ -478,7 +482,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>23.45</v>
@@ -504,7 +508,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>23.45</v>
@@ -530,7 +534,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>23.45</v>
@@ -556,7 +560,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>23.45</v>
@@ -582,7 +586,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>23.45</v>
@@ -608,7 +612,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>44217.59855579861</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>23.45</v>
@@ -634,7 +638,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>23.45</v>
@@ -660,7 +664,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>23.45</v>
@@ -686,7 +690,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>23.45</v>
@@ -712,7 +716,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>23.45</v>
@@ -738,7 +742,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>23.45</v>
@@ -764,7 +768,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>23.45</v>
@@ -790,7 +794,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>23.45</v>
@@ -816,7 +820,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>23.45</v>
@@ -842,7 +846,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>23.45</v>
@@ -868,7 +872,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>23.45</v>
@@ -894,7 +898,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>23.45</v>
@@ -920,7 +924,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44217.59855581018</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>23.45</v>
@@ -946,7 +950,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>23.45</v>
@@ -972,7 +976,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365034725</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>23.45</v>
@@ -998,7 +1002,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>23.45</v>
@@ -1024,7 +1028,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>23.45</v>
@@ -1050,7 +1054,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>23.45</v>
@@ -1076,7 +1080,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>23.45</v>
@@ -1102,7 +1106,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>23.45</v>
@@ -1128,7 +1132,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>23.45</v>
@@ -1154,7 +1158,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>23.45</v>
@@ -1180,7 +1184,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>23.45</v>
@@ -1206,7 +1210,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>23.45</v>
@@ -1232,7 +1236,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>23.45</v>
@@ -1258,7 +1262,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>44217.59855582176</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>23.45</v>
@@ -1284,7 +1288,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>23.45</v>
@@ -1310,7 +1314,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>23.45</v>
@@ -1336,7 +1340,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>23.45</v>
@@ -1362,7 +1366,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>23.45</v>
@@ -1388,7 +1392,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>23.45</v>
@@ -1414,7 +1418,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>23.45</v>
@@ -1440,7 +1444,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>23.45</v>
@@ -1466,7 +1470,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>23.45</v>
@@ -1492,7 +1496,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>23.45</v>
@@ -1518,7 +1522,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>23.45</v>
@@ -1544,7 +1548,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>23.45</v>
@@ -1570,7 +1574,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>44217.598555833334</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>23.45</v>
@@ -1596,7 +1600,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>23.45</v>
@@ -1622,7 +1626,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>23.45</v>
@@ -1648,7 +1652,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>23.45</v>
@@ -1674,7 +1678,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>23.45</v>
@@ -1700,7 +1704,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>23.45</v>
@@ -1726,7 +1730,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>23.45</v>
@@ -1752,7 +1756,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>23.45</v>
@@ -1778,7 +1782,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>23.45</v>
@@ -1804,7 +1808,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>23.45</v>
@@ -1830,7 +1834,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>44217.59855584491</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>23.45</v>
@@ -1856,7 +1860,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>23.45</v>
@@ -1882,7 +1886,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>23.45</v>
@@ -1908,7 +1912,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>23.45</v>
@@ -1934,7 +1938,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.914365046294</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>23.45</v>
@@ -1960,7 +1964,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>23.45</v>
@@ -1986,7 +1990,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>23.45</v>
@@ -2012,7 +2016,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>23.45</v>
@@ -2038,7 +2042,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>23.45</v>
@@ -2064,7 +2068,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>23.45</v>
@@ -2090,7 +2094,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>23.45</v>
@@ -2116,7 +2120,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>23.45</v>
@@ -2142,7 +2146,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>23.45</v>
@@ -2168,7 +2172,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>44217.59855585648</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>23.45</v>
@@ -2194,7 +2198,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>23.45</v>
@@ -2220,7 +2224,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>23.45</v>
@@ -2246,7 +2250,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>23.45</v>
@@ -2272,7 +2276,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>23.45</v>
@@ -2298,7 +2302,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>23.45</v>
@@ -2324,7 +2328,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>23.45</v>
@@ -2350,7 +2354,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>23.45</v>
@@ -2376,7 +2380,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>23.45</v>
@@ -2402,7 +2406,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>23.45</v>
@@ -2428,7 +2432,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>23.45</v>
@@ -2454,7 +2458,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>23.45</v>
@@ -2480,7 +2484,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>23.45</v>
@@ -2506,7 +2510,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>23.45</v>
@@ -2532,7 +2536,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>23.45</v>
@@ -2558,7 +2562,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>23.45</v>
@@ -2584,7 +2588,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>44217.598555868055</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>23.45</v>
@@ -2610,7 +2614,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>23.45</v>
@@ -2636,7 +2640,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>23.45</v>
@@ -2662,7 +2666,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>23.45</v>
@@ -2688,7 +2692,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>23.45</v>
@@ -2714,7 +2718,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>23.45</v>
@@ -2740,7 +2744,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>23.45</v>
@@ -2766,7 +2770,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>23.45</v>
@@ -2792,7 +2796,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>23.45</v>
@@ -2818,7 +2822,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>23.45</v>
@@ -2844,7 +2848,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>44217.59855587963</v>
+        <v>44219.91436505787</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>23.45</v>
@@ -2870,7 +2874,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>23.45</v>
@@ -2896,7 +2900,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>23.45</v>
@@ -2922,7 +2926,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>23.45</v>
@@ -2948,7 +2952,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>23.45</v>
@@ -2974,7 +2978,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>23.45</v>
@@ -3000,7 +3004,7 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>23.45</v>
@@ -3026,7 +3030,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>23.45</v>
@@ -3052,7 +3056,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>23.45</v>
@@ -3078,7 +3082,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>23.45</v>
@@ -3104,7 +3108,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>23.45</v>
@@ -3130,7 +3134,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>23.45</v>
@@ -3156,7 +3160,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F117" s="2" t="n">
         <v>23.45</v>
@@ -3182,7 +3186,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>23.45</v>
@@ -3208,7 +3212,7 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>23.45</v>
@@ -3234,7 +3238,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>44217.59855598379</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>23.45</v>
@@ -3260,7 +3264,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>23.45</v>
@@ -3286,7 +3290,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>23.45</v>
@@ -3312,7 +3316,7 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>23.45</v>
@@ -3338,7 +3342,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>23.45</v>
@@ -3364,7 +3368,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>23.45</v>
@@ -3390,7 +3394,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F126" s="2" t="n">
         <v>23.45</v>
@@ -3416,7 +3420,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F127" s="2" t="n">
         <v>23.45</v>
@@ -3442,7 +3446,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>23.45</v>
@@ -3468,7 +3472,7 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>23.45</v>
@@ -3494,7 +3498,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>23.45</v>
@@ -3520,7 +3524,7 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F131" s="2" t="n">
         <v>23.45</v>
@@ -3546,7 +3550,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>23.45</v>
@@ -3572,7 +3576,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>23.45</v>
@@ -3598,7 +3602,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>23.45</v>
@@ -3624,7 +3628,7 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>23.45</v>
@@ -3650,7 +3654,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>23.45</v>
@@ -3676,7 +3680,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.914365069446</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>23.45</v>
@@ -3702,7 +3706,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>23.45</v>
@@ -3728,7 +3732,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F139" s="2" t="n">
         <v>23.45</v>
@@ -3754,7 +3758,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>23.45</v>
@@ -3780,7 +3784,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>23.45</v>
@@ -3806,7 +3810,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>23.45</v>
@@ -3832,7 +3836,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>23.45</v>
@@ -3858,7 +3862,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>23.45</v>
@@ -3884,7 +3888,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F145" s="2" t="n">
         <v>23.45</v>
@@ -3910,7 +3914,7 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F146" s="2" t="n">
         <v>23.45</v>
@@ -3936,7 +3940,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>23.45</v>
@@ -3962,7 +3966,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F148" s="2" t="n">
         <v>23.45</v>
@@ -3988,7 +3992,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>23.45</v>
@@ -4014,7 +4018,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>44217.59855599537</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>23.45</v>
@@ -4040,7 +4044,7 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F151" s="2" t="n">
         <v>23.45</v>
@@ -4066,7 +4070,7 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F152" s="2" t="n">
         <v>23.45</v>
@@ -4092,7 +4096,7 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>23.45</v>
@@ -4118,7 +4122,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>23.45</v>
@@ -4144,7 +4148,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>23.45</v>
@@ -4170,7 +4174,7 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>23.45</v>
@@ -4196,7 +4200,7 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>23.45</v>
@@ -4222,7 +4226,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>23.45</v>
@@ -4248,7 +4252,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>23.45</v>
@@ -4274,7 +4278,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>23.45</v>
@@ -4300,7 +4304,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>23.45</v>
@@ -4326,7 +4330,7 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>23.45</v>
@@ -4352,7 +4356,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>23.45</v>
@@ -4378,7 +4382,7 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F164" s="2" t="n">
         <v>23.45</v>
@@ -4404,7 +4408,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>23.45</v>
@@ -4430,7 +4434,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>23.45</v>
@@ -4456,7 +4460,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F167" s="2" t="n">
         <v>23.45</v>
@@ -4482,7 +4486,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>23.45</v>
@@ -4508,7 +4512,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>23.45</v>
@@ -4534,7 +4538,7 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F170" s="2" t="n">
         <v>23.45</v>
@@ -4560,7 +4564,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>23.45</v>
@@ -4586,7 +4590,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F172" s="2" t="n">
         <v>23.45</v>
@@ -4612,7 +4616,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F173" s="2" t="n">
         <v>23.45</v>
@@ -4638,7 +4642,7 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F174" s="2" t="n">
         <v>23.45</v>
@@ -4664,7 +4668,7 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F175" s="2" t="n">
         <v>23.45</v>
@@ -4690,7 +4694,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>23.45</v>
@@ -4716,7 +4720,7 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>23.45</v>
@@ -4742,7 +4746,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>23.45</v>
@@ -4768,7 +4772,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F179" s="2" t="n">
         <v>23.45</v>
@@ -4794,7 +4798,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F180" s="2" t="n">
         <v>23.45</v>
@@ -4820,7 +4824,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F181" s="2" t="n">
         <v>23.45</v>
@@ -4846,7 +4850,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>23.45</v>
@@ -4872,7 +4876,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>23.45</v>
@@ -4898,7 +4902,7 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436508102</v>
       </c>
       <c r="F184" s="2" t="n">
         <v>23.45</v>
@@ -4924,7 +4928,7 @@
         </is>
       </c>
       <c r="E185" s="2" t="n">
-        <v>44217.598556006946</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>23.45</v>
@@ -4950,7 +4954,7 @@
         </is>
       </c>
       <c r="E186" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F186" s="2" t="n">
         <v>23.45</v>
@@ -4976,7 +4980,7 @@
         </is>
       </c>
       <c r="E187" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>23.45</v>
@@ -5002,7 +5006,7 @@
         </is>
       </c>
       <c r="E188" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>23.45</v>
@@ -5028,7 +5032,7 @@
         </is>
       </c>
       <c r="E189" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>23.45</v>
@@ -5054,7 +5058,7 @@
         </is>
       </c>
       <c r="E190" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F190" s="2" t="n">
         <v>23.45</v>
@@ -5080,7 +5084,7 @@
         </is>
       </c>
       <c r="E191" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F191" s="2" t="n">
         <v>23.45</v>
@@ -5106,7 +5110,7 @@
         </is>
       </c>
       <c r="E192" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F192" s="2" t="n">
         <v>23.45</v>
@@ -5132,7 +5136,7 @@
         </is>
       </c>
       <c r="E193" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>23.45</v>
@@ -5158,7 +5162,7 @@
         </is>
       </c>
       <c r="E194" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F194" s="2" t="n">
         <v>23.45</v>
@@ -5184,7 +5188,7 @@
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F195" s="2" t="n">
         <v>23.45</v>
@@ -5210,7 +5214,7 @@
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F196" s="2" t="n">
         <v>23.45</v>
@@ -5236,7 +5240,7 @@
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F197" s="2" t="n">
         <v>23.45</v>
@@ -5262,7 +5266,7 @@
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F198" s="2" t="n">
         <v>23.45</v>
@@ -5288,7 +5292,7 @@
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F199" s="2" t="n">
         <v>23.45</v>
@@ -5314,7 +5318,7 @@
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>23.45</v>
@@ -5340,7 +5344,7 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>23.45</v>
@@ -5366,7 +5370,7 @@
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F202" s="2" t="n">
         <v>23.45</v>
@@ -5392,7 +5396,7 @@
         </is>
       </c>
       <c r="E203" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>23.45</v>
@@ -5418,7 +5422,7 @@
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>23.45</v>
@@ -5444,7 +5448,7 @@
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F205" s="2" t="n">
         <v>23.45</v>
@@ -5470,7 +5474,7 @@
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F206" s="2" t="n">
         <v>23.45</v>
@@ -5496,7 +5500,7 @@
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>23.45</v>
@@ -5522,7 +5526,7 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>23.45</v>
@@ -5548,7 +5552,7 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>23.45</v>
@@ -5574,7 +5578,7 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>23.45</v>
@@ -5600,7 +5604,7 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>23.45</v>
@@ -5626,7 +5630,7 @@
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>23.45</v>
@@ -5652,7 +5656,7 @@
         </is>
       </c>
       <c r="E213" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>23.45</v>
@@ -5678,7 +5682,7 @@
         </is>
       </c>
       <c r="E214" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>23.45</v>
@@ -5704,7 +5708,7 @@
         </is>
       </c>
       <c r="E215" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>23.45</v>
@@ -5730,7 +5734,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>44217.59855601852</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>23.45</v>
@@ -5756,7 +5760,7 @@
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>23.45</v>
@@ -5782,7 +5786,7 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>23.45</v>
@@ -5808,7 +5812,7 @@
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>23.45</v>
@@ -5834,7 +5838,7 @@
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F220" s="2" t="n">
         <v>23.45</v>
@@ -5860,7 +5864,7 @@
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F221" s="2" t="n">
         <v>23.45</v>
@@ -5886,7 +5890,7 @@
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F222" s="2" t="n">
         <v>23.45</v>
@@ -5912,7 +5916,7 @@
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F223" s="2" t="n">
         <v>23.45</v>
@@ -5938,7 +5942,7 @@
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>23.45</v>
@@ -5964,7 +5968,7 @@
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F225" s="2" t="n">
         <v>23.45</v>
@@ -5990,7 +5994,7 @@
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>23.45</v>
@@ -6016,7 +6020,7 @@
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F227" s="2" t="n">
         <v>23.45</v>
@@ -6042,7 +6046,7 @@
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F228" s="2" t="n">
         <v>23.45</v>
@@ -6068,7 +6072,7 @@
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F229" s="2" t="n">
         <v>23.45</v>
@@ -6094,7 +6098,7 @@
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F230" s="2" t="n">
         <v>23.45</v>
@@ -6120,7 +6124,7 @@
         </is>
       </c>
       <c r="E231" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>23.45</v>
@@ -6146,7 +6150,7 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F232" s="2" t="n">
         <v>23.45</v>
@@ -6172,7 +6176,7 @@
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436509259</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>23.45</v>
@@ -6198,7 +6202,7 @@
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F234" s="2" t="n">
         <v>23.45</v>
@@ -6224,7 +6228,7 @@
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>23.45</v>
@@ -6250,7 +6254,7 @@
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F236" s="2" t="n">
         <v>23.45</v>
@@ -6276,7 +6280,7 @@
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>23.45</v>
@@ -6302,7 +6306,7 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F238" s="2" t="n">
         <v>23.45</v>
@@ -6328,7 +6332,7 @@
         </is>
       </c>
       <c r="E239" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F239" s="2" t="n">
         <v>23.45</v>
@@ -6354,7 +6358,7 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F240" s="2" t="n">
         <v>23.45</v>
@@ -6380,7 +6384,7 @@
         </is>
       </c>
       <c r="E241" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>23.45</v>
@@ -6406,7 +6410,7 @@
         </is>
       </c>
       <c r="E242" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F242" s="2" t="n">
         <v>23.45</v>
@@ -6432,7 +6436,7 @@
         </is>
       </c>
       <c r="E243" s="2" t="n">
-        <v>44217.59855603009</v>
+        <v>44219.91436513889</v>
       </c>
       <c r="F243" s="2" t="n">
         <v>23.45</v>
@@ -6458,7 +6462,7 @@
         </is>
       </c>
       <c r="E244" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F244" s="2" t="n">
         <v>23.45</v>
@@ -6484,7 +6488,7 @@
         </is>
       </c>
       <c r="E245" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F245" s="2" t="n">
         <v>23.45</v>
@@ -6510,7 +6514,7 @@
         </is>
       </c>
       <c r="E246" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F246" s="2" t="n">
         <v>23.45</v>
@@ -6536,7 +6540,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>23.45</v>
@@ -6562,7 +6566,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F248" s="2" t="n">
         <v>23.45</v>
@@ -6588,7 +6592,7 @@
         </is>
       </c>
       <c r="E249" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F249" s="2" t="n">
         <v>23.45</v>
@@ -6614,7 +6618,7 @@
         </is>
       </c>
       <c r="E250" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F250" s="2" t="n">
         <v>23.45</v>
@@ -6640,7 +6644,7 @@
         </is>
       </c>
       <c r="E251" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>23.45</v>
@@ -6666,7 +6670,7 @@
         </is>
       </c>
       <c r="E252" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F252" s="2" t="n">
         <v>23.45</v>
@@ -6692,7 +6696,7 @@
         </is>
       </c>
       <c r="E253" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F253" s="2" t="n">
         <v>23.45</v>
@@ -6718,7 +6722,7 @@
         </is>
       </c>
       <c r="E254" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F254" s="2" t="n">
         <v>23.45</v>
@@ -6744,7 +6748,7 @@
         </is>
       </c>
       <c r="E255" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F255" s="2" t="n">
         <v>23.45</v>
@@ -6770,7 +6774,7 @@
         </is>
       </c>
       <c r="E256" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F256" s="2" t="n">
         <v>23.45</v>
@@ -6796,7 +6800,7 @@
         </is>
       </c>
       <c r="E257" s="2" t="n">
-        <v>44217.59855604167</v>
+        <v>44219.914365150464</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>23.45</v>
@@ -6822,7 +6826,7 @@
         </is>
       </c>
       <c r="E258" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F258" s="2" t="n">
         <v>23.45</v>
@@ -6848,7 +6852,7 @@
         </is>
       </c>
       <c r="E259" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F259" s="2" t="n">
         <v>23.45</v>
@@ -6874,7 +6878,7 @@
         </is>
       </c>
       <c r="E260" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F260" s="2" t="n">
         <v>23.45</v>
@@ -6900,7 +6904,7 @@
         </is>
       </c>
       <c r="E261" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F261" s="2" t="n">
         <v>23.45</v>
@@ -6926,7 +6930,7 @@
         </is>
       </c>
       <c r="E262" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F262" s="2" t="n">
         <v>23.45</v>
@@ -6952,7 +6956,7 @@
         </is>
       </c>
       <c r="E263" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F263" s="2" t="n">
         <v>23.45</v>
@@ -6978,7 +6982,7 @@
         </is>
       </c>
       <c r="E264" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>23.45</v>
@@ -7004,7 +7008,7 @@
         </is>
       </c>
       <c r="E265" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F265" s="2" t="n">
         <v>23.45</v>
@@ -7030,7 +7034,7 @@
         </is>
       </c>
       <c r="E266" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F266" s="2" t="n">
         <v>23.45</v>
@@ -7056,7 +7060,7 @@
         </is>
       </c>
       <c r="E267" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>23.45</v>
@@ -7082,7 +7086,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F268" s="2" t="n">
         <v>23.45</v>
@@ -7108,7 +7112,7 @@
         </is>
       </c>
       <c r="E269" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F269" s="2" t="n">
         <v>23.45</v>
@@ -7134,7 +7138,7 @@
         </is>
       </c>
       <c r="E270" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>23.45</v>
@@ -7160,7 +7164,7 @@
         </is>
       </c>
       <c r="E271" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>23.45</v>
@@ -7186,7 +7190,7 @@
         </is>
       </c>
       <c r="E272" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F272" s="2" t="n">
         <v>23.45</v>
@@ -7212,7 +7216,7 @@
         </is>
       </c>
       <c r="E273" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F273" s="2" t="n">
         <v>23.45</v>
@@ -7238,7 +7242,7 @@
         </is>
       </c>
       <c r="E274" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F274" s="2" t="n">
         <v>23.45</v>
@@ -7264,7 +7268,7 @@
         </is>
       </c>
       <c r="E275" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F275" s="2" t="n">
         <v>23.45</v>
@@ -7290,7 +7294,7 @@
         </is>
       </c>
       <c r="E276" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F276" s="2" t="n">
         <v>23.45</v>
@@ -7316,7 +7320,7 @@
         </is>
       </c>
       <c r="E277" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F277" s="2" t="n">
         <v>23.45</v>
@@ -7342,7 +7346,7 @@
         </is>
       </c>
       <c r="E278" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F278" s="2" t="n">
         <v>23.45</v>
@@ -7368,7 +7372,7 @@
         </is>
       </c>
       <c r="E279" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F279" s="2" t="n">
         <v>23.45</v>
@@ -7394,7 +7398,7 @@
         </is>
       </c>
       <c r="E280" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F280" s="2" t="n">
         <v>23.45</v>
@@ -7420,7 +7424,7 @@
         </is>
       </c>
       <c r="E281" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F281" s="2" t="n">
         <v>23.45</v>
@@ -7446,7 +7450,7 @@
         </is>
       </c>
       <c r="E282" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F282" s="2" t="n">
         <v>23.45</v>
@@ -7472,7 +7476,7 @@
         </is>
       </c>
       <c r="E283" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F283" s="2" t="n">
         <v>23.45</v>
@@ -7498,7 +7502,7 @@
         </is>
       </c>
       <c r="E284" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>23.45</v>
@@ -7524,7 +7528,7 @@
         </is>
       </c>
       <c r="E285" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F285" s="2" t="n">
         <v>23.45</v>
@@ -7550,7 +7554,7 @@
         </is>
       </c>
       <c r="E286" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F286" s="2" t="n">
         <v>23.45</v>
@@ -7576,7 +7580,7 @@
         </is>
       </c>
       <c r="E287" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F287" s="2" t="n">
         <v>23.45</v>
@@ -7602,7 +7606,7 @@
         </is>
       </c>
       <c r="E288" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F288" s="2" t="n">
         <v>23.45</v>
@@ -7628,7 +7632,7 @@
         </is>
       </c>
       <c r="E289" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F289" s="2" t="n">
         <v>23.45</v>
@@ -7654,7 +7658,7 @@
         </is>
       </c>
       <c r="E290" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F290" s="2" t="n">
         <v>23.45</v>
@@ -7680,7 +7684,7 @@
         </is>
       </c>
       <c r="E291" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F291" s="2" t="n">
         <v>23.45</v>
@@ -7706,7 +7710,7 @@
         </is>
       </c>
       <c r="E292" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F292" s="2" t="n">
         <v>23.45</v>
@@ -7732,7 +7736,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F293" s="2" t="n">
         <v>23.45</v>
@@ -7758,7 +7762,7 @@
         </is>
       </c>
       <c r="E294" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F294" s="2" t="n">
         <v>23.45</v>
@@ -7784,7 +7788,7 @@
         </is>
       </c>
       <c r="E295" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F295" s="2" t="n">
         <v>23.45</v>
@@ -7810,7 +7814,7 @@
         </is>
       </c>
       <c r="E296" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F296" s="2" t="n">
         <v>23.45</v>
@@ -7836,7 +7840,7 @@
         </is>
       </c>
       <c r="E297" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F297" s="2" t="n">
         <v>23.45</v>
@@ -7862,7 +7866,7 @@
         </is>
       </c>
       <c r="E298" s="2" t="n">
-        <v>44217.59855611111</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F298" s="2" t="n">
         <v>23.45</v>
@@ -7888,7 +7892,7 @@
         </is>
       </c>
       <c r="E299" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F299" s="2" t="n">
         <v>23.45</v>
@@ -7914,7 +7918,7 @@
         </is>
       </c>
       <c r="E300" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F300" s="2" t="n">
         <v>23.45</v>
@@ -7940,7 +7944,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F301" s="2" t="n">
         <v>23.45</v>
@@ -7966,7 +7970,7 @@
         </is>
       </c>
       <c r="E302" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F302" s="2" t="n">
         <v>23.45</v>
@@ -7992,7 +7996,7 @@
         </is>
       </c>
       <c r="E303" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F303" s="2" t="n">
         <v>23.45</v>
@@ -8018,7 +8022,7 @@
         </is>
       </c>
       <c r="E304" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F304" s="2" t="n">
         <v>23.45</v>
@@ -8044,7 +8048,7 @@
         </is>
       </c>
       <c r="E305" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F305" s="2" t="n">
         <v>23.45</v>
@@ -8070,7 +8074,7 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F306" s="2" t="n">
         <v>23.45</v>
@@ -8096,7 +8100,7 @@
         </is>
       </c>
       <c r="E307" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F307" s="2" t="n">
         <v>23.45</v>
@@ -8122,7 +8126,7 @@
         </is>
       </c>
       <c r="E308" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F308" s="2" t="n">
         <v>23.45</v>
@@ -8148,7 +8152,7 @@
         </is>
       </c>
       <c r="E309" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F309" s="2" t="n">
         <v>23.45</v>
@@ -8174,7 +8178,7 @@
         </is>
       </c>
       <c r="E310" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F310" s="2" t="n">
         <v>23.45</v>
@@ -8200,7 +8204,7 @@
         </is>
       </c>
       <c r="E311" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F311" s="2" t="n">
         <v>23.45</v>
@@ -8226,7 +8230,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>23.45</v>
@@ -8252,7 +8256,7 @@
         </is>
       </c>
       <c r="E313" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F313" s="2" t="n">
         <v>23.45</v>
@@ -8278,7 +8282,7 @@
         </is>
       </c>
       <c r="E314" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F314" s="2" t="n">
         <v>23.45</v>
@@ -8304,7 +8308,7 @@
         </is>
       </c>
       <c r="E315" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F315" s="2" t="n">
         <v>23.45</v>
@@ -8330,7 +8334,7 @@
         </is>
       </c>
       <c r="E316" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>23.45</v>
@@ -8356,7 +8360,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F317" s="2" t="n">
         <v>23.45</v>
@@ -8382,7 +8386,7 @@
         </is>
       </c>
       <c r="E318" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F318" s="2" t="n">
         <v>23.45</v>
@@ -8408,7 +8412,7 @@
         </is>
       </c>
       <c r="E319" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F319" s="2" t="n">
         <v>23.45</v>
@@ -8434,7 +8438,7 @@
         </is>
       </c>
       <c r="E320" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F320" s="2" t="n">
         <v>23.45</v>
@@ -8460,7 +8464,7 @@
         </is>
       </c>
       <c r="E321" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F321" s="2" t="n">
         <v>23.45</v>
@@ -8486,7 +8490,7 @@
         </is>
       </c>
       <c r="E322" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F322" s="2" t="n">
         <v>23.45</v>
@@ -8512,7 +8516,7 @@
         </is>
       </c>
       <c r="E323" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F323" s="2" t="n">
         <v>23.45</v>
@@ -8538,7 +8542,7 @@
         </is>
       </c>
       <c r="E324" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F324" s="2" t="n">
         <v>23.45</v>
@@ -8564,7 +8568,7 @@
         </is>
       </c>
       <c r="E325" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F325" s="2" t="n">
         <v>23.45</v>
@@ -8590,7 +8594,7 @@
         </is>
       </c>
       <c r="E326" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F326" s="2" t="n">
         <v>23.45</v>
@@ -8616,7 +8620,7 @@
         </is>
       </c>
       <c r="E327" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F327" s="2" t="n">
         <v>23.45</v>
@@ -8642,7 +8646,7 @@
         </is>
       </c>
       <c r="E328" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F328" s="2" t="n">
         <v>23.45</v>
@@ -8668,7 +8672,7 @@
         </is>
       </c>
       <c r="E329" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F329" s="2" t="n">
         <v>23.45</v>
@@ -8694,7 +8698,7 @@
         </is>
       </c>
       <c r="E330" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F330" s="2" t="n">
         <v>23.45</v>
@@ -8720,7 +8724,7 @@
         </is>
       </c>
       <c r="E331" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F331" s="2" t="n">
         <v>23.45</v>
@@ -8746,7 +8750,7 @@
         </is>
       </c>
       <c r="E332" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F332" s="2" t="n">
         <v>23.45</v>
@@ -8772,7 +8776,7 @@
         </is>
       </c>
       <c r="E333" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F333" s="2" t="n">
         <v>23.45</v>
@@ -8798,7 +8802,7 @@
         </is>
       </c>
       <c r="E334" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F334" s="2" t="n">
         <v>23.45</v>
@@ -8824,7 +8828,7 @@
         </is>
       </c>
       <c r="E335" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F335" s="2" t="n">
         <v>23.45</v>
@@ -8850,7 +8854,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F336" s="2" t="n">
         <v>23.45</v>
@@ -8876,7 +8880,7 @@
         </is>
       </c>
       <c r="E337" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F337" s="2" t="n">
         <v>23.45</v>
@@ -8902,7 +8906,7 @@
         </is>
       </c>
       <c r="E338" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F338" s="2" t="n">
         <v>23.45</v>
@@ -8928,7 +8932,7 @@
         </is>
       </c>
       <c r="E339" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F339" s="2" t="n">
         <v>23.45</v>
@@ -8954,7 +8958,7 @@
         </is>
       </c>
       <c r="E340" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F340" s="2" t="n">
         <v>23.45</v>
@@ -8980,7 +8984,7 @@
         </is>
       </c>
       <c r="E341" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F341" s="2" t="n">
         <v>23.45</v>
@@ -9006,7 +9010,7 @@
         </is>
       </c>
       <c r="E342" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F342" s="2" t="n">
         <v>23.45</v>
@@ -9032,7 +9036,7 @@
         </is>
       </c>
       <c r="E343" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F343" s="2" t="n">
         <v>23.45</v>
@@ -9058,7 +9062,7 @@
         </is>
       </c>
       <c r="E344" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F344" s="2" t="n">
         <v>23.45</v>
@@ -9084,7 +9088,7 @@
         </is>
       </c>
       <c r="E345" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.914365185185</v>
       </c>
       <c r="F345" s="2" t="n">
         <v>23.45</v>
@@ -9110,7 +9114,7 @@
         </is>
       </c>
       <c r="E346" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F346" s="2" t="n">
         <v>23.45</v>
@@ -9136,7 +9140,7 @@
         </is>
       </c>
       <c r="E347" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F347" s="2" t="n">
         <v>23.45</v>
@@ -9162,7 +9166,7 @@
         </is>
       </c>
       <c r="E348" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F348" s="2" t="n">
         <v>23.45</v>
@@ -9188,7 +9192,7 @@
         </is>
       </c>
       <c r="E349" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F349" s="2" t="n">
         <v>23.45</v>
@@ -9214,7 +9218,7 @@
         </is>
       </c>
       <c r="E350" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F350" s="2" t="n">
         <v>23.45</v>
@@ -9240,7 +9244,7 @@
         </is>
       </c>
       <c r="E351" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F351" s="2" t="n">
         <v>23.45</v>
@@ -9266,7 +9270,7 @@
         </is>
       </c>
       <c r="E352" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F352" s="2" t="n">
         <v>23.45</v>
@@ -9292,7 +9296,7 @@
         </is>
       </c>
       <c r="E353" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F353" s="2" t="n">
         <v>23.45</v>
@@ -9318,7 +9322,7 @@
         </is>
       </c>
       <c r="E354" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F354" s="2" t="n">
         <v>23.45</v>
@@ -9344,7 +9348,7 @@
         </is>
       </c>
       <c r="E355" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F355" s="2" t="n">
         <v>23.45</v>
@@ -9370,7 +9374,7 @@
         </is>
       </c>
       <c r="E356" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F356" s="2" t="n">
         <v>23.45</v>
@@ -9396,7 +9400,7 @@
         </is>
       </c>
       <c r="E357" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F357" s="2" t="n">
         <v>23.45</v>
@@ -9422,7 +9426,7 @@
         </is>
       </c>
       <c r="E358" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F358" s="2" t="n">
         <v>23.45</v>
@@ -9448,7 +9452,7 @@
         </is>
       </c>
       <c r="E359" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F359" s="2" t="n">
         <v>23.45</v>
@@ -9474,7 +9478,7 @@
         </is>
       </c>
       <c r="E360" s="2" t="n">
-        <v>44217.598556122684</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F360" s="2" t="n">
         <v>23.45</v>
@@ -9500,7 +9504,7 @@
         </is>
       </c>
       <c r="E361" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F361" s="2" t="n">
         <v>23.45</v>
@@ -9526,7 +9530,7 @@
         </is>
       </c>
       <c r="E362" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F362" s="2" t="n">
         <v>23.45</v>
@@ -9552,7 +9556,7 @@
         </is>
       </c>
       <c r="E363" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F363" s="2" t="n">
         <v>23.45</v>
@@ -9578,7 +9582,7 @@
         </is>
       </c>
       <c r="E364" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F364" s="2" t="n">
         <v>23.45</v>
@@ -9604,7 +9608,7 @@
         </is>
       </c>
       <c r="E365" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F365" s="2" t="n">
         <v>23.45</v>
@@ -9630,7 +9634,7 @@
         </is>
       </c>
       <c r="E366" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F366" s="2" t="n">
         <v>23.45</v>
@@ -9656,7 +9660,7 @@
         </is>
       </c>
       <c r="E367" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F367" s="2" t="n">
         <v>23.45</v>
@@ -9682,7 +9686,7 @@
         </is>
       </c>
       <c r="E368" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F368" s="2" t="n">
         <v>23.45</v>
@@ -9708,7 +9712,7 @@
         </is>
       </c>
       <c r="E369" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F369" s="2" t="n">
         <v>23.45</v>
@@ -9734,7 +9738,7 @@
         </is>
       </c>
       <c r="E370" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F370" s="2" t="n">
         <v>23.45</v>
@@ -9760,7 +9764,7 @@
         </is>
       </c>
       <c r="E371" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F371" s="2" t="n">
         <v>23.45</v>
@@ -9786,7 +9790,7 @@
         </is>
       </c>
       <c r="E372" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F372" s="2" t="n">
         <v>23.45</v>
@@ -9812,7 +9816,7 @@
         </is>
       </c>
       <c r="E373" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F373" s="2" t="n">
         <v>23.45</v>
@@ -9838,7 +9842,7 @@
         </is>
       </c>
       <c r="E374" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F374" s="2" t="n">
         <v>23.45</v>
@@ -9864,7 +9868,7 @@
         </is>
       </c>
       <c r="E375" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F375" s="2" t="n">
         <v>23.45</v>
@@ -9890,7 +9894,7 @@
         </is>
       </c>
       <c r="E376" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F376" s="2" t="n">
         <v>23.45</v>
@@ -9916,7 +9920,7 @@
         </is>
       </c>
       <c r="E377" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F377" s="2" t="n">
         <v>23.45</v>
@@ -9942,7 +9946,7 @@
         </is>
       </c>
       <c r="E378" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F378" s="2" t="n">
         <v>23.45</v>
@@ -9968,7 +9972,7 @@
         </is>
       </c>
       <c r="E379" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F379" s="2" t="n">
         <v>23.45</v>
@@ -9994,7 +9998,7 @@
         </is>
       </c>
       <c r="E380" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F380" s="2" t="n">
         <v>23.45</v>
@@ -10020,7 +10024,7 @@
         </is>
       </c>
       <c r="E381" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F381" s="2" t="n">
         <v>23.45</v>
@@ -10046,7 +10050,7 @@
         </is>
       </c>
       <c r="E382" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F382" s="2" t="n">
         <v>23.45</v>
@@ -10072,7 +10076,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F383" s="2" t="n">
         <v>23.45</v>
@@ -10098,7 +10102,7 @@
         </is>
       </c>
       <c r="E384" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F384" s="2" t="n">
         <v>23.45</v>
@@ -10124,7 +10128,7 @@
         </is>
       </c>
       <c r="E385" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F385" s="2" t="n">
         <v>23.45</v>
@@ -10150,7 +10154,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F386" s="2" t="n">
         <v>23.45</v>
@@ -10176,7 +10180,7 @@
         </is>
       </c>
       <c r="E387" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F387" s="2" t="n">
         <v>23.45</v>
@@ -10202,7 +10206,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F388" s="2" t="n">
         <v>23.45</v>
@@ -10228,7 +10232,7 @@
         </is>
       </c>
       <c r="E389" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F389" s="2" t="n">
         <v>23.45</v>
@@ -10254,7 +10258,7 @@
         </is>
       </c>
       <c r="E390" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F390" s="2" t="n">
         <v>23.45</v>
@@ -10280,7 +10284,7 @@
         </is>
       </c>
       <c r="E391" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F391" s="2" t="n">
         <v>23.45</v>
@@ -10306,7 +10310,7 @@
         </is>
       </c>
       <c r="E392" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F392" s="2" t="n">
         <v>23.45</v>
@@ -10332,7 +10336,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F393" s="2" t="n">
         <v>23.45</v>
@@ -10358,7 +10362,7 @@
         </is>
       </c>
       <c r="E394" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F394" s="2" t="n">
         <v>23.45</v>
@@ -10384,7 +10388,7 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F395" s="2" t="n">
         <v>23.45</v>
@@ -10410,7 +10414,7 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F396" s="2" t="n">
         <v>23.45</v>
@@ -10436,7 +10440,7 @@
         </is>
       </c>
       <c r="E397" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F397" s="2" t="n">
         <v>23.45</v>
@@ -10462,7 +10466,7 @@
         </is>
       </c>
       <c r="E398" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F398" s="2" t="n">
         <v>23.45</v>
@@ -10488,7 +10492,7 @@
         </is>
       </c>
       <c r="E399" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F399" s="2" t="n">
         <v>23.45</v>
@@ -10514,7 +10518,7 @@
         </is>
       </c>
       <c r="E400" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F400" s="2" t="n">
         <v>23.45</v>
@@ -10540,7 +10544,7 @@
         </is>
       </c>
       <c r="E401" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F401" s="2" t="n">
         <v>23.45</v>
@@ -10566,7 +10570,7 @@
         </is>
       </c>
       <c r="E402" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F402" s="2" t="n">
         <v>23.45</v>
@@ -10592,7 +10596,7 @@
         </is>
       </c>
       <c r="E403" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F403" s="2" t="n">
         <v>23.45</v>
@@ -10618,7 +10622,7 @@
         </is>
       </c>
       <c r="E404" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F404" s="2" t="n">
         <v>23.45</v>
@@ -10644,7 +10648,7 @@
         </is>
       </c>
       <c r="E405" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F405" s="2" t="n">
         <v>23.45</v>
@@ -10670,7 +10674,7 @@
         </is>
       </c>
       <c r="E406" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F406" s="2" t="n">
         <v>23.45</v>
@@ -10696,7 +10700,7 @@
         </is>
       </c>
       <c r="E407" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F407" s="2" t="n">
         <v>23.45</v>
@@ -10722,7 +10726,7 @@
         </is>
       </c>
       <c r="E408" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F408" s="2" t="n">
         <v>23.45</v>
@@ -10748,7 +10752,7 @@
         </is>
       </c>
       <c r="E409" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F409" s="2" t="n">
         <v>23.45</v>
@@ -10774,7 +10778,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F410" s="2" t="n">
         <v>23.45</v>
@@ -10800,7 +10804,7 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F411" s="2" t="n">
         <v>23.45</v>
@@ -10826,7 +10830,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F412" s="2" t="n">
         <v>23.45</v>
@@ -10852,7 +10856,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F413" s="2" t="n">
         <v>23.45</v>
@@ -10878,7 +10882,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F414" s="2" t="n">
         <v>23.45</v>
@@ -10904,7 +10908,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F415" s="2" t="n">
         <v>23.45</v>
@@ -10930,7 +10934,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F416" s="2" t="n">
         <v>23.45</v>
@@ -10956,7 +10960,7 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F417" s="2" t="n">
         <v>23.45</v>
@@ -10982,7 +10986,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F418" s="2" t="n">
         <v>23.45</v>
@@ -11008,7 +11012,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F419" s="2" t="n">
         <v>23.45</v>
@@ -11034,7 +11038,7 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F420" s="2" t="n">
         <v>23.45</v>
@@ -11060,7 +11064,7 @@
         </is>
       </c>
       <c r="E421" s="2" t="n">
-        <v>44217.59855613426</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F421" s="2" t="n">
         <v>23.45</v>
@@ -11086,7 +11090,7 @@
         </is>
       </c>
       <c r="E422" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F422" s="2" t="n">
         <v>23.45</v>
@@ -11112,7 +11116,7 @@
         </is>
       </c>
       <c r="E423" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F423" s="2" t="n">
         <v>23.45</v>
@@ -11138,7 +11142,7 @@
         </is>
       </c>
       <c r="E424" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F424" s="2" t="n">
         <v>23.45</v>
@@ -11164,7 +11168,7 @@
         </is>
       </c>
       <c r="E425" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F425" s="2" t="n">
         <v>23.45</v>
@@ -11190,7 +11194,7 @@
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F426" s="2" t="n">
         <v>23.45</v>
@@ -11216,7 +11220,7 @@
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F427" s="2" t="n">
         <v>23.45</v>
@@ -11242,7 +11246,7 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F428" s="2" t="n">
         <v>23.45</v>
@@ -11268,7 +11272,7 @@
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F429" s="2" t="n">
         <v>23.45</v>
@@ -11294,7 +11298,7 @@
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F430" s="2" t="n">
         <v>23.45</v>
@@ -11320,7 +11324,7 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F431" s="2" t="n">
         <v>23.45</v>
@@ -11346,7 +11350,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>23.45</v>
@@ -11372,7 +11376,7 @@
         </is>
       </c>
       <c r="E433" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F433" s="2" t="n">
         <v>23.45</v>
@@ -11398,7 +11402,7 @@
         </is>
       </c>
       <c r="E434" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F434" s="2" t="n">
         <v>23.45</v>
@@ -11424,7 +11428,7 @@
         </is>
       </c>
       <c r="E435" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F435" s="2" t="n">
         <v>23.45</v>
@@ -11450,7 +11454,7 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F436" s="2" t="n">
         <v>23.45</v>
@@ -11476,7 +11480,7 @@
         </is>
       </c>
       <c r="E437" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F437" s="2" t="n">
         <v>23.45</v>
@@ -11502,7 +11506,7 @@
         </is>
       </c>
       <c r="E438" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F438" s="2" t="n">
         <v>23.45</v>
@@ -11528,7 +11532,7 @@
         </is>
       </c>
       <c r="E439" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F439" s="2" t="n">
         <v>23.45</v>
@@ -11554,7 +11558,7 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436519676</v>
       </c>
       <c r="F440" s="2" t="n">
         <v>23.45</v>
@@ -11580,7 +11584,7 @@
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F441" s="2" t="n">
         <v>23.45</v>
@@ -11606,7 +11610,7 @@
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F442" s="2" t="n">
         <v>23.45</v>
@@ -11632,7 +11636,7 @@
         </is>
       </c>
       <c r="E443" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F443" s="2" t="n">
         <v>23.45</v>
@@ -11658,7 +11662,7 @@
         </is>
       </c>
       <c r="E444" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F444" s="2" t="n">
         <v>23.45</v>
@@ -11684,7 +11688,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F445" s="2" t="n">
         <v>23.45</v>
@@ -11710,7 +11714,7 @@
         </is>
       </c>
       <c r="E446" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F446" s="2" t="n">
         <v>23.45</v>
@@ -11736,7 +11740,7 @@
         </is>
       </c>
       <c r="E447" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F447" s="2" t="n">
         <v>23.45</v>
@@ -11762,7 +11766,7 @@
         </is>
       </c>
       <c r="E448" s="2" t="n">
-        <v>44217.59855614584</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F448" s="2" t="n">
         <v>23.45</v>
@@ -11788,7 +11792,7 @@
         </is>
       </c>
       <c r="E449" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F449" s="2" t="n">
         <v>23.45</v>
@@ -11814,7 +11818,7 @@
         </is>
       </c>
       <c r="E450" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F450" s="2" t="n">
         <v>23.45</v>
@@ -11840,7 +11844,7 @@
         </is>
       </c>
       <c r="E451" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F451" s="2" t="n">
         <v>23.45</v>
@@ -11866,7 +11870,7 @@
         </is>
       </c>
       <c r="E452" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F452" s="2" t="n">
         <v>23.45</v>
@@ -11892,7 +11896,7 @@
         </is>
       </c>
       <c r="E453" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F453" s="2" t="n">
         <v>23.45</v>
@@ -11918,7 +11922,7 @@
         </is>
       </c>
       <c r="E454" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F454" s="2" t="n">
         <v>23.45</v>
@@ -11944,7 +11948,7 @@
         </is>
       </c>
       <c r="E455" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F455" s="2" t="n">
         <v>23.45</v>
@@ -11970,7 +11974,7 @@
         </is>
       </c>
       <c r="E456" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F456" s="2" t="n">
         <v>23.45</v>
@@ -11996,7 +12000,7 @@
         </is>
       </c>
       <c r="E457" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F457" s="2" t="n">
         <v>23.45</v>
@@ -12022,7 +12026,7 @@
         </is>
       </c>
       <c r="E458" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F458" s="2" t="n">
         <v>23.45</v>
@@ -12048,7 +12052,7 @@
         </is>
       </c>
       <c r="E459" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F459" s="2" t="n">
         <v>23.45</v>
@@ -12074,7 +12078,7 @@
         </is>
       </c>
       <c r="E460" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F460" s="2" t="n">
         <v>23.45</v>
@@ -12100,7 +12104,7 @@
         </is>
       </c>
       <c r="E461" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F461" s="2" t="n">
         <v>23.45</v>
@@ -12126,7 +12130,7 @@
         </is>
       </c>
       <c r="E462" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F462" s="2" t="n">
         <v>23.45</v>
@@ -12152,7 +12156,7 @@
         </is>
       </c>
       <c r="E463" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F463" s="2" t="n">
         <v>23.45</v>
@@ -12178,7 +12182,7 @@
         </is>
       </c>
       <c r="E464" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F464" s="2" t="n">
         <v>23.45</v>
@@ -12204,7 +12208,7 @@
         </is>
       </c>
       <c r="E465" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F465" s="2" t="n">
         <v>23.45</v>
@@ -12230,7 +12234,7 @@
         </is>
       </c>
       <c r="E466" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F466" s="2" t="n">
         <v>23.45</v>
@@ -12256,7 +12260,7 @@
         </is>
       </c>
       <c r="E467" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F467" s="2" t="n">
         <v>23.45</v>
@@ -12282,7 +12286,7 @@
         </is>
       </c>
       <c r="E468" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F468" s="2" t="n">
         <v>23.45</v>
@@ -12308,7 +12312,7 @@
         </is>
       </c>
       <c r="E469" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F469" s="2" t="n">
         <v>23.45</v>
@@ -12334,7 +12338,7 @@
         </is>
       </c>
       <c r="E470" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F470" s="2" t="n">
         <v>23.45</v>
@@ -12360,7 +12364,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>23.45</v>
@@ -12386,7 +12390,7 @@
         </is>
       </c>
       <c r="E472" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F472" s="2" t="n">
         <v>23.45</v>
@@ -12412,7 +12416,7 @@
         </is>
       </c>
       <c r="E473" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F473" s="2" t="n">
         <v>23.45</v>
@@ -12438,7 +12442,7 @@
         </is>
       </c>
       <c r="E474" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F474" s="2" t="n">
         <v>23.45</v>
@@ -12464,7 +12468,7 @@
         </is>
       </c>
       <c r="E475" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F475" s="2" t="n">
         <v>23.45</v>
@@ -12490,7 +12494,7 @@
         </is>
       </c>
       <c r="E476" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F476" s="2" t="n">
         <v>23.45</v>
@@ -12516,7 +12520,7 @@
         </is>
       </c>
       <c r="E477" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F477" s="2" t="n">
         <v>23.45</v>
@@ -12542,7 +12546,7 @@
         </is>
       </c>
       <c r="E478" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F478" s="2" t="n">
         <v>23.45</v>
@@ -12568,7 +12572,7 @@
         </is>
       </c>
       <c r="E479" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F479" s="2" t="n">
         <v>23.45</v>
@@ -12594,7 +12598,7 @@
         </is>
       </c>
       <c r="E480" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F480" s="2" t="n">
         <v>23.45</v>
@@ -12620,7 +12624,7 @@
         </is>
       </c>
       <c r="E481" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F481" s="2" t="n">
         <v>23.45</v>
@@ -12646,7 +12650,7 @@
         </is>
       </c>
       <c r="E482" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F482" s="2" t="n">
         <v>23.45</v>
@@ -12672,7 +12676,7 @@
         </is>
       </c>
       <c r="E483" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F483" s="2" t="n">
         <v>23.45</v>
@@ -12698,7 +12702,7 @@
         </is>
       </c>
       <c r="E484" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F484" s="2" t="n">
         <v>23.45</v>
@@ -12724,7 +12728,7 @@
         </is>
       </c>
       <c r="E485" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F485" s="2" t="n">
         <v>23.45</v>
@@ -12750,7 +12754,7 @@
         </is>
       </c>
       <c r="E486" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F486" s="2" t="n">
         <v>23.45</v>
@@ -12776,7 +12780,7 @@
         </is>
       </c>
       <c r="E487" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F487" s="2" t="n">
         <v>23.45</v>
@@ -12802,7 +12806,7 @@
         </is>
       </c>
       <c r="E488" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F488" s="2" t="n">
         <v>23.45</v>
@@ -12828,7 +12832,7 @@
         </is>
       </c>
       <c r="E489" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F489" s="2" t="n">
         <v>23.45</v>
@@ -12854,7 +12858,7 @@
         </is>
       </c>
       <c r="E490" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F490" s="2" t="n">
         <v>23.45</v>
@@ -12880,7 +12884,7 @@
         </is>
       </c>
       <c r="E491" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F491" s="2" t="n">
         <v>23.45</v>
@@ -12906,7 +12910,7 @@
         </is>
       </c>
       <c r="E492" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F492" s="2" t="n">
         <v>23.45</v>
@@ -12932,7 +12936,7 @@
         </is>
       </c>
       <c r="E493" s="2" t="n">
-        <v>44217.598556157405</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F493" s="2" t="n">
         <v>23.45</v>
@@ -12958,7 +12962,7 @@
         </is>
       </c>
       <c r="E494" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F494" s="2" t="n">
         <v>23.45</v>
@@ -12984,7 +12988,7 @@
         </is>
       </c>
       <c r="E495" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F495" s="2" t="n">
         <v>23.45</v>
@@ -13010,7 +13014,7 @@
         </is>
       </c>
       <c r="E496" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F496" s="2" t="n">
         <v>23.45</v>
@@ -13036,7 +13040,7 @@
         </is>
       </c>
       <c r="E497" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F497" s="2" t="n">
         <v>23.45</v>
@@ -13062,7 +13066,7 @@
         </is>
       </c>
       <c r="E498" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F498" s="2" t="n">
         <v>23.45</v>
@@ -13088,7 +13092,7 @@
         </is>
       </c>
       <c r="E499" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F499" s="2" t="n">
         <v>23.45</v>
@@ -13114,7 +13118,7 @@
         </is>
       </c>
       <c r="E500" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F500" s="2" t="n">
         <v>23.45</v>
@@ -13140,7 +13144,7 @@
         </is>
       </c>
       <c r="E501" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F501" s="2" t="n">
         <v>23.45</v>
@@ -13166,7 +13170,7 @@
         </is>
       </c>
       <c r="E502" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F502" s="2" t="n">
         <v>23.45</v>
@@ -13192,7 +13196,7 @@
         </is>
       </c>
       <c r="E503" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F503" s="2" t="n">
         <v>23.45</v>
@@ -13218,7 +13222,7 @@
         </is>
       </c>
       <c r="E504" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F504" s="2" t="n">
         <v>23.45</v>
@@ -13244,7 +13248,7 @@
         </is>
       </c>
       <c r="E505" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F505" s="2" t="n">
         <v>23.45</v>
@@ -13270,7 +13274,7 @@
         </is>
       </c>
       <c r="E506" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F506" s="2" t="n">
         <v>23.45</v>
@@ -13296,7 +13300,7 @@
         </is>
       </c>
       <c r="E507" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F507" s="2" t="n">
         <v>23.45</v>
@@ -13322,7 +13326,7 @@
         </is>
       </c>
       <c r="E508" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F508" s="2" t="n">
         <v>23.45</v>
@@ -13348,7 +13352,7 @@
         </is>
       </c>
       <c r="E509" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F509" s="2" t="n">
         <v>23.45</v>
@@ -13374,7 +13378,7 @@
         </is>
       </c>
       <c r="E510" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F510" s="2" t="n">
         <v>23.45</v>
@@ -13400,7 +13404,7 @@
         </is>
       </c>
       <c r="E511" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F511" s="2" t="n">
         <v>23.45</v>
@@ -13426,7 +13430,7 @@
         </is>
       </c>
       <c r="E512" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F512" s="2" t="n">
         <v>23.45</v>
@@ -13452,7 +13456,7 @@
         </is>
       </c>
       <c r="E513" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F513" s="2" t="n">
         <v>23.45</v>
@@ -13478,7 +13482,7 @@
         </is>
       </c>
       <c r="E514" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.91436520834</v>
       </c>
       <c r="F514" s="2" t="n">
         <v>23.45</v>
@@ -13504,7 +13508,7 @@
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F515" s="2" t="n">
         <v>23.45</v>
@@ -13530,7 +13534,7 @@
         </is>
       </c>
       <c r="E516" s="2" t="n">
-        <v>44217.59855616898</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F516" s="2" t="n">
         <v>23.45</v>
@@ -13556,7 +13560,7 @@
         </is>
       </c>
       <c r="E517" s="2" t="n">
-        <v>44217.59855618056</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F517" s="2" t="n">
         <v>23.45</v>
@@ -13582,7 +13586,7 @@
         </is>
       </c>
       <c r="E518" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F518" s="2" t="n">
         <v>23.45</v>
@@ -13608,7 +13612,7 @@
         </is>
       </c>
       <c r="E519" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F519" s="2" t="n">
         <v>23.45</v>
@@ -13634,7 +13638,7 @@
         </is>
       </c>
       <c r="E520" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F520" s="2" t="n">
         <v>23.45</v>
@@ -13660,7 +13664,7 @@
         </is>
       </c>
       <c r="E521" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F521" s="2" t="n">
         <v>23.45</v>
@@ -13686,7 +13690,7 @@
         </is>
       </c>
       <c r="E522" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F522" s="2" t="n">
         <v>23.45</v>
@@ -13712,7 +13716,7 @@
         </is>
       </c>
       <c r="E523" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F523" s="2" t="n">
         <v>23.45</v>
@@ -13738,7 +13742,7 @@
         </is>
       </c>
       <c r="E524" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F524" s="2" t="n">
         <v>23.45</v>
@@ -13764,7 +13768,7 @@
         </is>
       </c>
       <c r="E525" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F525" s="2" t="n">
         <v>23.45</v>
@@ -13790,7 +13794,7 @@
         </is>
       </c>
       <c r="E526" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F526" s="2" t="n">
         <v>23.45</v>
@@ -13816,7 +13820,7 @@
         </is>
       </c>
       <c r="E527" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F527" s="2" t="n">
         <v>23.45</v>
@@ -13842,7 +13846,7 @@
         </is>
       </c>
       <c r="E528" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F528" s="2" t="n">
         <v>23.45</v>
@@ -13868,7 +13872,7 @@
         </is>
       </c>
       <c r="E529" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F529" s="2" t="n">
         <v>23.45</v>
@@ -13894,7 +13898,7 @@
         </is>
       </c>
       <c r="E530" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F530" s="2" t="n">
         <v>23.45</v>
@@ -13920,7 +13924,7 @@
         </is>
       </c>
       <c r="E531" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F531" s="2" t="n">
         <v>23.45</v>
@@ -13946,7 +13950,7 @@
         </is>
       </c>
       <c r="E532" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F532" s="2" t="n">
         <v>23.45</v>
@@ -13972,7 +13976,7 @@
         </is>
       </c>
       <c r="E533" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F533" s="2" t="n">
         <v>23.45</v>
@@ -13998,7 +14002,7 @@
         </is>
       </c>
       <c r="E534" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F534" s="2" t="n">
         <v>23.45</v>
@@ -14024,7 +14028,7 @@
         </is>
       </c>
       <c r="E535" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F535" s="2" t="n">
         <v>23.45</v>
@@ -14050,7 +14054,7 @@
         </is>
       </c>
       <c r="E536" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F536" s="2" t="n">
         <v>23.45</v>
@@ -14076,7 +14080,7 @@
         </is>
       </c>
       <c r="E537" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F537" s="2" t="n">
         <v>23.45</v>
@@ -14102,7 +14106,7 @@
         </is>
       </c>
       <c r="E538" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F538" s="2" t="n">
         <v>23.45</v>
@@ -14128,7 +14132,7 @@
         </is>
       </c>
       <c r="E539" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F539" s="2" t="n">
         <v>23.45</v>
@@ -14154,7 +14158,7 @@
         </is>
       </c>
       <c r="E540" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F540" s="2" t="n">
         <v>23.45</v>
@@ -14180,7 +14184,7 @@
         </is>
       </c>
       <c r="E541" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F541" s="2" t="n">
         <v>23.45</v>
@@ -14206,7 +14210,7 @@
         </is>
       </c>
       <c r="E542" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F542" s="2" t="n">
         <v>23.45</v>
@@ -14232,7 +14236,7 @@
         </is>
       </c>
       <c r="E543" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F543" s="2" t="n">
         <v>23.45</v>
@@ -14258,7 +14262,7 @@
         </is>
       </c>
       <c r="E544" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F544" s="2" t="n">
         <v>23.45</v>
@@ -14284,7 +14288,7 @@
         </is>
       </c>
       <c r="E545" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F545" s="2" t="n">
         <v>23.45</v>
@@ -14310,7 +14314,7 @@
         </is>
       </c>
       <c r="E546" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F546" s="2" t="n">
         <v>23.45</v>
@@ -14336,7 +14340,7 @@
         </is>
       </c>
       <c r="E547" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F547" s="2" t="n">
         <v>23.45</v>
@@ -14362,7 +14366,7 @@
         </is>
       </c>
       <c r="E548" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F548" s="2" t="n">
         <v>23.45</v>
@@ -14388,7 +14392,7 @@
         </is>
       </c>
       <c r="E549" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F549" s="2" t="n">
         <v>23.45</v>
@@ -14414,7 +14418,7 @@
         </is>
       </c>
       <c r="E550" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F550" s="2" t="n">
         <v>23.45</v>
@@ -14440,7 +14444,7 @@
         </is>
       </c>
       <c r="E551" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F551" s="2" t="n">
         <v>23.45</v>
@@ -14466,7 +14470,7 @@
         </is>
       </c>
       <c r="E552" s="2" t="n">
-        <v>44217.5985562037</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F552" s="2" t="n">
         <v>23.45</v>
@@ -14492,7 +14496,7 @@
         </is>
       </c>
       <c r="E553" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F553" s="2" t="n">
         <v>23.45</v>
@@ -14518,7 +14522,7 @@
         </is>
       </c>
       <c r="E554" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F554" s="2" t="n">
         <v>23.45</v>
@@ -14544,7 +14548,7 @@
         </is>
       </c>
       <c r="E555" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F555" s="2" t="n">
         <v>23.45</v>
@@ -14570,7 +14574,7 @@
         </is>
       </c>
       <c r="E556" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F556" s="2" t="n">
         <v>23.45</v>
@@ -14596,7 +14600,7 @@
         </is>
       </c>
       <c r="E557" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F557" s="2" t="n">
         <v>23.45</v>
@@ -14622,7 +14626,7 @@
         </is>
       </c>
       <c r="E558" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F558" s="2" t="n">
         <v>23.45</v>
@@ -14648,7 +14652,7 @@
         </is>
       </c>
       <c r="E559" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F559" s="2" t="n">
         <v>23.45</v>
@@ -14674,7 +14678,7 @@
         </is>
       </c>
       <c r="E560" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F560" s="2" t="n">
         <v>23.45</v>
@@ -14700,7 +14704,7 @@
         </is>
       </c>
       <c r="E561" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F561" s="2" t="n">
         <v>23.45</v>
@@ -14726,7 +14730,7 @@
         </is>
       </c>
       <c r="E562" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F562" s="2" t="n">
         <v>23.45</v>
@@ -14752,7 +14756,7 @@
         </is>
       </c>
       <c r="E563" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F563" s="2" t="n">
         <v>23.45</v>
@@ -14778,7 +14782,7 @@
         </is>
       </c>
       <c r="E564" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F564" s="2" t="n">
         <v>23.45</v>
@@ -14804,7 +14808,7 @@
         </is>
       </c>
       <c r="E565" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F565" s="2" t="n">
         <v>23.45</v>
@@ -14830,7 +14834,7 @@
         </is>
       </c>
       <c r="E566" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F566" s="2" t="n">
         <v>23.45</v>
@@ -14856,7 +14860,7 @@
         </is>
       </c>
       <c r="E567" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F567" s="2" t="n">
         <v>23.45</v>
@@ -14882,7 +14886,7 @@
         </is>
       </c>
       <c r="E568" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F568" s="2" t="n">
         <v>23.45</v>
@@ -14908,7 +14912,7 @@
         </is>
       </c>
       <c r="E569" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F569" s="2" t="n">
         <v>23.45</v>
@@ -14934,7 +14938,7 @@
         </is>
       </c>
       <c r="E570" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F570" s="2" t="n">
         <v>23.45</v>
@@ -14960,7 +14964,7 @@
         </is>
       </c>
       <c r="E571" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F571" s="2" t="n">
         <v>23.45</v>
@@ -14986,7 +14990,7 @@
         </is>
       </c>
       <c r="E572" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F572" s="2" t="n">
         <v>23.45</v>
@@ -15012,7 +15016,7 @@
         </is>
       </c>
       <c r="E573" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F573" s="2" t="n">
         <v>23.45</v>
@@ -15038,7 +15042,7 @@
         </is>
       </c>
       <c r="E574" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F574" s="2" t="n">
         <v>23.45</v>
@@ -15064,7 +15068,7 @@
         </is>
       </c>
       <c r="E575" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F575" s="2" t="n">
         <v>23.45</v>
@@ -15090,7 +15094,7 @@
         </is>
       </c>
       <c r="E576" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F576" s="2" t="n">
         <v>23.45</v>
@@ -15116,7 +15120,7 @@
         </is>
       </c>
       <c r="E577" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F577" s="2" t="n">
         <v>23.45</v>
@@ -15142,7 +15146,7 @@
         </is>
       </c>
       <c r="E578" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F578" s="2" t="n">
         <v>23.45</v>
@@ -15168,7 +15172,7 @@
         </is>
       </c>
       <c r="E579" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F579" s="2" t="n">
         <v>23.45</v>
@@ -15194,7 +15198,7 @@
         </is>
       </c>
       <c r="E580" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F580" s="2" t="n">
         <v>23.45</v>
@@ -15220,7 +15224,7 @@
         </is>
       </c>
       <c r="E581" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F581" s="2" t="n">
         <v>23.45</v>
@@ -15246,7 +15250,7 @@
         </is>
       </c>
       <c r="E582" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F582" s="2" t="n">
         <v>23.45</v>
@@ -15272,7 +15276,7 @@
         </is>
       </c>
       <c r="E583" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F583" s="2" t="n">
         <v>23.45</v>
@@ -15298,7 +15302,7 @@
         </is>
       </c>
       <c r="E584" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F584" s="2" t="n">
         <v>23.45</v>
@@ -15324,7 +15328,7 @@
         </is>
       </c>
       <c r="E585" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F585" s="2" t="n">
         <v>23.45</v>
@@ -15350,7 +15354,7 @@
         </is>
       </c>
       <c r="E586" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F586" s="2" t="n">
         <v>23.45</v>
@@ -15376,7 +15380,7 @@
         </is>
       </c>
       <c r="E587" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F587" s="2" t="n">
         <v>23.45</v>
@@ -15402,7 +15406,7 @@
         </is>
       </c>
       <c r="E588" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F588" s="2" t="n">
         <v>23.45</v>
@@ -15428,7 +15432,7 @@
         </is>
       </c>
       <c r="E589" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F589" s="2" t="n">
         <v>23.45</v>
@@ -15454,7 +15458,7 @@
         </is>
       </c>
       <c r="E590" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F590" s="2" t="n">
         <v>23.45</v>
@@ -15480,7 +15484,7 @@
         </is>
       </c>
       <c r="E591" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F591" s="2" t="n">
         <v>23.45</v>
@@ -15506,7 +15510,7 @@
         </is>
       </c>
       <c r="E592" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F592" s="2" t="n">
         <v>23.45</v>
@@ -15532,7 +15536,7 @@
         </is>
       </c>
       <c r="E593" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.914365219905</v>
       </c>
       <c r="F593" s="2" t="n">
         <v>23.45</v>
@@ -15558,7 +15562,7 @@
         </is>
       </c>
       <c r="E594" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F594" s="2" t="n">
         <v>23.45</v>
@@ -15584,7 +15588,7 @@
         </is>
       </c>
       <c r="E595" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F595" s="2" t="n">
         <v>23.45</v>
@@ -15610,7 +15614,7 @@
         </is>
       </c>
       <c r="E596" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F596" s="2" t="n">
         <v>23.45</v>
@@ -15636,7 +15640,7 @@
         </is>
       </c>
       <c r="E597" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F597" s="2" t="n">
         <v>23.45</v>
@@ -15662,7 +15666,7 @@
         </is>
       </c>
       <c r="E598" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F598" s="2" t="n">
         <v>23.45</v>
@@ -15688,7 +15692,7 @@
         </is>
       </c>
       <c r="E599" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F599" s="2" t="n">
         <v>23.45</v>
@@ -15714,7 +15718,7 @@
         </is>
       </c>
       <c r="E600" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F600" s="2" t="n">
         <v>23.45</v>
@@ -15740,7 +15744,7 @@
         </is>
       </c>
       <c r="E601" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F601" s="2" t="n">
         <v>23.45</v>
@@ -15766,7 +15770,7 @@
         </is>
       </c>
       <c r="E602" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F602" s="2" t="n">
         <v>23.45</v>
@@ -15792,7 +15796,7 @@
         </is>
       </c>
       <c r="E603" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F603" s="2" t="n">
         <v>23.45</v>
@@ -15818,7 +15822,7 @@
         </is>
       </c>
       <c r="E604" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F604" s="2" t="n">
         <v>23.45</v>
@@ -15844,7 +15848,7 @@
         </is>
       </c>
       <c r="E605" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F605" s="2" t="n">
         <v>23.45</v>
@@ -15870,7 +15874,7 @@
         </is>
       </c>
       <c r="E606" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F606" s="2" t="n">
         <v>23.45</v>
@@ -15896,7 +15900,7 @@
         </is>
       </c>
       <c r="E607" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F607" s="2" t="n">
         <v>23.45</v>
@@ -15922,7 +15926,7 @@
         </is>
       </c>
       <c r="E608" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F608" s="2" t="n">
         <v>23.45</v>
@@ -15948,7 +15952,7 @@
         </is>
       </c>
       <c r="E609" s="2" t="n">
-        <v>44217.59855621528</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F609" s="2" t="n">
         <v>23.45</v>
@@ -15974,7 +15978,7 @@
         </is>
       </c>
       <c r="E610" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F610" s="2" t="n">
         <v>23.45</v>
@@ -16000,7 +16004,7 @@
         </is>
       </c>
       <c r="E611" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F611" s="2" t="n">
         <v>23.45</v>
@@ -16026,7 +16030,7 @@
         </is>
       </c>
       <c r="E612" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F612" s="2" t="n">
         <v>23.45</v>
@@ -16052,7 +16056,7 @@
         </is>
       </c>
       <c r="E613" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F613" s="2" t="n">
         <v>23.45</v>
@@ -16078,7 +16082,7 @@
         </is>
       </c>
       <c r="E614" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F614" s="2" t="n">
         <v>23.45</v>
@@ -16104,7 +16108,7 @@
         </is>
       </c>
       <c r="E615" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F615" s="2" t="n">
         <v>23.45</v>
@@ -16130,7 +16134,7 @@
         </is>
       </c>
       <c r="E616" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F616" s="2" t="n">
         <v>23.45</v>
@@ -16156,7 +16160,7 @@
         </is>
       </c>
       <c r="E617" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F617" s="2" t="n">
         <v>23.45</v>
@@ -16182,7 +16186,7 @@
         </is>
       </c>
       <c r="E618" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F618" s="2" t="n">
         <v>23.45</v>
@@ -16208,7 +16212,7 @@
         </is>
       </c>
       <c r="E619" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F619" s="2" t="n">
         <v>23.45</v>
@@ -16234,7 +16238,7 @@
         </is>
       </c>
       <c r="E620" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F620" s="2" t="n">
         <v>23.45</v>
@@ -16260,7 +16264,7 @@
         </is>
       </c>
       <c r="E621" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F621" s="2" t="n">
         <v>23.45</v>
@@ -16286,7 +16290,7 @@
         </is>
       </c>
       <c r="E622" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F622" s="2" t="n">
         <v>23.45</v>
@@ -16312,7 +16316,7 @@
         </is>
       </c>
       <c r="E623" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F623" s="2" t="n">
         <v>23.45</v>
@@ -16338,7 +16342,7 @@
         </is>
       </c>
       <c r="E624" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F624" s="2" t="n">
         <v>23.45</v>
@@ -16364,7 +16368,7 @@
         </is>
       </c>
       <c r="E625" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F625" s="2" t="n">
         <v>23.45</v>
@@ -16390,7 +16394,7 @@
         </is>
       </c>
       <c r="E626" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F626" s="2" t="n">
         <v>23.45</v>
@@ -16416,7 +16420,7 @@
         </is>
       </c>
       <c r="E627" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F627" s="2" t="n">
         <v>23.45</v>
@@ -16442,7 +16446,7 @@
         </is>
       </c>
       <c r="E628" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F628" s="2" t="n">
         <v>23.45</v>
@@ -16468,7 +16472,7 @@
         </is>
       </c>
       <c r="E629" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F629" s="2" t="n">
         <v>23.45</v>
@@ -16494,7 +16498,7 @@
         </is>
       </c>
       <c r="E630" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F630" s="2" t="n">
         <v>23.45</v>
@@ -16520,7 +16524,7 @@
         </is>
       </c>
       <c r="E631" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F631" s="2" t="n">
         <v>23.45</v>
@@ -16546,7 +16550,7 @@
         </is>
       </c>
       <c r="E632" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F632" s="2" t="n">
         <v>23.45</v>
@@ -16572,7 +16576,7 @@
         </is>
       </c>
       <c r="E633" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F633" s="2" t="n">
         <v>23.45</v>
@@ -16598,7 +16602,7 @@
         </is>
       </c>
       <c r="E634" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F634" s="2" t="n">
         <v>23.45</v>
@@ -16624,7 +16628,7 @@
         </is>
       </c>
       <c r="E635" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F635" s="2" t="n">
         <v>23.45</v>
@@ -16650,7 +16654,7 @@
         </is>
       </c>
       <c r="E636" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F636" s="2" t="n">
         <v>23.45</v>
@@ -16676,7 +16680,7 @@
         </is>
       </c>
       <c r="E637" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F637" s="2" t="n">
         <v>23.45</v>
@@ -16702,7 +16706,7 @@
         </is>
       </c>
       <c r="E638" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F638" s="2" t="n">
         <v>23.45</v>
@@ -16728,7 +16732,7 @@
         </is>
       </c>
       <c r="E639" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F639" s="2" t="n">
         <v>23.45</v>
@@ -16754,7 +16758,7 @@
         </is>
       </c>
       <c r="E640" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F640" s="2" t="n">
         <v>23.45</v>
@@ -16780,7 +16784,7 @@
         </is>
       </c>
       <c r="E641" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F641" s="2" t="n">
         <v>23.45</v>
@@ -16806,7 +16810,7 @@
         </is>
       </c>
       <c r="E642" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F642" s="2" t="n">
         <v>23.45</v>
@@ -16832,7 +16836,7 @@
         </is>
       </c>
       <c r="E643" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F643" s="2" t="n">
         <v>23.45</v>
@@ -16858,7 +16862,7 @@
         </is>
       </c>
       <c r="E644" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F644" s="2" t="n">
         <v>23.45</v>
@@ -16884,7 +16888,7 @@
         </is>
       </c>
       <c r="E645" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F645" s="2" t="n">
         <v>23.45</v>
@@ -16910,7 +16914,7 @@
         </is>
       </c>
       <c r="E646" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F646" s="2" t="n">
         <v>23.45</v>
@@ -16936,7 +16940,7 @@
         </is>
       </c>
       <c r="E647" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F647" s="2" t="n">
         <v>23.45</v>
@@ -16962,7 +16966,7 @@
         </is>
       </c>
       <c r="E648" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F648" s="2" t="n">
         <v>23.45</v>
@@ -16988,7 +16992,7 @@
         </is>
       </c>
       <c r="E649" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F649" s="2" t="n">
         <v>23.45</v>
@@ -17014,7 +17018,7 @@
         </is>
       </c>
       <c r="E650" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F650" s="2" t="n">
         <v>23.45</v>
@@ -17040,7 +17044,7 @@
         </is>
       </c>
       <c r="E651" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F651" s="2" t="n">
         <v>23.45</v>
@@ -17066,7 +17070,7 @@
         </is>
       </c>
       <c r="E652" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F652" s="2" t="n">
         <v>23.45</v>
@@ -17092,7 +17096,7 @@
         </is>
       </c>
       <c r="E653" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F653" s="2" t="n">
         <v>23.45</v>
@@ -17118,7 +17122,7 @@
         </is>
       </c>
       <c r="E654" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F654" s="2" t="n">
         <v>23.45</v>
@@ -17144,7 +17148,7 @@
         </is>
       </c>
       <c r="E655" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F655" s="2" t="n">
         <v>23.45</v>
@@ -17170,7 +17174,7 @@
         </is>
       </c>
       <c r="E656" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F656" s="2" t="n">
         <v>23.45</v>
@@ -17196,7 +17200,7 @@
         </is>
       </c>
       <c r="E657" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F657" s="2" t="n">
         <v>23.45</v>
@@ -17222,7 +17226,7 @@
         </is>
       </c>
       <c r="E658" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F658" s="2" t="n">
         <v>23.45</v>
@@ -17248,7 +17252,7 @@
         </is>
       </c>
       <c r="E659" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F659" s="2" t="n">
         <v>23.45</v>
@@ -17274,7 +17278,7 @@
         </is>
       </c>
       <c r="E660" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F660" s="2" t="n">
         <v>23.45</v>
@@ -17300,7 +17304,7 @@
         </is>
       </c>
       <c r="E661" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F661" s="2" t="n">
         <v>23.45</v>
@@ -17326,7 +17330,7 @@
         </is>
       </c>
       <c r="E662" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F662" s="2" t="n">
         <v>23.45</v>
@@ -17352,7 +17356,7 @@
         </is>
       </c>
       <c r="E663" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F663" s="2" t="n">
         <v>23.45</v>
@@ -17378,7 +17382,7 @@
         </is>
       </c>
       <c r="E664" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F664" s="2" t="n">
         <v>23.45</v>
@@ -17404,7 +17408,7 @@
         </is>
       </c>
       <c r="E665" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F665" s="2" t="n">
         <v>23.45</v>
@@ -17430,7 +17434,7 @@
         </is>
       </c>
       <c r="E666" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F666" s="2" t="n">
         <v>23.45</v>
@@ -17456,7 +17460,7 @@
         </is>
       </c>
       <c r="E667" s="2" t="n">
-        <v>44217.598556226854</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F667" s="2" t="n">
         <v>23.45</v>
@@ -17482,7 +17486,7 @@
         </is>
       </c>
       <c r="E668" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F668" s="2" t="n">
         <v>23.45</v>
@@ -17508,7 +17512,7 @@
         </is>
       </c>
       <c r="E669" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F669" s="2" t="n">
         <v>23.45</v>
@@ -17534,7 +17538,7 @@
         </is>
       </c>
       <c r="E670" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F670" s="2" t="n">
         <v>23.45</v>
@@ -17560,7 +17564,7 @@
         </is>
       </c>
       <c r="E671" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F671" s="2" t="n">
         <v>23.45</v>
@@ -17586,7 +17590,7 @@
         </is>
       </c>
       <c r="E672" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F672" s="2" t="n">
         <v>23.45</v>
@@ -17612,7 +17616,7 @@
         </is>
       </c>
       <c r="E673" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F673" s="2" t="n">
         <v>23.45</v>
@@ -17638,7 +17642,7 @@
         </is>
       </c>
       <c r="E674" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F674" s="2" t="n">
         <v>23.45</v>
@@ -17664,7 +17668,7 @@
         </is>
       </c>
       <c r="E675" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F675" s="2" t="n">
         <v>23.45</v>
@@ -17690,7 +17694,7 @@
         </is>
       </c>
       <c r="E676" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F676" s="2" t="n">
         <v>23.45</v>
@@ -17716,7 +17720,7 @@
         </is>
       </c>
       <c r="E677" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F677" s="2" t="n">
         <v>23.45</v>
@@ -17742,7 +17746,7 @@
         </is>
       </c>
       <c r="E678" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F678" s="2" t="n">
         <v>23.45</v>
@@ -17768,7 +17772,7 @@
         </is>
       </c>
       <c r="E679" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F679" s="2" t="n">
         <v>23.45</v>
@@ -17794,7 +17798,7 @@
         </is>
       </c>
       <c r="E680" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F680" s="2" t="n">
         <v>23.45</v>
@@ -17820,7 +17824,7 @@
         </is>
       </c>
       <c r="E681" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F681" s="2" t="n">
         <v>23.45</v>
@@ -17846,7 +17850,7 @@
         </is>
       </c>
       <c r="E682" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F682" s="2" t="n">
         <v>23.45</v>
@@ -17872,7 +17876,7 @@
         </is>
       </c>
       <c r="E683" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F683" s="2" t="n">
         <v>23.45</v>
@@ -17898,7 +17902,7 @@
         </is>
       </c>
       <c r="E684" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F684" s="2" t="n">
         <v>23.45</v>
@@ -17924,7 +17928,7 @@
         </is>
       </c>
       <c r="E685" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F685" s="2" t="n">
         <v>23.45</v>
@@ -17950,7 +17954,7 @@
         </is>
       </c>
       <c r="E686" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F686" s="2" t="n">
         <v>23.45</v>
@@ -17976,7 +17980,7 @@
         </is>
       </c>
       <c r="E687" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F687" s="2" t="n">
         <v>23.45</v>
@@ -18002,7 +18006,7 @@
         </is>
       </c>
       <c r="E688" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F688" s="2" t="n">
         <v>23.45</v>
@@ -18028,7 +18032,7 @@
         </is>
       </c>
       <c r="E689" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F689" s="2" t="n">
         <v>23.45</v>
@@ -18054,7 +18058,7 @@
         </is>
       </c>
       <c r="E690" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F690" s="2" t="n">
         <v>23.45</v>
@@ -18080,7 +18084,7 @@
         </is>
       </c>
       <c r="E691" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F691" s="2" t="n">
         <v>23.45</v>
@@ -18106,7 +18110,7 @@
         </is>
       </c>
       <c r="E692" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F692" s="2" t="n">
         <v>23.45</v>
@@ -18132,7 +18136,7 @@
         </is>
       </c>
       <c r="E693" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F693" s="2" t="n">
         <v>23.45</v>
@@ -18158,7 +18162,7 @@
         </is>
       </c>
       <c r="E694" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F694" s="2" t="n">
         <v>23.45</v>
@@ -18184,7 +18188,7 @@
         </is>
       </c>
       <c r="E695" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F695" s="2" t="n">
         <v>23.45</v>
@@ -18210,7 +18214,7 @@
         </is>
       </c>
       <c r="E696" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F696" s="2" t="n">
         <v>23.45</v>
@@ -18236,7 +18240,7 @@
         </is>
       </c>
       <c r="E697" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F697" s="2" t="n">
         <v>23.45</v>
@@ -18262,7 +18266,7 @@
         </is>
       </c>
       <c r="E698" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436523148</v>
       </c>
       <c r="F698" s="2" t="n">
         <v>23.45</v>
@@ -18288,7 +18292,7 @@
         </is>
       </c>
       <c r="E699" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F699" s="2" t="n">
         <v>23.45</v>
@@ -18314,7 +18318,7 @@
         </is>
       </c>
       <c r="E700" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F700" s="2" t="n">
         <v>23.45</v>
@@ -18340,7 +18344,7 @@
         </is>
       </c>
       <c r="E701" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F701" s="2" t="n">
         <v>23.45</v>
@@ -18366,7 +18370,7 @@
         </is>
       </c>
       <c r="E702" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F702" s="2" t="n">
         <v>23.45</v>
@@ -18392,7 +18396,7 @@
         </is>
       </c>
       <c r="E703" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F703" s="2" t="n">
         <v>23.45</v>
@@ -18418,7 +18422,7 @@
         </is>
       </c>
       <c r="E704" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F704" s="2" t="n">
         <v>23.45</v>
@@ -18444,7 +18448,7 @@
         </is>
       </c>
       <c r="E705" s="2" t="n">
-        <v>44217.59855623842</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F705" s="2" t="n">
         <v>23.45</v>
@@ -18470,7 +18474,7 @@
         </is>
       </c>
       <c r="E706" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F706" s="2" t="n">
         <v>23.45</v>
@@ -18496,7 +18500,7 @@
         </is>
       </c>
       <c r="E707" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F707" s="2" t="n">
         <v>23.45</v>
@@ -18522,7 +18526,7 @@
         </is>
       </c>
       <c r="E708" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F708" s="2" t="n">
         <v>23.45</v>
@@ -18548,7 +18552,7 @@
         </is>
       </c>
       <c r="E709" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F709" s="2" t="n">
         <v>23.45</v>
@@ -18574,7 +18578,7 @@
         </is>
       </c>
       <c r="E710" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F710" s="2" t="n">
         <v>23.45</v>
@@ -18600,7 +18604,7 @@
         </is>
       </c>
       <c r="E711" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F711" s="2" t="n">
         <v>23.45</v>
@@ -18626,7 +18630,7 @@
         </is>
       </c>
       <c r="E712" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F712" s="2" t="n">
         <v>23.45</v>
@@ -18652,7 +18656,7 @@
         </is>
       </c>
       <c r="E713" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F713" s="2" t="n">
         <v>23.45</v>
@@ -18678,7 +18682,7 @@
         </is>
       </c>
       <c r="E714" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F714" s="2" t="n">
         <v>23.45</v>
@@ -18704,7 +18708,7 @@
         </is>
       </c>
       <c r="E715" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F715" s="2" t="n">
         <v>23.45</v>
@@ -18730,7 +18734,7 @@
         </is>
       </c>
       <c r="E716" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F716" s="2" t="n">
         <v>23.45</v>
@@ -18756,7 +18760,7 @@
         </is>
       </c>
       <c r="E717" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F717" s="2" t="n">
         <v>23.45</v>
@@ -18782,7 +18786,7 @@
         </is>
       </c>
       <c r="E718" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F718" s="2" t="n">
         <v>23.45</v>
@@ -18808,7 +18812,7 @@
         </is>
       </c>
       <c r="E719" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F719" s="2" t="n">
         <v>23.45</v>
@@ -18834,7 +18838,7 @@
         </is>
       </c>
       <c r="E720" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F720" s="2" t="n">
         <v>23.45</v>
@@ -18860,7 +18864,7 @@
         </is>
       </c>
       <c r="E721" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F721" s="2" t="n">
         <v>23.45</v>
@@ -18886,7 +18890,7 @@
         </is>
       </c>
       <c r="E722" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F722" s="2" t="n">
         <v>23.45</v>
@@ -18912,7 +18916,7 @@
         </is>
       </c>
       <c r="E723" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F723" s="2" t="n">
         <v>23.45</v>
@@ -18938,7 +18942,7 @@
         </is>
       </c>
       <c r="E724" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F724" s="2" t="n">
         <v>23.45</v>
@@ -18964,7 +18968,7 @@
         </is>
       </c>
       <c r="E725" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F725" s="2" t="n">
         <v>23.45</v>
@@ -18990,7 +18994,7 @@
         </is>
       </c>
       <c r="E726" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F726" s="2" t="n">
         <v>23.45</v>
@@ -19016,7 +19020,7 @@
         </is>
       </c>
       <c r="E727" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F727" s="2" t="n">
         <v>23.45</v>
@@ -19042,7 +19046,7 @@
         </is>
       </c>
       <c r="E728" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F728" s="2" t="n">
         <v>23.45</v>
@@ -19068,7 +19072,7 @@
         </is>
       </c>
       <c r="E729" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F729" s="2" t="n">
         <v>23.45</v>
@@ -19094,7 +19098,7 @@
         </is>
       </c>
       <c r="E730" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F730" s="2" t="n">
         <v>23.45</v>
@@ -19120,7 +19124,7 @@
         </is>
       </c>
       <c r="E731" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F731" s="2" t="n">
         <v>23.45</v>
@@ -19146,7 +19150,7 @@
         </is>
       </c>
       <c r="E732" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F732" s="2" t="n">
         <v>23.45</v>
@@ -19172,7 +19176,7 @@
         </is>
       </c>
       <c r="E733" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F733" s="2" t="n">
         <v>23.45</v>
@@ -19198,7 +19202,7 @@
         </is>
       </c>
       <c r="E734" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F734" s="2" t="n">
         <v>23.45</v>
@@ -19224,7 +19228,7 @@
         </is>
       </c>
       <c r="E735" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F735" s="2" t="n">
         <v>23.45</v>
@@ -19250,7 +19254,7 @@
         </is>
       </c>
       <c r="E736" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F736" s="2" t="n">
         <v>23.45</v>
@@ -19276,7 +19280,7 @@
         </is>
       </c>
       <c r="E737" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F737" s="2" t="n">
         <v>23.45</v>
@@ -19302,7 +19306,7 @@
         </is>
       </c>
       <c r="E738" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F738" s="2" t="n">
         <v>23.45</v>
@@ -19328,7 +19332,7 @@
         </is>
       </c>
       <c r="E739" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F739" s="2" t="n">
         <v>23.45</v>
@@ -19354,7 +19358,7 @@
         </is>
       </c>
       <c r="E740" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F740" s="2" t="n">
         <v>23.45</v>
@@ -19380,7 +19384,7 @@
         </is>
       </c>
       <c r="E741" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F741" s="2" t="n">
         <v>23.45</v>
@@ -19406,7 +19410,7 @@
         </is>
       </c>
       <c r="E742" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F742" s="2" t="n">
         <v>23.45</v>
@@ -19432,7 +19436,7 @@
         </is>
       </c>
       <c r="E743" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F743" s="2" t="n">
         <v>23.45</v>
@@ -19458,7 +19462,7 @@
         </is>
       </c>
       <c r="E744" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F744" s="2" t="n">
         <v>23.45</v>
@@ -19484,7 +19488,7 @@
         </is>
       </c>
       <c r="E745" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F745" s="2" t="n">
         <v>23.45</v>
@@ -19510,7 +19514,7 @@
         </is>
       </c>
       <c r="E746" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F746" s="2" t="n">
         <v>23.45</v>
@@ -19536,7 +19540,7 @@
         </is>
       </c>
       <c r="E747" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F747" s="2" t="n">
         <v>23.45</v>
@@ -19562,7 +19566,7 @@
         </is>
       </c>
       <c r="E748" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F748" s="2" t="n">
         <v>23.45</v>
@@ -19588,7 +19592,7 @@
         </is>
       </c>
       <c r="E749" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F749" s="2" t="n">
         <v>23.45</v>
@@ -19614,7 +19618,7 @@
         </is>
       </c>
       <c r="E750" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F750" s="2" t="n">
         <v>23.45</v>
@@ -19640,7 +19644,7 @@
         </is>
       </c>
       <c r="E751" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F751" s="2" t="n">
         <v>23.45</v>
@@ -19666,7 +19670,7 @@
         </is>
       </c>
       <c r="E752" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F752" s="2" t="n">
         <v>23.45</v>
@@ -19692,7 +19696,7 @@
         </is>
       </c>
       <c r="E753" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F753" s="2" t="n">
         <v>23.45</v>
@@ -19718,7 +19722,7 @@
         </is>
       </c>
       <c r="E754" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F754" s="2" t="n">
         <v>23.45</v>
@@ -19744,7 +19748,7 @@
         </is>
       </c>
       <c r="E755" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F755" s="2" t="n">
         <v>23.45</v>
@@ -19770,7 +19774,7 @@
         </is>
       </c>
       <c r="E756" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F756" s="2" t="n">
         <v>23.45</v>
@@ -19796,7 +19800,7 @@
         </is>
       </c>
       <c r="E757" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F757" s="2" t="n">
         <v>23.45</v>
@@ -19822,7 +19826,7 @@
         </is>
       </c>
       <c r="E758" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F758" s="2" t="n">
         <v>23.45</v>
@@ -19848,7 +19852,7 @@
         </is>
       </c>
       <c r="E759" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F759" s="2" t="n">
         <v>23.45</v>
@@ -19874,7 +19878,7 @@
         </is>
       </c>
       <c r="E760" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F760" s="2" t="n">
         <v>23.45</v>
@@ -19900,7 +19904,7 @@
         </is>
       </c>
       <c r="E761" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F761" s="2" t="n">
         <v>23.45</v>
@@ -19926,7 +19930,7 @@
         </is>
       </c>
       <c r="E762" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F762" s="2" t="n">
         <v>23.45</v>
@@ -19952,7 +19956,7 @@
         </is>
       </c>
       <c r="E763" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F763" s="2" t="n">
         <v>23.45</v>
@@ -19978,7 +19982,7 @@
         </is>
       </c>
       <c r="E764" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F764" s="2" t="n">
         <v>23.45</v>
@@ -20004,7 +20008,7 @@
         </is>
       </c>
       <c r="E765" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F765" s="2" t="n">
         <v>23.45</v>
@@ -20030,7 +20034,7 @@
         </is>
       </c>
       <c r="E766" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F766" s="2" t="n">
         <v>23.45</v>
@@ -20056,7 +20060,7 @@
         </is>
       </c>
       <c r="E767" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F767" s="2" t="n">
         <v>23.45</v>
@@ -20082,7 +20086,7 @@
         </is>
       </c>
       <c r="E768" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F768" s="2" t="n">
         <v>23.45</v>
@@ -20108,7 +20112,7 @@
         </is>
       </c>
       <c r="E769" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F769" s="2" t="n">
         <v>23.45</v>
@@ -20134,7 +20138,7 @@
         </is>
       </c>
       <c r="E770" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F770" s="2" t="n">
         <v>23.45</v>
@@ -20160,7 +20164,7 @@
         </is>
       </c>
       <c r="E771" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F771" s="2" t="n">
         <v>23.45</v>
@@ -20186,7 +20190,7 @@
         </is>
       </c>
       <c r="E772" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F772" s="2" t="n">
         <v>23.45</v>
@@ -20212,7 +20216,7 @@
         </is>
       </c>
       <c r="E773" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F773" s="2" t="n">
         <v>23.45</v>
@@ -20238,7 +20242,7 @@
         </is>
       </c>
       <c r="E774" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F774" s="2" t="n">
         <v>23.45</v>
@@ -20264,7 +20268,7 @@
         </is>
       </c>
       <c r="E775" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F775" s="2" t="n">
         <v>23.45</v>
@@ -20290,7 +20294,7 @@
         </is>
       </c>
       <c r="E776" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F776" s="2" t="n">
         <v>23.45</v>
@@ -20316,7 +20320,7 @@
         </is>
       </c>
       <c r="E777" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F777" s="2" t="n">
         <v>23.45</v>
@@ -20342,7 +20346,7 @@
         </is>
       </c>
       <c r="E778" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F778" s="2" t="n">
         <v>23.45</v>
@@ -20368,7 +20372,7 @@
         </is>
       </c>
       <c r="E779" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F779" s="2" t="n">
         <v>23.45</v>
@@ -20394,7 +20398,7 @@
         </is>
       </c>
       <c r="E780" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F780" s="2" t="n">
         <v>23.45</v>
@@ -20420,7 +20424,7 @@
         </is>
       </c>
       <c r="E781" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F781" s="2" t="n">
         <v>23.45</v>
@@ -20446,7 +20450,7 @@
         </is>
       </c>
       <c r="E782" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F782" s="2" t="n">
         <v>23.45</v>
@@ -20472,7 +20476,7 @@
         </is>
       </c>
       <c r="E783" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F783" s="2" t="n">
         <v>23.45</v>
@@ -20498,7 +20502,7 @@
         </is>
       </c>
       <c r="E784" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F784" s="2" t="n">
         <v>23.45</v>
@@ -20524,7 +20528,7 @@
         </is>
       </c>
       <c r="E785" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F785" s="2" t="n">
         <v>23.45</v>
@@ -20550,7 +20554,7 @@
         </is>
       </c>
       <c r="E786" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F786" s="2" t="n">
         <v>23.45</v>
@@ -20576,7 +20580,7 @@
         </is>
       </c>
       <c r="E787" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F787" s="2" t="n">
         <v>23.45</v>
@@ -20602,7 +20606,7 @@
         </is>
       </c>
       <c r="E788" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F788" s="2" t="n">
         <v>23.45</v>
@@ -20628,7 +20632,7 @@
         </is>
       </c>
       <c r="E789" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F789" s="2" t="n">
         <v>23.45</v>
@@ -20654,7 +20658,7 @@
         </is>
       </c>
       <c r="E790" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F790" s="2" t="n">
         <v>23.45</v>
@@ -20680,7 +20684,7 @@
         </is>
       </c>
       <c r="E791" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F791" s="2" t="n">
         <v>23.45</v>
@@ -20706,7 +20710,7 @@
         </is>
       </c>
       <c r="E792" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F792" s="2" t="n">
         <v>23.45</v>
@@ -20732,7 +20736,7 @@
         </is>
       </c>
       <c r="E793" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F793" s="2" t="n">
         <v>23.45</v>
@@ -20758,7 +20762,7 @@
         </is>
       </c>
       <c r="E794" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F794" s="2" t="n">
         <v>23.45</v>
@@ -20784,7 +20788,7 @@
         </is>
       </c>
       <c r="E795" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F795" s="2" t="n">
         <v>23.45</v>
@@ -20810,7 +20814,7 @@
         </is>
       </c>
       <c r="E796" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F796" s="2" t="n">
         <v>23.45</v>
@@ -20836,7 +20840,7 @@
         </is>
       </c>
       <c r="E797" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F797" s="2" t="n">
         <v>23.45</v>
@@ -20862,7 +20866,7 @@
         </is>
       </c>
       <c r="E798" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F798" s="2" t="n">
         <v>23.45</v>
@@ -20888,7 +20892,7 @@
         </is>
       </c>
       <c r="E799" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F799" s="2" t="n">
         <v>23.45</v>
@@ -20914,7 +20918,7 @@
         </is>
       </c>
       <c r="E800" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F800" s="2" t="n">
         <v>23.45</v>
@@ -20940,7 +20944,7 @@
         </is>
       </c>
       <c r="E801" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F801" s="2" t="n">
         <v>23.45</v>
@@ -20966,7 +20970,7 @@
         </is>
       </c>
       <c r="E802" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F802" s="2" t="n">
         <v>23.45</v>
@@ -20992,7 +20996,7 @@
         </is>
       </c>
       <c r="E803" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F803" s="2" t="n">
         <v>23.45</v>
@@ -21018,7 +21022,7 @@
         </is>
       </c>
       <c r="E804" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F804" s="2" t="n">
         <v>23.45</v>
@@ -21044,7 +21048,7 @@
         </is>
       </c>
       <c r="E805" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F805" s="2" t="n">
         <v>23.45</v>
@@ -21070,7 +21074,7 @@
         </is>
       </c>
       <c r="E806" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F806" s="2" t="n">
         <v>23.45</v>
@@ -21096,7 +21100,7 @@
         </is>
       </c>
       <c r="E807" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F807" s="2" t="n">
         <v>23.45</v>
@@ -21122,7 +21126,7 @@
         </is>
       </c>
       <c r="E808" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F808" s="2" t="n">
         <v>23.45</v>
@@ -21148,7 +21152,7 @@
         </is>
       </c>
       <c r="E809" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F809" s="2" t="n">
         <v>23.45</v>
@@ -21174,7 +21178,7 @@
         </is>
       </c>
       <c r="E810" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F810" s="2" t="n">
         <v>23.45</v>
@@ -21200,7 +21204,7 @@
         </is>
       </c>
       <c r="E811" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F811" s="2" t="n">
         <v>23.45</v>
@@ -21226,7 +21230,7 @@
         </is>
       </c>
       <c r="E812" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F812" s="2" t="n">
         <v>23.45</v>
@@ -21252,7 +21256,7 @@
         </is>
       </c>
       <c r="E813" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F813" s="2" t="n">
         <v>23.45</v>
@@ -21278,7 +21282,7 @@
         </is>
       </c>
       <c r="E814" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F814" s="2" t="n">
         <v>23.45</v>
@@ -21304,7 +21308,7 @@
         </is>
       </c>
       <c r="E815" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F815" s="2" t="n">
         <v>23.45</v>
@@ -21330,7 +21334,7 @@
         </is>
       </c>
       <c r="E816" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F816" s="2" t="n">
         <v>23.45</v>
@@ -21356,7 +21360,7 @@
         </is>
       </c>
       <c r="E817" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F817" s="2" t="n">
         <v>23.45</v>
@@ -21382,7 +21386,7 @@
         </is>
       </c>
       <c r="E818" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F818" s="2" t="n">
         <v>23.45</v>
@@ -21408,7 +21412,7 @@
         </is>
       </c>
       <c r="E819" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F819" s="2" t="n">
         <v>23.45</v>
@@ -21434,7 +21438,7 @@
         </is>
       </c>
       <c r="E820" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F820" s="2" t="n">
         <v>23.45</v>
@@ -21460,7 +21464,7 @@
         </is>
       </c>
       <c r="E821" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F821" s="2" t="n">
         <v>23.45</v>
@@ -21486,7 +21490,7 @@
         </is>
       </c>
       <c r="E822" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F822" s="2" t="n">
         <v>23.45</v>
@@ -21512,7 +21516,7 @@
         </is>
       </c>
       <c r="E823" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F823" s="2" t="n">
         <v>23.45</v>
@@ -21538,7 +21542,7 @@
         </is>
       </c>
       <c r="E824" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F824" s="2" t="n">
         <v>23.45</v>
@@ -21564,7 +21568,7 @@
         </is>
       </c>
       <c r="E825" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F825" s="2" t="n">
         <v>23.45</v>
@@ -21590,7 +21594,7 @@
         </is>
       </c>
       <c r="E826" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F826" s="2" t="n">
         <v>23.45</v>
@@ -21616,7 +21620,7 @@
         </is>
       </c>
       <c r="E827" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F827" s="2" t="n">
         <v>23.45</v>
@@ -21642,7 +21646,7 @@
         </is>
       </c>
       <c r="E828" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F828" s="2" t="n">
         <v>23.45</v>
@@ -21668,7 +21672,7 @@
         </is>
       </c>
       <c r="E829" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F829" s="2" t="n">
         <v>23.45</v>
@@ -21694,7 +21698,7 @@
         </is>
       </c>
       <c r="E830" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F830" s="2" t="n">
         <v>23.45</v>
@@ -21720,7 +21724,7 @@
         </is>
       </c>
       <c r="E831" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F831" s="2" t="n">
         <v>23.45</v>
@@ -21746,7 +21750,7 @@
         </is>
       </c>
       <c r="E832" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F832" s="2" t="n">
         <v>23.45</v>
@@ -21772,7 +21776,7 @@
         </is>
       </c>
       <c r="E833" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F833" s="2" t="n">
         <v>23.45</v>
@@ -21798,7 +21802,7 @@
         </is>
       </c>
       <c r="E834" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F834" s="2" t="n">
         <v>23.45</v>
@@ -21824,7 +21828,7 @@
         </is>
       </c>
       <c r="E835" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F835" s="2" t="n">
         <v>23.45</v>
@@ -21850,7 +21854,7 @@
         </is>
       </c>
       <c r="E836" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F836" s="2" t="n">
         <v>23.45</v>
@@ -21876,7 +21880,7 @@
         </is>
       </c>
       <c r="E837" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F837" s="2" t="n">
         <v>23.45</v>
@@ -21902,7 +21906,7 @@
         </is>
       </c>
       <c r="E838" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F838" s="2" t="n">
         <v>23.45</v>
@@ -21928,7 +21932,7 @@
         </is>
       </c>
       <c r="E839" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F839" s="2" t="n">
         <v>23.45</v>
@@ -21954,7 +21958,7 @@
         </is>
       </c>
       <c r="E840" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F840" s="2" t="n">
         <v>23.45</v>
@@ -21980,7 +21984,7 @@
         </is>
       </c>
       <c r="E841" s="2" t="n">
-        <v>44217.59855625</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F841" s="2" t="n">
         <v>23.45</v>
@@ -22006,7 +22010,7 @@
         </is>
       </c>
       <c r="E842" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F842" s="2" t="n">
         <v>23.45</v>
@@ -22032,7 +22036,7 @@
         </is>
       </c>
       <c r="E843" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.91436524306</v>
       </c>
       <c r="F843" s="2" t="n">
         <v>23.45</v>
@@ -22058,7 +22062,7 @@
         </is>
       </c>
       <c r="E844" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F844" s="2" t="n">
         <v>23.45</v>
@@ -22084,7 +22088,7 @@
         </is>
       </c>
       <c r="E845" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F845" s="2" t="n">
         <v>23.45</v>
@@ -22110,7 +22114,7 @@
         </is>
       </c>
       <c r="E846" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F846" s="2" t="n">
         <v>23.45</v>
@@ -22136,7 +22140,7 @@
         </is>
       </c>
       <c r="E847" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F847" s="2" t="n">
         <v>23.45</v>
@@ -22162,7 +22166,7 @@
         </is>
       </c>
       <c r="E848" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F848" s="2" t="n">
         <v>23.45</v>
@@ -22188,7 +22192,7 @@
         </is>
       </c>
       <c r="E849" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F849" s="2" t="n">
         <v>23.45</v>
@@ -22214,7 +22218,7 @@
         </is>
       </c>
       <c r="E850" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F850" s="2" t="n">
         <v>23.45</v>
@@ -22240,7 +22244,7 @@
         </is>
       </c>
       <c r="E851" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F851" s="2" t="n">
         <v>23.45</v>
@@ -22266,7 +22270,7 @@
         </is>
       </c>
       <c r="E852" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F852" s="2" t="n">
         <v>23.45</v>
@@ -22292,7 +22296,7 @@
         </is>
       </c>
       <c r="E853" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F853" s="2" t="n">
         <v>23.45</v>
@@ -22318,7 +22322,7 @@
         </is>
       </c>
       <c r="E854" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F854" s="2" t="n">
         <v>23.45</v>
@@ -22344,7 +22348,7 @@
         </is>
       </c>
       <c r="E855" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F855" s="2" t="n">
         <v>23.45</v>
@@ -22370,7 +22374,7 @@
         </is>
       </c>
       <c r="E856" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F856" s="2" t="n">
         <v>23.45</v>
@@ -22396,7 +22400,7 @@
         </is>
       </c>
       <c r="E857" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F857" s="2" t="n">
         <v>23.45</v>
@@ -22422,7 +22426,7 @@
         </is>
       </c>
       <c r="E858" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F858" s="2" t="n">
         <v>23.45</v>
@@ -22448,7 +22452,7 @@
         </is>
       </c>
       <c r="E859" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F859" s="2" t="n">
         <v>23.45</v>
@@ -22474,7 +22478,7 @@
         </is>
       </c>
       <c r="E860" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F860" s="2" t="n">
         <v>23.45</v>
@@ -22500,7 +22504,7 @@
         </is>
       </c>
       <c r="E861" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F861" s="2" t="n">
         <v>23.45</v>
@@ -22526,7 +22530,7 @@
         </is>
       </c>
       <c r="E862" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F862" s="2" t="n">
         <v>23.45</v>
@@ -22552,7 +22556,7 @@
         </is>
       </c>
       <c r="E863" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F863" s="2" t="n">
         <v>23.45</v>
@@ -22578,7 +22582,7 @@
         </is>
       </c>
       <c r="E864" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F864" s="2" t="n">
         <v>23.45</v>
@@ -22604,7 +22608,7 @@
         </is>
       </c>
       <c r="E865" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F865" s="2" t="n">
         <v>23.45</v>
@@ -22630,7 +22634,7 @@
         </is>
       </c>
       <c r="E866" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F866" s="2" t="n">
         <v>23.45</v>
@@ -22656,7 +22660,7 @@
         </is>
       </c>
       <c r="E867" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F867" s="2" t="n">
         <v>23.45</v>
@@ -22682,7 +22686,7 @@
         </is>
       </c>
       <c r="E868" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F868" s="2" t="n">
         <v>23.45</v>
@@ -22708,7 +22712,7 @@
         </is>
       </c>
       <c r="E869" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F869" s="2" t="n">
         <v>23.45</v>
@@ -22734,7 +22738,7 @@
         </is>
       </c>
       <c r="E870" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F870" s="2" t="n">
         <v>23.45</v>
@@ -22760,7 +22764,7 @@
         </is>
       </c>
       <c r="E871" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F871" s="2" t="n">
         <v>23.45</v>
@@ -22786,7 +22790,7 @@
         </is>
       </c>
       <c r="E872" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F872" s="2" t="n">
         <v>23.45</v>
@@ -22812,7 +22816,7 @@
         </is>
       </c>
       <c r="E873" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F873" s="2" t="n">
         <v>23.45</v>
@@ -22838,7 +22842,7 @@
         </is>
       </c>
       <c r="E874" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F874" s="2" t="n">
         <v>23.45</v>
@@ -22864,7 +22868,7 @@
         </is>
       </c>
       <c r="E875" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F875" s="2" t="n">
         <v>23.45</v>
@@ -22890,7 +22894,7 @@
         </is>
       </c>
       <c r="E876" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F876" s="2" t="n">
         <v>23.45</v>
@@ -22916,7 +22920,7 @@
         </is>
       </c>
       <c r="E877" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F877" s="2" t="n">
         <v>23.45</v>
@@ -22942,7 +22946,7 @@
         </is>
       </c>
       <c r="E878" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F878" s="2" t="n">
         <v>23.45</v>
@@ -22968,7 +22972,7 @@
         </is>
       </c>
       <c r="E879" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F879" s="2" t="n">
         <v>23.45</v>
@@ -22994,7 +22998,7 @@
         </is>
       </c>
       <c r="E880" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F880" s="2" t="n">
         <v>23.45</v>
@@ -23020,7 +23024,7 @@
         </is>
       </c>
       <c r="E881" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F881" s="2" t="n">
         <v>23.45</v>
@@ -23046,7 +23050,7 @@
         </is>
       </c>
       <c r="E882" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F882" s="2" t="n">
         <v>23.45</v>
@@ -23072,7 +23076,7 @@
         </is>
       </c>
       <c r="E883" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F883" s="2" t="n">
         <v>23.45</v>
@@ -23098,7 +23102,7 @@
         </is>
       </c>
       <c r="E884" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F884" s="2" t="n">
         <v>23.45</v>
@@ -23124,7 +23128,7 @@
         </is>
       </c>
       <c r="E885" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F885" s="2" t="n">
         <v>23.45</v>
@@ -23150,7 +23154,7 @@
         </is>
       </c>
       <c r="E886" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F886" s="2" t="n">
         <v>23.45</v>
@@ -23176,7 +23180,7 @@
         </is>
       </c>
       <c r="E887" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F887" s="2" t="n">
         <v>23.45</v>
@@ -23202,7 +23206,7 @@
         </is>
       </c>
       <c r="E888" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F888" s="2" t="n">
         <v>23.45</v>
@@ -23228,7 +23232,7 @@
         </is>
       </c>
       <c r="E889" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F889" s="2" t="n">
         <v>23.45</v>
@@ -23254,7 +23258,7 @@
         </is>
       </c>
       <c r="E890" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F890" s="2" t="n">
         <v>23.45</v>
@@ -23280,7 +23284,7 @@
         </is>
       </c>
       <c r="E891" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F891" s="2" t="n">
         <v>23.45</v>
@@ -23306,7 +23310,7 @@
         </is>
       </c>
       <c r="E892" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F892" s="2" t="n">
         <v>23.45</v>
@@ -23332,7 +23336,7 @@
         </is>
       </c>
       <c r="E893" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F893" s="2" t="n">
         <v>23.45</v>
@@ -23358,7 +23362,7 @@
         </is>
       </c>
       <c r="E894" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F894" s="2" t="n">
         <v>23.45</v>
@@ -23384,7 +23388,7 @@
         </is>
       </c>
       <c r="E895" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F895" s="2" t="n">
         <v>23.45</v>
@@ -23410,7 +23414,7 @@
         </is>
       </c>
       <c r="E896" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F896" s="2" t="n">
         <v>23.45</v>
@@ -23436,7 +23440,7 @@
         </is>
       </c>
       <c r="E897" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F897" s="2" t="n">
         <v>23.45</v>
@@ -23462,7 +23466,7 @@
         </is>
       </c>
       <c r="E898" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F898" s="2" t="n">
         <v>23.45</v>
@@ -23488,7 +23492,7 @@
         </is>
       </c>
       <c r="E899" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F899" s="2" t="n">
         <v>23.45</v>
@@ -23514,7 +23518,7 @@
         </is>
       </c>
       <c r="E900" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F900" s="2" t="n">
         <v>23.45</v>
@@ -23540,7 +23544,7 @@
         </is>
       </c>
       <c r="E901" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F901" s="2" t="n">
         <v>23.45</v>
@@ -23566,7 +23570,7 @@
         </is>
       </c>
       <c r="E902" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F902" s="2" t="n">
         <v>23.45</v>
@@ -23592,7 +23596,7 @@
         </is>
       </c>
       <c r="E903" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F903" s="2" t="n">
         <v>23.45</v>
@@ -23618,7 +23622,7 @@
         </is>
       </c>
       <c r="E904" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F904" s="2" t="n">
         <v>23.45</v>
@@ -23644,7 +23648,7 @@
         </is>
       </c>
       <c r="E905" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F905" s="2" t="n">
         <v>23.45</v>
@@ -23670,7 +23674,7 @@
         </is>
       </c>
       <c r="E906" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F906" s="2" t="n">
         <v>23.45</v>
@@ -23696,7 +23700,7 @@
         </is>
       </c>
       <c r="E907" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F907" s="2" t="n">
         <v>23.45</v>
@@ -23722,7 +23726,7 @@
         </is>
       </c>
       <c r="E908" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F908" s="2" t="n">
         <v>23.45</v>
@@ -23748,7 +23752,7 @@
         </is>
       </c>
       <c r="E909" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F909" s="2" t="n">
         <v>23.45</v>
@@ -23774,7 +23778,7 @@
         </is>
       </c>
       <c r="E910" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F910" s="2" t="n">
         <v>23.45</v>
@@ -23800,7 +23804,7 @@
         </is>
       </c>
       <c r="E911" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F911" s="2" t="n">
         <v>23.45</v>
@@ -23826,7 +23830,7 @@
         </is>
       </c>
       <c r="E912" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F912" s="2" t="n">
         <v>23.45</v>
@@ -23852,7 +23856,7 @@
         </is>
       </c>
       <c r="E913" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F913" s="2" t="n">
         <v>23.45</v>
@@ -23878,7 +23882,7 @@
         </is>
       </c>
       <c r="E914" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F914" s="2" t="n">
         <v>23.45</v>
@@ -23904,7 +23908,7 @@
         </is>
       </c>
       <c r="E915" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F915" s="2" t="n">
         <v>23.45</v>
@@ -23930,7 +23934,7 @@
         </is>
       </c>
       <c r="E916" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F916" s="2" t="n">
         <v>23.45</v>
@@ -23956,7 +23960,7 @@
         </is>
       </c>
       <c r="E917" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F917" s="2" t="n">
         <v>23.45</v>
@@ -23982,7 +23986,7 @@
         </is>
       </c>
       <c r="E918" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F918" s="2" t="n">
         <v>23.45</v>
@@ -24008,7 +24012,7 @@
         </is>
       </c>
       <c r="E919" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F919" s="2" t="n">
         <v>23.45</v>
@@ -24034,7 +24038,7 @@
         </is>
       </c>
       <c r="E920" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F920" s="2" t="n">
         <v>23.45</v>
@@ -24060,7 +24064,7 @@
         </is>
       </c>
       <c r="E921" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F921" s="2" t="n">
         <v>23.45</v>
@@ -24086,7 +24090,7 @@
         </is>
       </c>
       <c r="E922" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F922" s="2" t="n">
         <v>23.45</v>
@@ -24112,7 +24116,7 @@
         </is>
       </c>
       <c r="E923" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F923" s="2" t="n">
         <v>23.45</v>
@@ -24138,7 +24142,7 @@
         </is>
       </c>
       <c r="E924" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F924" s="2" t="n">
         <v>23.45</v>
@@ -24164,7 +24168,7 @@
         </is>
       </c>
       <c r="E925" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F925" s="2" t="n">
         <v>23.45</v>
@@ -24190,7 +24194,7 @@
         </is>
       </c>
       <c r="E926" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F926" s="2" t="n">
         <v>23.45</v>
@@ -24216,7 +24220,7 @@
         </is>
       </c>
       <c r="E927" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F927" s="2" t="n">
         <v>23.45</v>
@@ -24242,7 +24246,7 @@
         </is>
       </c>
       <c r="E928" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F928" s="2" t="n">
         <v>23.45</v>
@@ -24268,7 +24272,7 @@
         </is>
       </c>
       <c r="E929" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F929" s="2" t="n">
         <v>23.45</v>
@@ -24294,7 +24298,7 @@
         </is>
       </c>
       <c r="E930" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F930" s="2" t="n">
         <v>23.45</v>
@@ -24320,7 +24324,7 @@
         </is>
       </c>
       <c r="E931" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F931" s="2" t="n">
         <v>23.45</v>
@@ -24346,7 +24350,7 @@
         </is>
       </c>
       <c r="E932" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F932" s="2" t="n">
         <v>23.45</v>
@@ -24372,7 +24376,7 @@
         </is>
       </c>
       <c r="E933" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F933" s="2" t="n">
         <v>23.45</v>
@@ -24398,7 +24402,7 @@
         </is>
       </c>
       <c r="E934" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F934" s="2" t="n">
         <v>23.45</v>
@@ -24424,7 +24428,7 @@
         </is>
       </c>
       <c r="E935" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F935" s="2" t="n">
         <v>23.45</v>
@@ -24450,7 +24454,7 @@
         </is>
       </c>
       <c r="E936" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F936" s="2" t="n">
         <v>23.45</v>
@@ -24476,7 +24480,7 @@
         </is>
       </c>
       <c r="E937" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F937" s="2" t="n">
         <v>23.45</v>
@@ -24502,7 +24506,7 @@
         </is>
       </c>
       <c r="E938" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F938" s="2" t="n">
         <v>23.45</v>
@@ -24528,7 +24532,7 @@
         </is>
       </c>
       <c r="E939" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F939" s="2" t="n">
         <v>23.45</v>
@@ -24554,7 +24558,7 @@
         </is>
       </c>
       <c r="E940" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F940" s="2" t="n">
         <v>23.45</v>
@@ -24580,7 +24584,7 @@
         </is>
       </c>
       <c r="E941" s="2" t="n">
-        <v>44217.598556261575</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F941" s="2" t="n">
         <v>23.45</v>
@@ -24606,7 +24610,7 @@
         </is>
       </c>
       <c r="E942" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F942" s="2" t="n">
         <v>23.45</v>
@@ -24632,7 +24636,7 @@
         </is>
       </c>
       <c r="E943" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F943" s="2" t="n">
         <v>23.45</v>
@@ -24658,7 +24662,7 @@
         </is>
       </c>
       <c r="E944" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F944" s="2" t="n">
         <v>23.45</v>
@@ -24684,7 +24688,7 @@
         </is>
       </c>
       <c r="E945" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F945" s="2" t="n">
         <v>23.45</v>
@@ -24710,7 +24714,7 @@
         </is>
       </c>
       <c r="E946" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F946" s="2" t="n">
         <v>23.45</v>
@@ -24736,7 +24740,7 @@
         </is>
       </c>
       <c r="E947" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F947" s="2" t="n">
         <v>23.45</v>
@@ -24762,7 +24766,7 @@
         </is>
       </c>
       <c r="E948" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F948" s="2" t="n">
         <v>23.45</v>
@@ -24788,7 +24792,7 @@
         </is>
       </c>
       <c r="E949" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F949" s="2" t="n">
         <v>23.45</v>
@@ -24814,7 +24818,7 @@
         </is>
       </c>
       <c r="E950" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F950" s="2" t="n">
         <v>23.45</v>
@@ -24840,7 +24844,7 @@
         </is>
       </c>
       <c r="E951" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F951" s="2" t="n">
         <v>23.45</v>
@@ -24866,7 +24870,7 @@
         </is>
       </c>
       <c r="E952" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F952" s="2" t="n">
         <v>23.45</v>
@@ -24892,7 +24896,7 @@
         </is>
       </c>
       <c r="E953" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F953" s="2" t="n">
         <v>23.45</v>
@@ -24918,7 +24922,7 @@
         </is>
       </c>
       <c r="E954" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F954" s="2" t="n">
         <v>23.45</v>
@@ -24944,7 +24948,7 @@
         </is>
       </c>
       <c r="E955" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F955" s="2" t="n">
         <v>23.45</v>
@@ -24970,7 +24974,7 @@
         </is>
       </c>
       <c r="E956" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F956" s="2" t="n">
         <v>23.45</v>
@@ -24996,7 +25000,7 @@
         </is>
       </c>
       <c r="E957" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F957" s="2" t="n">
         <v>23.45</v>
@@ -25022,7 +25026,7 @@
         </is>
       </c>
       <c r="E958" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F958" s="2" t="n">
         <v>23.45</v>
@@ -25048,7 +25052,7 @@
         </is>
       </c>
       <c r="E959" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F959" s="2" t="n">
         <v>23.45</v>
@@ -25074,7 +25078,7 @@
         </is>
       </c>
       <c r="E960" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F960" s="2" t="n">
         <v>23.45</v>
@@ -25100,7 +25104,7 @@
         </is>
       </c>
       <c r="E961" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F961" s="2" t="n">
         <v>23.45</v>
@@ -25126,7 +25130,7 @@
         </is>
       </c>
       <c r="E962" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F962" s="2" t="n">
         <v>23.45</v>
@@ -25152,7 +25156,7 @@
         </is>
       </c>
       <c r="E963" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F963" s="2" t="n">
         <v>23.45</v>
@@ -25178,7 +25182,7 @@
         </is>
       </c>
       <c r="E964" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F964" s="2" t="n">
         <v>23.45</v>
@@ -25204,7 +25208,7 @@
         </is>
       </c>
       <c r="E965" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F965" s="2" t="n">
         <v>23.45</v>
@@ -25230,7 +25234,7 @@
         </is>
       </c>
       <c r="E966" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F966" s="2" t="n">
         <v>23.45</v>
@@ -25256,7 +25260,7 @@
         </is>
       </c>
       <c r="E967" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F967" s="2" t="n">
         <v>23.45</v>
@@ -25282,7 +25286,7 @@
         </is>
       </c>
       <c r="E968" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F968" s="2" t="n">
         <v>23.45</v>
@@ -25308,7 +25312,7 @@
         </is>
       </c>
       <c r="E969" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F969" s="2" t="n">
         <v>23.45</v>
@@ -25334,7 +25338,7 @@
         </is>
       </c>
       <c r="E970" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F970" s="2" t="n">
         <v>23.45</v>
@@ -25360,7 +25364,7 @@
         </is>
       </c>
       <c r="E971" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F971" s="2" t="n">
         <v>23.45</v>
@@ -25386,7 +25390,7 @@
         </is>
       </c>
       <c r="E972" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F972" s="2" t="n">
         <v>23.45</v>
@@ -25412,7 +25416,7 @@
         </is>
       </c>
       <c r="E973" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F973" s="2" t="n">
         <v>23.45</v>
@@ -25438,7 +25442,7 @@
         </is>
       </c>
       <c r="E974" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F974" s="2" t="n">
         <v>23.45</v>
@@ -25464,7 +25468,7 @@
         </is>
       </c>
       <c r="E975" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F975" s="2" t="n">
         <v>23.45</v>
@@ -25490,7 +25494,7 @@
         </is>
       </c>
       <c r="E976" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F976" s="2" t="n">
         <v>23.45</v>
@@ -25516,7 +25520,7 @@
         </is>
       </c>
       <c r="E977" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F977" s="2" t="n">
         <v>23.45</v>
@@ -25542,7 +25546,7 @@
         </is>
       </c>
       <c r="E978" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F978" s="2" t="n">
         <v>23.45</v>
@@ -25568,7 +25572,7 @@
         </is>
       </c>
       <c r="E979" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F979" s="2" t="n">
         <v>23.45</v>
@@ -25594,7 +25598,7 @@
         </is>
       </c>
       <c r="E980" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F980" s="2" t="n">
         <v>23.45</v>
@@ -25620,7 +25624,7 @@
         </is>
       </c>
       <c r="E981" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F981" s="2" t="n">
         <v>23.45</v>
@@ -25646,7 +25650,7 @@
         </is>
       </c>
       <c r="E982" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F982" s="2" t="n">
         <v>23.45</v>
@@ -25672,7 +25676,7 @@
         </is>
       </c>
       <c r="E983" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F983" s="2" t="n">
         <v>23.45</v>
@@ -25698,7 +25702,7 @@
         </is>
       </c>
       <c r="E984" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F984" s="2" t="n">
         <v>23.45</v>
@@ -25724,7 +25728,7 @@
         </is>
       </c>
       <c r="E985" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F985" s="2" t="n">
         <v>23.45</v>
@@ -25750,7 +25754,7 @@
         </is>
       </c>
       <c r="E986" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F986" s="2" t="n">
         <v>23.45</v>
@@ -25776,7 +25780,7 @@
         </is>
       </c>
       <c r="E987" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F987" s="2" t="n">
         <v>23.45</v>
@@ -25802,7 +25806,7 @@
         </is>
       </c>
       <c r="E988" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F988" s="2" t="n">
         <v>23.45</v>
@@ -25828,7 +25832,7 @@
         </is>
       </c>
       <c r="E989" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F989" s="2" t="n">
         <v>23.45</v>
@@ -25854,7 +25858,7 @@
         </is>
       </c>
       <c r="E990" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F990" s="2" t="n">
         <v>23.45</v>
@@ -25880,7 +25884,7 @@
         </is>
       </c>
       <c r="E991" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F991" s="2" t="n">
         <v>23.45</v>
@@ -25906,7 +25910,7 @@
         </is>
       </c>
       <c r="E992" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F992" s="2" t="n">
         <v>23.45</v>
@@ -25932,7 +25936,7 @@
         </is>
       </c>
       <c r="E993" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F993" s="2" t="n">
         <v>23.45</v>
@@ -25958,7 +25962,7 @@
         </is>
       </c>
       <c r="E994" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F994" s="2" t="n">
         <v>23.45</v>
@@ -25984,7 +25988,7 @@
         </is>
       </c>
       <c r="E995" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F995" s="2" t="n">
         <v>23.45</v>
@@ -26010,7 +26014,7 @@
         </is>
       </c>
       <c r="E996" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F996" s="2" t="n">
         <v>23.45</v>
@@ -26036,7 +26040,7 @@
         </is>
       </c>
       <c r="E997" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F997" s="2" t="n">
         <v>23.45</v>
@@ -26062,7 +26066,7 @@
         </is>
       </c>
       <c r="E998" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F998" s="2" t="n">
         <v>23.45</v>
@@ -26088,7 +26092,7 @@
         </is>
       </c>
       <c r="E999" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F999" s="2" t="n">
         <v>23.45</v>
@@ -26114,7 +26118,7 @@
         </is>
       </c>
       <c r="E1000" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F1000" s="2" t="n">
         <v>23.45</v>
@@ -26140,7 +26144,7 @@
         </is>
       </c>
       <c r="E1001" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F1001" s="2" t="n">
         <v>23.45</v>
@@ -26166,7 +26170,7 @@
         </is>
       </c>
       <c r="E1002" s="2" t="n">
-        <v>44217.59855627315</v>
+        <v>44219.914365254626</v>
       </c>
       <c r="F1002" s="2" t="n">
         <v>23.45</v>
@@ -26177,7 +26181,7 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F2"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
